--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -10,16 +10,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entities" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curves" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Notes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brent_vs_Bisection" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve_Interface" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Entities" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Parameters" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Quotes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Bootstrap" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Solver" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Schedule" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Pricer" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Validation" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Root_Methods" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brent_vs_Bisection" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve_Interface" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Entities" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Parameters" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Quotes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Bootstrap" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Solver" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Schedule" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Pricer" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Validation" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_DATE">Curve_Interface!$O$5</definedName>
@@ -295,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -562,6 +563,14 @@
     <xf numFmtId="167" fontId="17" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1123,6 +1132,21 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>B-Model</author>
+  </authors>
+  <commentList>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>This is what Hazard_Solver does in cells - 30 halvings per tenor. The baseline for the comparison.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
     <author>B-Model white paper</author>
   </authors>
   <commentList>
@@ -1136,7 +1160,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>B-Model white paper</author>
@@ -1153,7 +1177,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>B-Model white paper</author>
@@ -1183,7 +1207,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>B-Model white paper</author>
@@ -1200,7 +1224,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>B-Model white paper</author>
@@ -1267,7 +1291,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>B-Model white paper</author>
@@ -1964,6 +1988,399 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hazard_Bootstrap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="65" t="inlineStr">
+        <is>
+          <t>Piecewise-constant hazard. Col D solved live by Hazard_Solver, no Goal Seek. CDS_Parameters!B17 switches to a flat hazard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="70" t="inlineStr">
+        <is>
+          <t>Maturity by maturity: hold earlier hazards fixed, solve the current segment so model spread = market. Col J (repricing error) stays ~0 as inputs move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="140" t="inlineStr">
+        <is>
+          <t>Tenor</t>
+        </is>
+      </c>
+      <c r="B6" s="140" t="inlineStr">
+        <is>
+          <t>Maturity</t>
+        </is>
+      </c>
+      <c r="C6" s="140" t="inlineStr">
+        <is>
+          <t>Market spread (bp)</t>
+        </is>
+      </c>
+      <c r="D6" s="140" t="inlineStr">
+        <is>
+          <t>Hazard lambda (solve)</t>
+        </is>
+      </c>
+      <c r="E6" s="140" t="inlineStr">
+        <is>
+          <t>Cum. survival Q(T)</t>
+        </is>
+      </c>
+      <c r="F6" s="140" t="inlineStr">
+        <is>
+          <t>Cum. default 1-Q</t>
+        </is>
+      </c>
+      <c r="G6" s="140" t="inlineStr">
+        <is>
+          <t>RPV01 (risky annuity)</t>
+        </is>
+      </c>
+      <c r="H6" s="140" t="inlineStr">
+        <is>
+          <t>Protection PV factor</t>
+        </is>
+      </c>
+      <c r="I6" s="140" t="inlineStr">
+        <is>
+          <t>Model spread (bp)</t>
+        </is>
+      </c>
+      <c r="J6" s="140" t="inlineStr">
+        <is>
+          <t>Repricing error (bp)</t>
+        </is>
+      </c>
+      <c r="L6" s="140" t="inlineStr">
+        <is>
+          <t>Solver resid</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="B7" s="18">
+        <f>CDS_Quotes!C7</f>
+        <v/>
+      </c>
+      <c r="C7" s="17">
+        <f>CDS_Quotes!F7</f>
+        <v/>
+      </c>
+      <c r="D7" s="71">
+        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,Hazard_Solver!$B$46)</f>
+        <v/>
+      </c>
+      <c r="E7" s="34">
+        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B7,CDS_Schedule!$C$7:$C$46,1))</f>
+        <v/>
+      </c>
+      <c r="F7" s="34">
+        <f>1-E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B7,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B7,CDS_Schedule!$N$7:$N$46)</f>
+        <v/>
+      </c>
+      <c r="H7" s="36">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B7,CDS_Schedule!$O$7:$O$46)</f>
+        <v/>
+      </c>
+      <c r="I7" s="131">
+        <f>(1-CDS_Parameters!$B$8)*H7/(G7-CDS_Parameters!$B$26)*10000</f>
+        <v/>
+      </c>
+      <c r="J7" s="53">
+        <f>I7-C7</f>
+        <v/>
+      </c>
+      <c r="L7" s="72">
+        <f>Hazard_Solver!$D$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>CDS_Quotes!C8</f>
+        <v/>
+      </c>
+      <c r="C8" s="17">
+        <f>CDS_Quotes!F8</f>
+        <v/>
+      </c>
+      <c r="D8" s="71">
+        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,Hazard_Solver!$B$89)</f>
+        <v/>
+      </c>
+      <c r="E8" s="34">
+        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B8,CDS_Schedule!$C$7:$C$46,1))</f>
+        <v/>
+      </c>
+      <c r="F8" s="34">
+        <f>1-E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$N$7:$N$46)</f>
+        <v/>
+      </c>
+      <c r="H8" s="36">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)</f>
+        <v/>
+      </c>
+      <c r="I8" s="131">
+        <f>(1-CDS_Parameters!$B$8)*H8/(G8-CDS_Parameters!$B$26)*10000</f>
+        <v/>
+      </c>
+      <c r="J8" s="53">
+        <f>I8-C8</f>
+        <v/>
+      </c>
+      <c r="L8" s="72">
+        <f>Hazard_Solver!$D$89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="B9" s="18">
+        <f>CDS_Quotes!C9</f>
+        <v/>
+      </c>
+      <c r="C9" s="17">
+        <f>CDS_Quotes!F9</f>
+        <v/>
+      </c>
+      <c r="D9" s="71">
+        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,Hazard_Solver!$B$132)</f>
+        <v/>
+      </c>
+      <c r="E9" s="34">
+        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B9,CDS_Schedule!$C$7:$C$46,1))</f>
+        <v/>
+      </c>
+      <c r="F9" s="34">
+        <f>1-E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B9,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B9,CDS_Schedule!$N$7:$N$46)</f>
+        <v/>
+      </c>
+      <c r="H9" s="36">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B9,CDS_Schedule!$O$7:$O$46)</f>
+        <v/>
+      </c>
+      <c r="I9" s="131">
+        <f>(1-CDS_Parameters!$B$8)*H9/(G9-CDS_Parameters!$B$26)*10000</f>
+        <v/>
+      </c>
+      <c r="J9" s="53">
+        <f>I9-C9</f>
+        <v/>
+      </c>
+      <c r="L9" s="72">
+        <f>Hazard_Solver!$D$132</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="B10" s="18">
+        <f>CDS_Quotes!C10</f>
+        <v/>
+      </c>
+      <c r="C10" s="17">
+        <f>CDS_Quotes!F10</f>
+        <v/>
+      </c>
+      <c r="D10" s="71">
+        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,Hazard_Solver!$B$175)</f>
+        <v/>
+      </c>
+      <c r="E10" s="34">
+        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B10,CDS_Schedule!$C$7:$C$46,1))</f>
+        <v/>
+      </c>
+      <c r="F10" s="34">
+        <f>1-E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B10,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B10,CDS_Schedule!$N$7:$N$46)</f>
+        <v/>
+      </c>
+      <c r="H10" s="36">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B10,CDS_Schedule!$O$7:$O$46)</f>
+        <v/>
+      </c>
+      <c r="I10" s="131">
+        <f>(1-CDS_Parameters!$B$8)*H10/(G10-CDS_Parameters!$B$26)*10000</f>
+        <v/>
+      </c>
+      <c r="J10" s="53">
+        <f>I10-C10</f>
+        <v/>
+      </c>
+      <c r="L10" s="72">
+        <f>Hazard_Solver!$D$175</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="B11" s="18">
+        <f>CDS_Quotes!C11</f>
+        <v/>
+      </c>
+      <c r="C11" s="17">
+        <f>CDS_Quotes!F11</f>
+        <v/>
+      </c>
+      <c r="D11" s="71">
+        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,Hazard_Solver!$B$218)</f>
+        <v/>
+      </c>
+      <c r="E11" s="34">
+        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B11,CDS_Schedule!$C$7:$C$46,1))</f>
+        <v/>
+      </c>
+      <c r="F11" s="34">
+        <f>1-E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B11,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B11,CDS_Schedule!$N$7:$N$46)</f>
+        <v/>
+      </c>
+      <c r="H11" s="36">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B11,CDS_Schedule!$O$7:$O$46)</f>
+        <v/>
+      </c>
+      <c r="I11" s="131">
+        <f>(1-CDS_Parameters!$B$8)*H11/(G11-CDS_Parameters!$B$26)*10000</f>
+        <v/>
+      </c>
+      <c r="J11" s="53">
+        <f>I11-C11</f>
+        <v/>
+      </c>
+      <c r="L11" s="72">
+        <f>Hazard_Solver!$D$218</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="B12" s="18">
+        <f>CDS_Quotes!C12</f>
+        <v/>
+      </c>
+      <c r="C12" s="17">
+        <f>CDS_Quotes!F12</f>
+        <v/>
+      </c>
+      <c r="D12" s="71">
+        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,Hazard_Solver!$B$261)</f>
+        <v/>
+      </c>
+      <c r="E12" s="34">
+        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B12,CDS_Schedule!$C$7:$C$46,1))</f>
+        <v/>
+      </c>
+      <c r="F12" s="34">
+        <f>1-E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B12,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B12,CDS_Schedule!$N$7:$N$46)</f>
+        <v/>
+      </c>
+      <c r="H12" s="36">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B12,CDS_Schedule!$O$7:$O$46)</f>
+        <v/>
+      </c>
+      <c r="I12" s="131">
+        <f>(1-CDS_Parameters!$B$8)*H12/(G12-CDS_Parameters!$B$26)*10000</f>
+        <v/>
+      </c>
+      <c r="J12" s="53">
+        <f>I12-C12</f>
+        <v/>
+      </c>
+      <c r="L12" s="72">
+        <f>Hazard_Solver!$D$261</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:J5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="006A1B9A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:V261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -18940,7 +19357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006A1B9A"/>
@@ -21613,7 +22030,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006A1B9A"/>
@@ -22348,7 +22765,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006A1B9A"/>
@@ -24608,6 +25025,758 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="86" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="176" t="inlineStr">
+        <is>
+          <t>Root-finding methods on the hazard strip</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="177" t="inlineStr">
+        <is>
+          <t>Every method solves the same objective at the same step: f(h) = (1-R)*Prot(h) - S*(RPV01(h) - AI), B-Model (3.3). They must agree - what differs is cost and robustness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="98" t="inlineStr">
+        <is>
+          <t>BASELINE is the scheme, not the algorithm. Section 4 p.8 fixes piecewise-constant hazard solved maturity by maturity, each one a 1-D root-find with earlier hazards held fixed; it does not name a method. Hazard_Solver in this workbook is bisection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="177" t="inlineStr">
+        <is>
+          <t>Needs CDSBrent.bas and CDSRootFinders.bas imported, saved as .xlsm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="188" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B6" s="188" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C6" s="188" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="D6" s="188" t="inlineStr">
+        <is>
+          <t>Needs</t>
+        </is>
+      </c>
+      <c r="E6" s="188" t="inlineStr">
+        <is>
+          <t>Bracketed</t>
+        </is>
+      </c>
+      <c r="F6" s="188" t="inlineStr">
+        <is>
+          <t>5Y hazard</t>
+        </is>
+      </c>
+      <c r="G6" s="188" t="inlineStr">
+        <is>
+          <t>its</t>
+        </is>
+      </c>
+      <c r="H6" s="188" t="inlineStr">
+        <is>
+          <t>|f(root)|</t>
+        </is>
+      </c>
+      <c r="I6" s="188" t="inlineStr">
+        <is>
+          <t>vs baseline</t>
+        </is>
+      </c>
+      <c r="J6" s="188" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="189" t="inlineStr">
+        <is>
+          <t>BISECTION</t>
+        </is>
+      </c>
+      <c r="B7" s="189" t="inlineStr">
+        <is>
+          <t>bracketing</t>
+        </is>
+      </c>
+      <c r="C7" s="190" t="inlineStr">
+        <is>
+          <t>linear (halves)</t>
+        </is>
+      </c>
+      <c r="D7" s="190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E7" s="190" t="inlineStr">
+        <is>
+          <t>yes, always</t>
+        </is>
+      </c>
+      <c r="F7" s="191">
+        <f>IFERROR(CDS_Root("BISECTION",Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142),"module not loaded")</f>
+        <v/>
+      </c>
+      <c r="G7" s="180">
+        <f>IFERROR(CDS_RootIterations(),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="192">
+        <f>IFERROR(ABS(CDS_Objective(F7,Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142)),"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="192">
+        <f>IF(ISNUMBER(F7),F7-Hazard_Solver!$B$175,"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="190" t="inlineStr">
+        <is>
+          <t>The safe floor. Cannot fail once bracketed, but pays for it - ~52 steps to machine precision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="190" t="inlineStr">
+        <is>
+          <t>FALSE POSITION</t>
+        </is>
+      </c>
+      <c r="B8" s="190" t="inlineStr">
+        <is>
+          <t>bracketing</t>
+        </is>
+      </c>
+      <c r="C8" s="190" t="inlineStr">
+        <is>
+          <t>super-linear</t>
+        </is>
+      </c>
+      <c r="D8" s="190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E8" s="190" t="inlineStr">
+        <is>
+          <t>yes, always</t>
+        </is>
+      </c>
+      <c r="F8" s="191">
+        <f>IFERROR(CDS_Root("FALSE POSITION",Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142),"module not loaded")</f>
+        <v/>
+      </c>
+      <c r="G8" s="180">
+        <f>IFERROR(CDS_RootIterations(),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="192">
+        <f>IFERROR(ABS(CDS_Objective(F8,Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142)),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="192">
+        <f>IF(ISNUMBER(F8),F8-Hazard_Solver!$B$175,"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="190" t="inlineStr">
+        <is>
+          <t>Keeps a bracket like bisection but interpolates. Can stall when one end stays fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="190" t="inlineStr">
+        <is>
+          <t>SECANT</t>
+        </is>
+      </c>
+      <c r="B9" s="190" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="C9" s="190" t="inlineStr">
+        <is>
+          <t>~1.618</t>
+        </is>
+      </c>
+      <c r="D9" s="190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E9" s="190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F9" s="191">
+        <f>IFERROR(CDS_Root("SECANT",Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142),"module not loaded")</f>
+        <v/>
+      </c>
+      <c r="G9" s="180">
+        <f>IFERROR(CDS_RootIterations(),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="192">
+        <f>IFERROR(ABS(CDS_Objective(F9,Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142)),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="192">
+        <f>IF(ISNUMBER(F9),F9-Hazard_Solver!$B$175,"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="190" t="inlineStr">
+        <is>
+          <t>Newton without a derivative, using the secant of the last two points. No bracket, so it can leave the domain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="190" t="inlineStr">
+        <is>
+          <t>NEWTON</t>
+        </is>
+      </c>
+      <c r="B10" s="190" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="C10" s="190" t="inlineStr">
+        <is>
+          <t>2 (quadratic)</t>
+        </is>
+      </c>
+      <c r="D10" s="190" t="inlineStr">
+        <is>
+          <t>f'</t>
+        </is>
+      </c>
+      <c r="E10" s="190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F10" s="191">
+        <f>IFERROR(CDS_Root("NEWTON",Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142),"module not loaded")</f>
+        <v/>
+      </c>
+      <c r="G10" s="180">
+        <f>IFERROR(CDS_RootIterations(),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="192">
+        <f>IFERROR(ABS(CDS_Objective(F10,Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142)),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="192">
+        <f>IF(ISNUMBER(F10),F10-Hazard_Solver!$B$175,"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="190" t="inlineStr">
+        <is>
+          <t>Householder d=1. Derivative is analytic here - dQ/dh = -cum*Q - so no bumping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="190" t="inlineStr">
+        <is>
+          <t>HALLEY</t>
+        </is>
+      </c>
+      <c r="B11" s="190" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="C11" s="190" t="inlineStr">
+        <is>
+          <t>3 (cubic)</t>
+        </is>
+      </c>
+      <c r="D11" s="190" t="inlineStr">
+        <is>
+          <t>f', f''</t>
+        </is>
+      </c>
+      <c r="E11" s="190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F11" s="191">
+        <f>IFERROR(CDS_Root("HALLEY",Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142),"module not loaded")</f>
+        <v/>
+      </c>
+      <c r="G11" s="180">
+        <f>IFERROR(CDS_RootIterations(),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="192">
+        <f>IFERROR(ABS(CDS_Objective(F11,Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142)),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="192">
+        <f>IF(ISNUMBER(F11),F11-Hazard_Solver!$B$175,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="190" t="inlineStr">
+        <is>
+          <t>Householder d=2. Second derivative also analytic: d2Q/dh2 = cum^2*Q.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="190" t="inlineStr">
+        <is>
+          <t>HOUSEHOLDER</t>
+        </is>
+      </c>
+      <c r="B12" s="190" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="C12" s="190" t="inlineStr">
+        <is>
+          <t>d+1</t>
+        </is>
+      </c>
+      <c r="D12" s="190" t="inlineStr">
+        <is>
+          <t>f' ... f^(d)</t>
+        </is>
+      </c>
+      <c r="E12" s="190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F12" s="191">
+        <f>IFERROR(CDS_Root("HOUSEHOLDER",Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142),"module not loaded")</f>
+        <v/>
+      </c>
+      <c r="G12" s="180">
+        <f>IFERROR(CDS_RootIterations(),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="192">
+        <f>IFERROR(ABS(CDS_Objective(F12,Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142)),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="192">
+        <f>IF(ISNUMBER(F12),F12-Hazard_Solver!$B$175,"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="190" t="inlineStr">
+        <is>
+          <t>General order d. d=1 reduces to Newton and d=2 to Halley, the M2 identity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="190" t="inlineStr">
+        <is>
+          <t>RIDDERS</t>
+        </is>
+      </c>
+      <c r="B13" s="190" t="inlineStr">
+        <is>
+          <t>bracketing hybrid</t>
+        </is>
+      </c>
+      <c r="C13" s="190" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="D13" s="190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E13" s="190" t="inlineStr">
+        <is>
+          <t>yes, always</t>
+        </is>
+      </c>
+      <c r="F13" s="191">
+        <f>IFERROR(CDS_Root("RIDDERS",Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142),"module not loaded")</f>
+        <v/>
+      </c>
+      <c r="G13" s="180">
+        <f>IFERROR(CDS_RootIterations(),"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="192">
+        <f>IFERROR(ABS(CDS_Objective(F13,Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142)),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="192">
+        <f>IF(ISNUMBER(F13),F13-Hazard_Solver!$B$175,"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="190" t="inlineStr">
+        <is>
+          <t>Bisection plus exponential interpolation. Keeps the bracket and converges fast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="190" t="inlineStr">
+        <is>
+          <t>BRENT</t>
+        </is>
+      </c>
+      <c r="B14" s="190" t="inlineStr">
+        <is>
+          <t>bracketing hybrid</t>
+        </is>
+      </c>
+      <c r="C14" s="190" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="D14" s="190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E14" s="190" t="inlineStr">
+        <is>
+          <t>yes, always</t>
+        </is>
+      </c>
+      <c r="F14" s="191">
+        <f>IFERROR(CDS_Root("BRENT",Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142),"module not loaded")</f>
+        <v/>
+      </c>
+      <c r="G14" s="180">
+        <f>IFERROR(CDS_RootIterations(),"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="192">
+        <f>IFERROR(ABS(CDS_Objective(F14,Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142)),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="192">
+        <f>IF(ISNUMBER(F14),F14-Hazard_Solver!$B$175,"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="190" t="inlineStr">
+        <is>
+          <t>IQI, falling back to secant, falling back to bisection. Bisection's guarantee at near-secant speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="67" t="inlineStr">
+        <is>
+          <t>Spread of the eight roots (max - min)</t>
+        </is>
+      </c>
+      <c r="F16" s="193">
+        <f>IF(COUNT(F7:F14)=0,"module not loaded",MAX(F7:F14)-MIN(F7:F14))</f>
+        <v/>
+      </c>
+      <c r="G16" s="177" t="inlineStr">
+        <is>
+          <t>they solve the same equation, so this is the real check</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="67" t="inlineStr">
+        <is>
+          <t>Measured on the 5Y objective (quarterly, R=40%, S=95bp), tolerance 1e-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="183" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B19" s="183" t="inlineStr">
+        <is>
+          <t>iters</t>
+        </is>
+      </c>
+      <c r="C19" s="183" t="inlineStr">
+        <is>
+          <t>|root - scipy.brentq|</t>
+        </is>
+      </c>
+      <c r="D19" s="183" t="inlineStr">
+        <is>
+          <t>|f(root)|</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="190" t="inlineStr">
+        <is>
+          <t>bisection</t>
+        </is>
+      </c>
+      <c r="B20" s="190" t="n">
+        <v>52</v>
+      </c>
+      <c r="C20" s="190" t="inlineStr">
+        <is>
+          <t>5.0e-16</t>
+        </is>
+      </c>
+      <c r="D20" s="190" t="inlineStr">
+        <is>
+          <t>1.3e-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="190" t="inlineStr">
+        <is>
+          <t>false position</t>
+        </is>
+      </c>
+      <c r="B21" s="190" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" s="190" t="inlineStr">
+        <is>
+          <t>2.4e-17</t>
+        </is>
+      </c>
+      <c r="D21" s="190" t="inlineStr">
+        <is>
+          <t>6.9e-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="190" t="inlineStr">
+        <is>
+          <t>secant</t>
+        </is>
+      </c>
+      <c r="B22" s="190" t="n">
+        <v>13</v>
+      </c>
+      <c r="C22" s="190" t="inlineStr">
+        <is>
+          <t>3.5e-18</t>
+        </is>
+      </c>
+      <c r="D22" s="190" t="inlineStr">
+        <is>
+          <t>1.4e-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="190" t="inlineStr">
+        <is>
+          <t>Newton (d=1)</t>
+        </is>
+      </c>
+      <c r="B23" s="190" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" s="190" t="inlineStr">
+        <is>
+          <t>6.9e-18</t>
+        </is>
+      </c>
+      <c r="D23" s="190" t="inlineStr">
+        <is>
+          <t>1.4e-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="190" t="inlineStr">
+        <is>
+          <t>Halley (d=2)</t>
+        </is>
+      </c>
+      <c r="B24" s="190" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" s="190" t="inlineStr">
+        <is>
+          <t>3.5e-18</t>
+        </is>
+      </c>
+      <c r="D24" s="190" t="inlineStr">
+        <is>
+          <t>1.4e-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="190" t="inlineStr">
+        <is>
+          <t>Householder d=3</t>
+        </is>
+      </c>
+      <c r="B25" s="190" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" s="190" t="inlineStr">
+        <is>
+          <t>3.5e-18</t>
+        </is>
+      </c>
+      <c r="D25" s="190" t="inlineStr">
+        <is>
+          <t>1.4e-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="190" t="inlineStr">
+        <is>
+          <t>Ridders</t>
+        </is>
+      </c>
+      <c r="B26" s="190" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="190" t="inlineStr">
+        <is>
+          <t>2.1e-17</t>
+        </is>
+      </c>
+      <c r="D26" s="190" t="inlineStr">
+        <is>
+          <t>3.5e-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="190" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="B27" s="190" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" s="190" t="inlineStr">
+        <is>
+          <t>1.4e-17</t>
+        </is>
+      </c>
+      <c r="D27" s="190" t="inlineStr">
+        <is>
+          <t>1.4e-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="67" t="inlineStr">
+        <is>
+          <t>Reading it honestly</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="126" t="inlineStr">
+        <is>
+          <t>All eight land on the same root to ~1e-16. On this problem the method is a cost question, not an accuracy one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="126" t="inlineStr">
+        <is>
+          <t>Bisection needs 52 steps where Newton needs 6 - the price of never using the shape of f.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="126" t="inlineStr">
+        <is>
+          <t>Halley and Householder d=3 do NOT beat Newton here. f is close to linear in h near the root, so the extra</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    order buys nothing before the tolerance is reached. Higher order is not free and not always faster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="126" t="inlineStr">
+        <is>
+          <t>Ridders is fastest at 5, but every open method (secant, Newton, Halley) can leave the domain on a bad start;</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    the bracketing ones cannot. On a strip that must never return h &lt; 0, that guarantee is worth more than speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="126" t="inlineStr">
+        <is>
+          <t>If no method converges, suspect the quote, not the solver - see the p.9 strippability note on Model_Notes.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00B7950B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -25218,7 +26387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E7D32"/>
@@ -27185,7 +28354,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006A1B9A"/>
@@ -28652,7 +29821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006A1B9A"/>
@@ -29070,7 +30239,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006A1B9A"/>
@@ -29481,397 +30650,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="006A1B9A"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Hazard_Bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="65" t="inlineStr">
-        <is>
-          <t>Piecewise-constant hazard. Col D solved live by Hazard_Solver, no Goal Seek. CDS_Parameters!B17 switches to a flat hazard.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="70" t="inlineStr">
-        <is>
-          <t>Maturity by maturity: hold earlier hazards fixed, solve the current segment so model spread = market. Col J (repricing error) stays ~0 as inputs move.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="140" t="inlineStr">
-        <is>
-          <t>Tenor</t>
-        </is>
-      </c>
-      <c r="B6" s="140" t="inlineStr">
-        <is>
-          <t>Maturity</t>
-        </is>
-      </c>
-      <c r="C6" s="140" t="inlineStr">
-        <is>
-          <t>Market spread (bp)</t>
-        </is>
-      </c>
-      <c r="D6" s="140" t="inlineStr">
-        <is>
-          <t>Hazard lambda (solve)</t>
-        </is>
-      </c>
-      <c r="E6" s="140" t="inlineStr">
-        <is>
-          <t>Cum. survival Q(T)</t>
-        </is>
-      </c>
-      <c r="F6" s="140" t="inlineStr">
-        <is>
-          <t>Cum. default 1-Q</t>
-        </is>
-      </c>
-      <c r="G6" s="140" t="inlineStr">
-        <is>
-          <t>RPV01 (risky annuity)</t>
-        </is>
-      </c>
-      <c r="H6" s="140" t="inlineStr">
-        <is>
-          <t>Protection PV factor</t>
-        </is>
-      </c>
-      <c r="I6" s="140" t="inlineStr">
-        <is>
-          <t>Model spread (bp)</t>
-        </is>
-      </c>
-      <c r="J6" s="140" t="inlineStr">
-        <is>
-          <t>Repricing error (bp)</t>
-        </is>
-      </c>
-      <c r="L6" s="140" t="inlineStr">
-        <is>
-          <t>Solver resid</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>1Y</t>
-        </is>
-      </c>
-      <c r="B7" s="18">
-        <f>CDS_Quotes!C7</f>
-        <v/>
-      </c>
-      <c r="C7" s="17">
-        <f>CDS_Quotes!F7</f>
-        <v/>
-      </c>
-      <c r="D7" s="71">
-        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,Hazard_Solver!$B$46)</f>
-        <v/>
-      </c>
-      <c r="E7" s="34">
-        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B7,CDS_Schedule!$C$7:$C$46,1))</f>
-        <v/>
-      </c>
-      <c r="F7" s="34">
-        <f>1-E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="34">
-        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B7,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B7,CDS_Schedule!$N$7:$N$46)</f>
-        <v/>
-      </c>
-      <c r="H7" s="36">
-        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B7,CDS_Schedule!$O$7:$O$46)</f>
-        <v/>
-      </c>
-      <c r="I7" s="131">
-        <f>(1-CDS_Parameters!$B$8)*H7/(G7-CDS_Parameters!$B$26)*10000</f>
-        <v/>
-      </c>
-      <c r="J7" s="53">
-        <f>I7-C7</f>
-        <v/>
-      </c>
-      <c r="L7" s="72">
-        <f>Hazard_Solver!$D$46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>2Y</t>
-        </is>
-      </c>
-      <c r="B8" s="18">
-        <f>CDS_Quotes!C8</f>
-        <v/>
-      </c>
-      <c r="C8" s="17">
-        <f>CDS_Quotes!F8</f>
-        <v/>
-      </c>
-      <c r="D8" s="71">
-        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,Hazard_Solver!$B$89)</f>
-        <v/>
-      </c>
-      <c r="E8" s="34">
-        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B8,CDS_Schedule!$C$7:$C$46,1))</f>
-        <v/>
-      </c>
-      <c r="F8" s="34">
-        <f>1-E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="34">
-        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$N$7:$N$46)</f>
-        <v/>
-      </c>
-      <c r="H8" s="36">
-        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)</f>
-        <v/>
-      </c>
-      <c r="I8" s="131">
-        <f>(1-CDS_Parameters!$B$8)*H8/(G8-CDS_Parameters!$B$26)*10000</f>
-        <v/>
-      </c>
-      <c r="J8" s="53">
-        <f>I8-C8</f>
-        <v/>
-      </c>
-      <c r="L8" s="72">
-        <f>Hazard_Solver!$D$89</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>3Y</t>
-        </is>
-      </c>
-      <c r="B9" s="18">
-        <f>CDS_Quotes!C9</f>
-        <v/>
-      </c>
-      <c r="C9" s="17">
-        <f>CDS_Quotes!F9</f>
-        <v/>
-      </c>
-      <c r="D9" s="71">
-        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,Hazard_Solver!$B$132)</f>
-        <v/>
-      </c>
-      <c r="E9" s="34">
-        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B9,CDS_Schedule!$C$7:$C$46,1))</f>
-        <v/>
-      </c>
-      <c r="F9" s="34">
-        <f>1-E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="34">
-        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B9,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B9,CDS_Schedule!$N$7:$N$46)</f>
-        <v/>
-      </c>
-      <c r="H9" s="36">
-        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B9,CDS_Schedule!$O$7:$O$46)</f>
-        <v/>
-      </c>
-      <c r="I9" s="131">
-        <f>(1-CDS_Parameters!$B$8)*H9/(G9-CDS_Parameters!$B$26)*10000</f>
-        <v/>
-      </c>
-      <c r="J9" s="53">
-        <f>I9-C9</f>
-        <v/>
-      </c>
-      <c r="L9" s="72">
-        <f>Hazard_Solver!$D$132</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="B10" s="18">
-        <f>CDS_Quotes!C10</f>
-        <v/>
-      </c>
-      <c r="C10" s="17">
-        <f>CDS_Quotes!F10</f>
-        <v/>
-      </c>
-      <c r="D10" s="71">
-        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,Hazard_Solver!$B$175)</f>
-        <v/>
-      </c>
-      <c r="E10" s="34">
-        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B10,CDS_Schedule!$C$7:$C$46,1))</f>
-        <v/>
-      </c>
-      <c r="F10" s="34">
-        <f>1-E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="34">
-        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B10,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B10,CDS_Schedule!$N$7:$N$46)</f>
-        <v/>
-      </c>
-      <c r="H10" s="36">
-        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B10,CDS_Schedule!$O$7:$O$46)</f>
-        <v/>
-      </c>
-      <c r="I10" s="131">
-        <f>(1-CDS_Parameters!$B$8)*H10/(G10-CDS_Parameters!$B$26)*10000</f>
-        <v/>
-      </c>
-      <c r="J10" s="53">
-        <f>I10-C10</f>
-        <v/>
-      </c>
-      <c r="L10" s="72">
-        <f>Hazard_Solver!$D$175</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>7Y</t>
-        </is>
-      </c>
-      <c r="B11" s="18">
-        <f>CDS_Quotes!C11</f>
-        <v/>
-      </c>
-      <c r="C11" s="17">
-        <f>CDS_Quotes!F11</f>
-        <v/>
-      </c>
-      <c r="D11" s="71">
-        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,Hazard_Solver!$B$218)</f>
-        <v/>
-      </c>
-      <c r="E11" s="34">
-        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B11,CDS_Schedule!$C$7:$C$46,1))</f>
-        <v/>
-      </c>
-      <c r="F11" s="34">
-        <f>1-E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="34">
-        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B11,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B11,CDS_Schedule!$N$7:$N$46)</f>
-        <v/>
-      </c>
-      <c r="H11" s="36">
-        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B11,CDS_Schedule!$O$7:$O$46)</f>
-        <v/>
-      </c>
-      <c r="I11" s="131">
-        <f>(1-CDS_Parameters!$B$8)*H11/(G11-CDS_Parameters!$B$26)*10000</f>
-        <v/>
-      </c>
-      <c r="J11" s="53">
-        <f>I11-C11</f>
-        <v/>
-      </c>
-      <c r="L11" s="72">
-        <f>Hazard_Solver!$D$218</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="B12" s="18">
-        <f>CDS_Quotes!C12</f>
-        <v/>
-      </c>
-      <c r="C12" s="17">
-        <f>CDS_Quotes!F12</f>
-        <v/>
-      </c>
-      <c r="D12" s="71">
-        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,Hazard_Solver!$B$261)</f>
-        <v/>
-      </c>
-      <c r="E12" s="34">
-        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B12,CDS_Schedule!$C$7:$C$46,1))</f>
-        <v/>
-      </c>
-      <c r="F12" s="34">
-        <f>1-E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="34">
-        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B12,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B12,CDS_Schedule!$N$7:$N$46)</f>
-        <v/>
-      </c>
-      <c r="H12" s="36">
-        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B12,CDS_Schedule!$O$7:$O$46)</f>
-        <v/>
-      </c>
-      <c r="I12" s="131">
-        <f>(1-CDS_Parameters!$B$8)*H12/(G12-CDS_Parameters!$B$26)*10000</f>
-        <v/>
-      </c>
-      <c r="J12" s="53">
-        <f>I12-C12</f>
-        <v/>
-      </c>
-      <c r="L12" s="72">
-        <f>Hazard_Solver!$D$261</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:J5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
 </file>
--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -1715,7 +1715,7 @@
     <row r="2">
       <c r="A2" s="177" t="inlineStr">
         <is>
-          <t>Set On to 0 to take a name out. Overrides win over the Bloomberg pull; leave blank to use the pull.</t>
+          <t>On = 0 takes a name out. Overrides beat the BDP pull; blank uses the pull.</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
     <row r="6">
       <c r="A6" s="73" t="inlineStr">
         <is>
-          <t>TENOR 1Y   —   periods 1-4   —   solve lambda1</t>
+          <t>TENOR 1Y: periods 1-4   -   solve lambda1</t>
         </is>
       </c>
       <c r="B6" s="74" t="n"/>
@@ -5309,7 +5309,7 @@
     <row r="49">
       <c r="A49" s="73" t="inlineStr">
         <is>
-          <t>TENOR 2Y   —   periods 5-8   —   solve lambda2</t>
+          <t>TENOR 2Y: periods 5-8   -   solve lambda2</t>
         </is>
       </c>
       <c r="B49" s="74" t="n"/>
@@ -8099,7 +8099,7 @@
     <row r="92">
       <c r="A92" s="73" t="inlineStr">
         <is>
-          <t>TENOR 3Y   —   periods 9-12   —   solve lambda3</t>
+          <t>TENOR 3Y: periods 9-12   -   solve lambda3</t>
         </is>
       </c>
       <c r="B92" s="74" t="n"/>
@@ -10889,7 +10889,7 @@
     <row r="135">
       <c r="A135" s="73" t="inlineStr">
         <is>
-          <t>TENOR 5Y   —   periods 13-20   —   solve lambda4</t>
+          <t>TENOR 5Y: periods 13-20   -   solve lambda4</t>
         </is>
       </c>
       <c r="B135" s="74" t="n"/>
@@ -13703,7 +13703,7 @@
     <row r="178">
       <c r="A178" s="73" t="inlineStr">
         <is>
-          <t>TENOR 7Y   —   periods 21-28   —   solve lambda5</t>
+          <t>TENOR 7Y: periods 21-28   -   solve lambda5</t>
         </is>
       </c>
       <c r="B178" s="74" t="n"/>
@@ -16517,7 +16517,7 @@
     <row r="221">
       <c r="A221" s="73" t="inlineStr">
         <is>
-          <t>TENOR 10Y   —   periods 29-40   —   solve lambda6</t>
+          <t>TENOR 10Y: periods 29-40   -   solve lambda6</t>
         </is>
       </c>
       <c r="B221" s="74" t="n"/>
@@ -19409,7 +19409,7 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Each row is one quarterly coupon period. DF(end)/DF(mid) interpolate the SOFR Curve_Interface; hazard is the piecewise-constant Hazard_Bootstrap lambda for the segment (by pay date); Q(end)=Q(prev)*exp(-hazard*dt). Premium factor = alpha*DF*Q ; Accrual factor = (alpha/2)*DF(mid)*deltaPD ; Protection factor = DF(mid)*deltaPD. Front period is a stub from valuation to the first roll.</t>
+          <t>One row per quarterly coupon period. DF(end) and DF(mid) interpolate the SOFR curve; hazard is the piecewise-constant lambda for the segment, by pay date. Q(end) = Q(prev)*exp(-hazard*dt). See Model_Notes.</t>
         </is>
       </c>
       <c r="Q4" s="139" t="inlineStr">
@@ -22055,7 +22055,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Price a CDS off the SOFR + hazard curves (protection − premium legs)</t>
+          <t>Prices a CDS off the SOFR discount curve and the stripped hazard curve. Equations on Model_Notes.</t>
         </is>
       </c>
     </row>
@@ -22253,7 +22253,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>PV — protection buyer</t>
+          <t>PV: protection buyer</t>
         </is>
       </c>
       <c r="B16" s="44">
@@ -23076,7 +23076,7 @@
     <row r="2">
       <c r="A2" s="177" t="inlineStr">
         <is>
-          <t>Discount curve is the pasted snapshot. Hazard and survival come out of the strip.</t>
+          <t>Discount curve is the pasted snapshot. Hazard and survival come from the strip.</t>
         </is>
       </c>
     </row>
@@ -24549,7 +24549,7 @@
     <row r="1">
       <c r="A1" s="176" t="inlineStr">
         <is>
-          <t>Model notes — Bloomberg B-Model (CDSW)</t>
+          <t>Model notes: Bloomberg B-Model (CDSW)</t>
         </is>
       </c>
     </row>
@@ -24714,7 +24714,7 @@
       </c>
       <c r="B18" s="126" t="inlineStr">
         <is>
-          <t>USD discounting is the SOFR RFR curve — ISDA moved to RFR curves and the B-Model follows.</t>
+          <t>USD discounting is the SOFR RFR curve: ISDA moved to RFR curves and the B-Model follows.</t>
         </is>
       </c>
     </row>
@@ -24863,7 +24863,7 @@
       </c>
       <c r="D37" s="187" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E37" s="187" t="inlineStr">
@@ -24985,35 +24985,35 @@
     <row r="44">
       <c r="A44" s="177" t="inlineStr">
         <is>
-          <t>A fail here is the p.9 condition, and it is a warning about the quotes, not about the solver.</t>
+          <t>A fail is the p.9 condition: a warning about the quotes, not the solver.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="177" t="inlineStr">
         <is>
-          <t>The bound is approximate; it holds while cumulative default probability is low.</t>
+          <t>Bound is approximate, valid while cumulative default probability is low.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="66" t="inlineStr">
         <is>
-          <t>Not covered by any of this</t>
+          <t>Limits</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="126" t="inlineStr">
         <is>
-          <t>The strip has no external validation — Bloomberg exports no hazard curve (Help Desk H#1330731572).</t>
+          <t>No external validation of the strip: Bloomberg exports no hazard curve (Help Desk H#1330731572).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="126" t="inlineStr">
         <is>
-          <t>Spreads in this workbook are demo values, not market. The SOFR curve is real; the credit curve is not.</t>
+          <t>Spreads here are demo values. The SOFR curve is real market data; the credit curve is not.</t>
         </is>
       </c>
     </row>
@@ -25053,14 +25053,14 @@
     <row r="2">
       <c r="A2" s="177" t="inlineStr">
         <is>
-          <t>Every method solves the same objective at the same step: f(h) = (1-R)*Prot(h) - S*(RPV01(h) - AI), B-Model (3.3). They must agree - what differs is cost and robustness.</t>
+          <t>All methods solve the same f(h) = (1-R)*Prot(h) - S*(RPV01(h) - AI), B-Model (3.3). Same root; different cost.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="98" t="inlineStr">
         <is>
-          <t>BASELINE is the scheme, not the algorithm. Section 4 p.8 fixes piecewise-constant hazard solved maturity by maturity, each one a 1-D root-find with earlier hazards held fixed; it does not name a method. Hazard_Solver in this workbook is bisection.</t>
+          <t>Baseline is the scheme, not the algorithm. Section 4 p.8 fixes piecewise-constant hazard solved maturity by maturity, each a 1-D root-find with earlier hazards fixed. It names no method. Hazard_Solver here is bisection.</t>
         </is>
       </c>
     </row>
@@ -25715,56 +25715,56 @@
     <row r="29">
       <c r="A29" s="67" t="inlineStr">
         <is>
-          <t>Reading it honestly</t>
+          <t>Results</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="126" t="inlineStr">
         <is>
-          <t>All eight land on the same root to ~1e-16. On this problem the method is a cost question, not an accuracy one.</t>
+          <t>All eight agree to ~1e-16. Method is a cost choice here, not an accuracy one.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="126" t="inlineStr">
         <is>
-          <t>Bisection needs 52 steps where Newton needs 6 - the price of never using the shape of f.</t>
+          <t>Bisection: 52 steps. Newton: 6. That is the cost of ignoring the shape of f.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="126" t="inlineStr">
         <is>
-          <t>Halley and Householder d=3 do NOT beat Newton here. f is close to linear in h near the root, so the extra</t>
+          <t>Halley and Householder d=3 do not beat Newton here: 6 iterations each. f is near-linear in h at the root,</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">    order buys nothing before the tolerance is reached. Higher order is not free and not always faster.</t>
+          <t xml:space="preserve">    so the extra order is spent before tolerance is reached.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="126" t="inlineStr">
         <is>
-          <t>Ridders is fastest at 5, but every open method (secant, Newton, Halley) can leave the domain on a bad start;</t>
+          <t>Ridders is fastest at 5. But secant, Newton and Halley can all leave the domain on a bad start;</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">    the bracketing ones cannot. On a strip that must never return h &lt; 0, that guarantee is worth more than speed.</t>
+          <t xml:space="preserve">    bracketing methods cannot. The strip must never return h &lt; 0 (p.8), so the guarantee outranks the speed.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="126" t="inlineStr">
         <is>
-          <t>If no method converges, suspect the quote, not the solver - see the p.9 strippability note on Model_Notes.</t>
+          <t>If nothing converges, suspect the quote. See the p.9 strippability check on Model_Notes.</t>
         </is>
       </c>
     </row>
@@ -25800,21 +25800,21 @@
     <row r="1">
       <c r="A1" s="123" t="inlineStr">
         <is>
-          <t>Brent (VBA) vs in-cell bisection — same objective, same inputs</t>
+          <t>Brent (VBA) vs in-cell bisection</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="65" t="inlineStr">
         <is>
-          <t>Both solve (3.3): f(h) = (1-R)*ProtCum - S*(RPV01Cum - D0*D(Ts)). Only the root-finder differs. Columns D:F need the VBA module.</t>
+          <t>Same objective (3.3), same inputs. Only the root-finder differs. Eight methods on Root_Methods.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="66" t="inlineStr">
         <is>
-          <t>Import: Alt+F11 &gt; File &gt; Import File &gt; bloomberg/vba/CDSBrent.bas, then save as .xlsm. Until then D:F read 'module not loaded' — the workbook is .xlsx and stays fully functional without it.</t>
+          <t>Import CDSBrent.bas (Alt+F11 &gt; File &gt; Import File), save as .xlsm. Until then col D reads 'module not loaded'.</t>
         </is>
       </c>
     </row>
@@ -26357,14 +26357,14 @@
     <row r="30">
       <c r="A30" s="65" t="inlineStr">
         <is>
-          <t>Brent is the better root-finder and it is not close — 8-13 iterations to machine precision against 30 to 1e-9. But the accuracy is not the binding constraint: our strip already reprices to ~1e-5 bp, which is set by the quarterly discretisation, not by the solver. Going to 1e-17 changes no price.</t>
+          <t>Brent wins on the numbers: 8-13 iterations to machine precision vs 30 fixed halvings, residual ~1e-17 vs ~1e-9.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="65" t="inlineStr">
         <is>
-          <t>What it would actually buy is ~3,600 cells back and a faster recalc. What it costs is the working — the reason the bisection is laid out as rows is that every halving is inspectable, which is what was asked for. A UDF is a black box.</t>
+          <t>It would return ~3,600 cells and a faster recalc. It costs the visible working and forces .xlsm.</t>
         </is>
       </c>
     </row>
@@ -26378,7 +26378,7 @@
     <row r="33">
       <c r="A33" s="66" t="inlineStr">
         <is>
-          <t>One genuine functional gain worth stealing: Brent returns #NUM! when the quote is unbracketed on [0,3], where the bisection pins at a bracket end and looks converged. That is deliverable D8 and can be added to the in-cell version without VBA.</t>
+          <t>Functional gain worth taking: Brent returns #NUM! on an unbracketed quote. Bisection returns a bracket end that looks like an answer. See Model_Notes, p.9.</t>
         </is>
       </c>
     </row>
@@ -28415,7 +28415,7 @@
     <row r="1">
       <c r="A1" s="123" t="inlineStr">
         <is>
-          <t>CDS_Entities — names pulled from Bloomberg</t>
+          <t>CDS_Entities: names pulled from Bloomberg</t>
         </is>
       </c>
     </row>
@@ -28439,7 +28439,7 @@
     <row r="3">
       <c r="A3" s="65" t="inlineStr">
         <is>
-          <t>Spreads H:M are T3 (term structure). O:AC are T4 (the CDSW screen for that name) and are the acceptance test — see TEST_CASES.md.</t>
+          <t>Spreads H:M are T3 (term structure). O:AC are T4 (the CDSW screen for that name) and are the acceptance test: see TEST_CASES.md.</t>
         </is>
       </c>
       <c r="H3" s="67" t="inlineStr">
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AE3" s="67" t="inlineStr">
         <is>
-          <t>DYNAMIC PULL — Help Desk H#1330731572</t>
+          <t>DYNAMIC PULL: Help Desk H#1330731572</t>
         </is>
       </c>
       <c r="AR3" s="67" t="inlineStr">
@@ -29805,7 +29805,7 @@
     <row r="16">
       <c r="A16" s="66" t="inlineStr">
         <is>
-          <t>Row 5 is the reference screen already on file. Only its 5Y spread is known — the rest of its term structure was never captured, which is exactly what T3 is for. Its CDSW outputs ARE known and are the target to hit.</t>
+          <t>Row 5 is the reference screen already on file. Only its 5Y spread is known: the rest of its term structure was never captured, which is exactly what T3 is for. Its CDSW outputs ARE known and are the target to hit.</t>
         </is>
       </c>
     </row>
@@ -30285,7 +30285,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Enter each tenor's Bloomberg CDS ticker in col D (e.g. the entity's par-spread series); Market spread = BDP(ticker,"PX_LAST") when it resolves, else the yellow Manual spread so the module still runs. Do NOT mix seniorities, currencies, or restructuring clauses.</t>
+          <t>Enter each tenor's CDS ticker, or let col D resolve it. Two-step pull per Help Desk H#1330731572, documented in K.</t>
         </is>
       </c>
       <c r="K4" s="137" t="inlineStr">

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -45,7 +45,7 @@
     <numFmt numFmtId="174" formatCode="0.###"/>
     <numFmt numFmtId="175" formatCode="$#,##0;($#,##0);-"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -210,6 +210,11 @@
       <b val="1"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -296,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -571,6 +576,20 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="30" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -26443,12 +26462,12 @@
     <row r="6">
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>Curve grid - snapshot from the SOFR bootstrap</t>
+          <t>Curve grid - LIVE LINK to the curve workbook</t>
         </is>
       </c>
       <c r="M6" s="177" t="inlineStr">
         <is>
-          <t>pasted 07/21/2026, not linked</t>
+          <t>source: [USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface!K8 (anchor) + K10:L74 (65 pillars)</t>
         </is>
       </c>
       <c r="N6" s="177" t="inlineStr">
@@ -26472,8 +26491,9 @@
           <t>Spot:</t>
         </is>
       </c>
-      <c r="D7" s="47" t="n">
-        <v>46226</v>
+      <c r="D7" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$D$7</f>
+        <v/>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -26516,12 +26536,18 @@
           <t>Step-function forward reproduces S490 (confirmed on screen: Step Forward (Cont)). Piecewise Linear (Simple) is 48x worse here. Only switch if the screen says so.</t>
         </is>
       </c>
-      <c r="K8" s="86">
-        <f>VAL_DATE</f>
-        <v/>
-      </c>
-      <c r="L8" s="76" t="n">
-        <v>1</v>
+      <c r="K8" s="195">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$8</f>
+        <v/>
+      </c>
+      <c r="L8" s="196">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$8</f>
+        <v/>
+      </c>
+      <c r="N8" s="67" t="inlineStr">
+        <is>
+          <t>LINK CHECK</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -26565,11 +26591,22 @@
           <t>Interp zero (%)</t>
         </is>
       </c>
-      <c r="K9" s="143" t="n">
-        <v>46233</v>
-      </c>
-      <c r="L9" s="144" t="n">
-        <v>0.999091426257</v>
+      <c r="K9" s="197">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$10</f>
+        <v/>
+      </c>
+      <c r="L9" s="198">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$10</f>
+        <v/>
+      </c>
+      <c r="N9" s="126" t="inlineStr">
+        <is>
+          <t>pillars linked</t>
+        </is>
+      </c>
+      <c r="O9" s="184">
+        <f>COUNT($L$8:$L$73)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -26609,11 +26646,22 @@
           <t>Method 1: DF=1/(1+r_s*t), r_s linear, ACT/360, flat outside the pillars.</t>
         </is>
       </c>
-      <c r="K10" s="18" t="n">
-        <v>46240</v>
-      </c>
-      <c r="L10" s="36" t="n">
-        <v>0.998370083188</v>
+      <c r="K10" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$11</f>
+        <v/>
+      </c>
+      <c r="L10" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$11</f>
+        <v/>
+      </c>
+      <c r="N10" s="126" t="inlineStr">
+        <is>
+          <t>first date</t>
+        </is>
+      </c>
+      <c r="O10" s="201">
+        <f>IF(COUNT($K$8:$K$73)=0,"",MIN($K$8:$K$73))</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -26653,11 +26701,22 @@
           <t>Method 3: flat forward between pillars = log-linear in DF.</t>
         </is>
       </c>
-      <c r="K11" s="18" t="n">
-        <v>46247</v>
-      </c>
-      <c r="L11" s="36" t="n">
-        <v>0.997649704403</v>
+      <c r="K11" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$12</f>
+        <v/>
+      </c>
+      <c r="L11" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$12</f>
+        <v/>
+      </c>
+      <c r="N11" s="126" t="inlineStr">
+        <is>
+          <t>last date</t>
+        </is>
+      </c>
+      <c r="O11" s="201">
+        <f>IF(COUNT($K$8:$K$73)=0,"",MAX($K$8:$K$73))</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -26697,11 +26756,22 @@
           <t>Identical at the pillars. They differ off-pillar, which is what CDS_Schedule looks up. ~0.07bp in a 2Y gap.</t>
         </is>
       </c>
-      <c r="K12" s="18" t="n">
-        <v>46258</v>
-      </c>
-      <c r="L12" s="36" t="n">
-        <v>0.996520959865</v>
+      <c r="K12" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$13</f>
+        <v/>
+      </c>
+      <c r="L12" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$13</f>
+        <v/>
+      </c>
+      <c r="N12" s="126" t="inlineStr">
+        <is>
+          <t>anchor DF (want 1)</t>
+        </is>
+      </c>
+      <c r="O12" s="202">
+        <f>IF($L$8="","",$L$8)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -26736,11 +26806,22 @@
         <f>-LN(G13)/C13*100</f>
         <v/>
       </c>
-      <c r="K13" s="18" t="n">
-        <v>46288</v>
-      </c>
-      <c r="L13" s="36" t="n">
-        <v>0.993425641561</v>
+      <c r="K13" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$14</f>
+        <v/>
+      </c>
+      <c r="L13" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$14</f>
+        <v/>
+      </c>
+      <c r="N13" s="126" t="inlineStr">
+        <is>
+          <t>first tenor date</t>
+        </is>
+      </c>
+      <c r="O13" s="201">
+        <f>IF($K$9="","",$K$9)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -26775,11 +26856,22 @@
         <f>-LN(G14)/C14*100</f>
         <v/>
       </c>
-      <c r="K14" s="18" t="n">
-        <v>46318</v>
-      </c>
-      <c r="L14" s="36" t="n">
-        <v>0.990238626466</v>
+      <c r="K14" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$15</f>
+        <v/>
+      </c>
+      <c r="L14" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$15</f>
+        <v/>
+      </c>
+      <c r="N14" s="126" t="inlineStr">
+        <is>
+          <t>DF monotone?</t>
+        </is>
+      </c>
+      <c r="O14" s="184">
+        <f>IF(COUNT($L$8:$L$73)&lt;2,"",IF(SUMPRODUCT(--($L$9:$L$73&gt;$L$8:$L$72))=0,"ok","NOT DECREASING"))</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -26814,11 +26906,17 @@
         <f>-LN(G15)/C15*100</f>
         <v/>
       </c>
-      <c r="K15" s="18" t="n">
-        <v>46349</v>
-      </c>
-      <c r="L15" s="36" t="n">
-        <v>0.986906864263</v>
+      <c r="K15" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$16</f>
+        <v/>
+      </c>
+      <c r="L15" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$16</f>
+        <v/>
+      </c>
+      <c r="N15" s="66">
+        <f>IF(O9=0,"LINK NOT RESOLVING - open USD_SOFR_Curve_Bloomberg_Pricer.xlsx",IF(ABS(O12-1)&gt;0.000001,"ROW 8 IS NOT THE ANCHOR - check the offset",IF(O13-VAL_DATE&gt;14,"FIRST TENOR LOOKS WRONG - expected about a week after the curve date",IF(O9&lt;60,"FEWER PILLARS THAN EXPECTED - check the source range","link ok"))))</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -26853,11 +26951,18 @@
         <f>-LN(G16)/C16*100</f>
         <v/>
       </c>
-      <c r="K16" s="18" t="n">
-        <v>46379</v>
-      </c>
-      <c r="L16" s="36" t="n">
-        <v>0.983643081173</v>
+      <c r="K16" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$17</f>
+        <v/>
+      </c>
+      <c r="L16" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$17</f>
+        <v/>
+      </c>
+      <c r="N16" s="177" t="inlineStr">
+        <is>
+          <t>Live only while the curve workbook is OPEN. Closed, Excel serves the last cached values and the BDP pulls in the source do not refresh.</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -26892,11 +26997,18 @@
         <f>-LN(G17)/C17*100</f>
         <v/>
       </c>
-      <c r="K17" s="18" t="n">
-        <v>46412</v>
-      </c>
-      <c r="L17" s="36" t="n">
-        <v>0.979999729956</v>
+      <c r="K17" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$18</f>
+        <v/>
+      </c>
+      <c r="L17" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$18</f>
+        <v/>
+      </c>
+      <c r="N17" s="177" t="inlineStr">
+        <is>
+          <t>Live only while the curve workbook is OPEN. Closed, Excel serves the last cached values and the BDP pulls in the source do not refresh.</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -26931,11 +27043,18 @@
         <f>-LN(G18)/C18*100</f>
         <v/>
       </c>
-      <c r="K18" s="18" t="n">
-        <v>46441</v>
-      </c>
-      <c r="L18" s="36" t="n">
-        <v>0.976792879929</v>
+      <c r="K18" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$19</f>
+        <v/>
+      </c>
+      <c r="L18" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$19</f>
+        <v/>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Data &gt; Edit Links &gt; Change Source if the file moves.</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -26970,11 +27089,13 @@
         <f>-LN(G19)/C19*100</f>
         <v/>
       </c>
-      <c r="K19" s="18" t="n">
-        <v>46469</v>
-      </c>
-      <c r="L19" s="36" t="n">
-        <v>0.973694329154</v>
+      <c r="K19" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$20</f>
+        <v/>
+      </c>
+      <c r="L19" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$20</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -27009,11 +27130,13 @@
         <f>-LN(G20)/C20*100</f>
         <v/>
       </c>
-      <c r="K20" s="18" t="n">
-        <v>46500</v>
-      </c>
-      <c r="L20" s="36" t="n">
-        <v>0.970240743572</v>
+      <c r="K20" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$21</f>
+        <v/>
+      </c>
+      <c r="L20" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$21</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -27048,11 +27171,13 @@
         <f>-LN(G21)/C21*100</f>
         <v/>
       </c>
-      <c r="K21" s="18" t="n">
-        <v>46531</v>
-      </c>
-      <c r="L21" s="36" t="n">
-        <v>0.966785661018</v>
+      <c r="K21" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$22</f>
+        <v/>
+      </c>
+      <c r="L21" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$22</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -27087,11 +27212,13 @@
         <f>-LN(G22)/C22*100</f>
         <v/>
       </c>
-      <c r="K22" s="18" t="n">
-        <v>46561</v>
-      </c>
-      <c r="L22" s="36" t="n">
-        <v>0.963452368418</v>
+      <c r="K22" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$23</f>
+        <v/>
+      </c>
+      <c r="L22" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$23</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -27126,11 +27253,13 @@
         <f>-LN(G23)/C23*100</f>
         <v/>
       </c>
-      <c r="K23" s="18" t="n">
-        <v>46591</v>
-      </c>
-      <c r="L23" s="36" t="n">
-        <v>0.960131959256</v>
+      <c r="K23" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$24</f>
+        <v/>
+      </c>
+      <c r="L23" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$24</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -27165,11 +27294,13 @@
         <f>-LN(G24)/C24*100</f>
         <v/>
       </c>
-      <c r="K24" s="18" t="n">
-        <v>46776</v>
-      </c>
-      <c r="L24" s="36" t="n">
-        <v>0.940192848138</v>
+      <c r="K24" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$25</f>
+        <v/>
+      </c>
+      <c r="L24" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$25</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -27204,11 +27335,13 @@
         <f>-LN(G25)/C25*100</f>
         <v/>
       </c>
-      <c r="K25" s="18" t="n">
-        <v>46958</v>
-      </c>
-      <c r="L25" s="36" t="n">
-        <v>0.921422244824</v>
+      <c r="K25" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$26</f>
+        <v/>
+      </c>
+      <c r="L25" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$26</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -27243,11 +27376,13 @@
         <f>-LN(G26)/C26*100</f>
         <v/>
       </c>
-      <c r="K26" s="18" t="n">
-        <v>47322</v>
-      </c>
-      <c r="L26" s="36" t="n">
-        <v>0.885314762367</v>
+      <c r="K26" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$27</f>
+        <v/>
+      </c>
+      <c r="L26" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$27</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -27282,11 +27417,13 @@
         <f>-LN(G27)/C27*100</f>
         <v/>
       </c>
-      <c r="K27" s="18" t="n">
-        <v>47687</v>
-      </c>
-      <c r="L27" s="36" t="n">
-        <v>0.850528545612</v>
+      <c r="K27" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$28</f>
+        <v/>
+      </c>
+      <c r="L27" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$28</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -27321,11 +27458,13 @@
         <f>-LN(G28)/C28*100</f>
         <v/>
       </c>
-      <c r="K28" s="18" t="n">
-        <v>48052</v>
-      </c>
-      <c r="L28" s="36" t="n">
-        <v>0.816635491704</v>
+      <c r="K28" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$29</f>
+        <v/>
+      </c>
+      <c r="L28" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$29</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -27360,11 +27499,13 @@
         <f>-LN(G29)/C29*100</f>
         <v/>
       </c>
-      <c r="K29" s="18" t="n">
-        <v>48418</v>
-      </c>
-      <c r="L29" s="36" t="n">
-        <v>0.783279937952</v>
+      <c r="K29" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$30</f>
+        <v/>
+      </c>
+      <c r="L29" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$30</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -27399,11 +27540,13 @@
         <f>-LN(G30)/C30*100</f>
         <v/>
       </c>
-      <c r="K30" s="18" t="n">
-        <v>48785</v>
-      </c>
-      <c r="L30" s="36" t="n">
-        <v>0.750566447936</v>
+      <c r="K30" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$31</f>
+        <v/>
+      </c>
+      <c r="L30" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$31</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -27438,11 +27581,13 @@
         <f>-LN(G31)/C31*100</f>
         <v/>
       </c>
-      <c r="K31" s="18" t="n">
-        <v>49149</v>
-      </c>
-      <c r="L31" s="36" t="n">
-        <v>0.718863905471</v>
+      <c r="K31" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$32</f>
+        <v/>
+      </c>
+      <c r="L31" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$32</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -27477,11 +27622,13 @@
         <f>-LN(G32)/C32*100</f>
         <v/>
       </c>
-      <c r="K32" s="18" t="n">
-        <v>49513</v>
-      </c>
-      <c r="L32" s="36" t="n">
-        <v>0.6878698307360001</v>
+      <c r="K32" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$33</f>
+        <v/>
+      </c>
+      <c r="L32" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$33</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -27516,11 +27663,13 @@
         <f>-LN(G33)/C33*100</f>
         <v/>
       </c>
-      <c r="K33" s="18" t="n">
-        <v>49879</v>
-      </c>
-      <c r="L33" s="36" t="n">
-        <v>0.657456920028</v>
+      <c r="K33" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$34</f>
+        <v/>
+      </c>
+      <c r="L33" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$34</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -27555,11 +27704,13 @@
         <f>-LN(G34)/C34*100</f>
         <v/>
       </c>
-      <c r="K34" s="18" t="n">
-        <v>50244</v>
-      </c>
-      <c r="L34" s="36" t="n">
-        <v>0.627649723811</v>
+      <c r="K34" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$35</f>
+        <v/>
+      </c>
+      <c r="L34" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$35</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -27594,11 +27745,13 @@
         <f>-LN(G35)/C35*100</f>
         <v/>
       </c>
-      <c r="K35" s="18" t="n">
-        <v>50609</v>
-      </c>
-      <c r="L35" s="36" t="n">
-        <v>0.599193899706</v>
+      <c r="K35" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$36</f>
+        <v/>
+      </c>
+      <c r="L35" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$36</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -27633,11 +27786,13 @@
         <f>-LN(G36)/C36*100</f>
         <v/>
       </c>
-      <c r="K36" s="18" t="n">
-        <v>50976</v>
-      </c>
-      <c r="L36" s="36" t="n">
-        <v>0.571081435815</v>
+      <c r="K36" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$37</f>
+        <v/>
+      </c>
+      <c r="L36" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$37</f>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -27672,11 +27827,13 @@
         <f>-LN(G37)/C37*100</f>
         <v/>
       </c>
-      <c r="K37" s="18" t="n">
-        <v>51340</v>
-      </c>
-      <c r="L37" s="36" t="n">
-        <v>0.544501770614</v>
+      <c r="K37" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$38</f>
+        <v/>
+      </c>
+      <c r="L37" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$38</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -27711,11 +27868,13 @@
         <f>-LN(G38)/C38*100</f>
         <v/>
       </c>
-      <c r="K38" s="18" t="n">
-        <v>51705</v>
-      </c>
-      <c r="L38" s="36" t="n">
-        <v>0.519091222417</v>
+      <c r="K38" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$39</f>
+        <v/>
+      </c>
+      <c r="L38" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$39</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -27750,11 +27909,13 @@
         <f>-LN(G39)/C39*100</f>
         <v/>
       </c>
-      <c r="K39" s="18" t="n">
-        <v>52070</v>
-      </c>
-      <c r="L39" s="36" t="n">
-        <v>0.495172865974</v>
+      <c r="K39" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$40</f>
+        <v/>
+      </c>
+      <c r="L39" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$40</f>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -27789,11 +27950,13 @@
         <f>-LN(G40)/C40*100</f>
         <v/>
       </c>
-      <c r="K40" s="18" t="n">
-        <v>52435</v>
-      </c>
-      <c r="L40" s="36" t="n">
-        <v>0.472356604404</v>
+      <c r="K40" s="199">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$41</f>
+        <v/>
+      </c>
+      <c r="L40" s="200">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$41</f>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -27828,11 +27991,13 @@
         <f>-LN(G41)/C41*100</f>
         <v/>
       </c>
-      <c r="K41" s="47" t="n">
-        <v>52803</v>
-      </c>
-      <c r="L41" s="27" t="n">
-        <v>0.450416986146</v>
+      <c r="K41" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$42</f>
+        <v/>
+      </c>
+      <c r="L41" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$42</f>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -27867,11 +28032,13 @@
         <f>-LN(G42)/C42*100</f>
         <v/>
       </c>
-      <c r="K42" s="47" t="n">
-        <v>53167</v>
-      </c>
-      <c r="L42" s="27" t="n">
-        <v>0.429718491004</v>
+      <c r="K42" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$43</f>
+        <v/>
+      </c>
+      <c r="L42" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$43</f>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -27906,11 +28073,13 @@
         <f>-LN(G43)/C43*100</f>
         <v/>
       </c>
-      <c r="K43" s="47" t="n">
-        <v>53531</v>
-      </c>
-      <c r="L43" s="27" t="n">
-        <v>0.409971176023</v>
+      <c r="K43" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$44</f>
+        <v/>
+      </c>
+      <c r="L43" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$44</f>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -27945,11 +28114,13 @@
         <f>-LN(G44)/C44*100</f>
         <v/>
       </c>
-      <c r="K44" s="47" t="n">
-        <v>53896</v>
-      </c>
-      <c r="L44" s="27" t="n">
-        <v>0.392507507974</v>
+      <c r="K44" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$45</f>
+        <v/>
+      </c>
+      <c r="L44" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$45</f>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -27984,11 +28155,13 @@
         <f>-LN(G45)/C45*100</f>
         <v/>
       </c>
-      <c r="K45" s="47" t="n">
-        <v>54262</v>
-      </c>
-      <c r="L45" s="27" t="n">
-        <v>0.375742930053</v>
+      <c r="K45" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$46</f>
+        <v/>
+      </c>
+      <c r="L45" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$46</f>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -28023,11 +28196,13 @@
         <f>-LN(G46)/C46*100</f>
         <v/>
       </c>
-      <c r="K46" s="47" t="n">
-        <v>54627</v>
-      </c>
-      <c r="L46" s="27" t="n">
-        <v>0.359737293106</v>
+      <c r="K46" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$47</f>
+        <v/>
+      </c>
+      <c r="L46" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$47</f>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -28062,11 +28237,13 @@
         <f>-LN(G47)/C47*100</f>
         <v/>
       </c>
-      <c r="K47" s="47" t="n">
-        <v>54994</v>
-      </c>
-      <c r="L47" s="27" t="n">
-        <v>0.344331311056</v>
+      <c r="K47" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$48</f>
+        <v/>
+      </c>
+      <c r="L47" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$48</f>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -28101,11 +28278,13 @@
         <f>-LN(G48)/C48*100</f>
         <v/>
       </c>
-      <c r="K48" s="47" t="n">
-        <v>55358</v>
-      </c>
-      <c r="L48" s="27" t="n">
-        <v>0.329703043692</v>
+      <c r="K48" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$49</f>
+        <v/>
+      </c>
+      <c r="L48" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$49</f>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -28140,203 +28319,253 @@
         <f>-LN(G49)/C49*100</f>
         <v/>
       </c>
-      <c r="K49" s="47" t="n">
-        <v>55723</v>
-      </c>
-      <c r="L49" s="27" t="n">
-        <v>0.316927094311</v>
+      <c r="K49" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$50</f>
+        <v/>
+      </c>
+      <c r="L49" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$50</f>
+        <v/>
       </c>
     </row>
     <row r="50">
-      <c r="K50" s="47" t="n">
-        <v>56088</v>
-      </c>
-      <c r="L50" s="27" t="n">
-        <v>0.304646211281</v>
+      <c r="K50" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$51</f>
+        <v/>
+      </c>
+      <c r="L50" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$51</f>
+        <v/>
       </c>
     </row>
     <row r="51">
-      <c r="K51" s="47" t="n">
-        <v>56453</v>
-      </c>
-      <c r="L51" s="27" t="n">
-        <v>0.292841210846</v>
+      <c r="K51" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$52</f>
+        <v/>
+      </c>
+      <c r="L51" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$52</f>
+        <v/>
       </c>
     </row>
     <row r="52">
-      <c r="K52" s="47" t="n">
-        <v>56818</v>
-      </c>
-      <c r="L52" s="27" t="n">
-        <v>0.281493652618</v>
+      <c r="K52" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$53</f>
+        <v/>
+      </c>
+      <c r="L52" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$53</f>
+        <v/>
       </c>
     </row>
     <row r="53">
-      <c r="K53" s="47" t="n">
-        <v>57185</v>
-      </c>
-      <c r="L53" s="27" t="n">
-        <v>0.270527221394</v>
+      <c r="K53" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$54</f>
+        <v/>
+      </c>
+      <c r="L53" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$54</f>
+        <v/>
       </c>
     </row>
     <row r="54">
-      <c r="K54" s="47" t="n">
-        <v>57549</v>
-      </c>
-      <c r="L54" s="27" t="n">
-        <v>0.261564982269</v>
+      <c r="K54" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$55</f>
+        <v/>
+      </c>
+      <c r="L54" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$55</f>
+        <v/>
       </c>
     </row>
     <row r="55">
-      <c r="K55" s="47" t="n">
-        <v>57914</v>
-      </c>
-      <c r="L55" s="27" t="n">
-        <v>0.252876245255</v>
+      <c r="K55" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$56</f>
+        <v/>
+      </c>
+      <c r="L55" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$56</f>
+        <v/>
       </c>
     </row>
     <row r="56">
-      <c r="K56" s="47" t="n">
-        <v>58279</v>
-      </c>
-      <c r="L56" s="27" t="n">
-        <v>0.24447613308</v>
+      <c r="K56" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$57</f>
+        <v/>
+      </c>
+      <c r="L56" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$57</f>
+        <v/>
       </c>
     </row>
     <row r="57">
-      <c r="K57" s="47" t="n">
-        <v>58645</v>
-      </c>
-      <c r="L57" s="27" t="n">
-        <v>0.236333183324</v>
+      <c r="K57" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$58</f>
+        <v/>
+      </c>
+      <c r="L57" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$58</f>
+        <v/>
       </c>
     </row>
     <row r="58">
-      <c r="K58" s="47" t="n">
-        <v>59012</v>
-      </c>
-      <c r="L58" s="27" t="n">
-        <v>0.228440312653</v>
+      <c r="K58" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$59</f>
+        <v/>
+      </c>
+      <c r="L58" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$59</f>
+        <v/>
       </c>
     </row>
     <row r="59">
-      <c r="K59" s="47" t="n">
-        <v>59376</v>
-      </c>
-      <c r="L59" s="27" t="n">
-        <v>0.220872361829</v>
+      <c r="K59" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$60</f>
+        <v/>
+      </c>
+      <c r="L59" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$60</f>
+        <v/>
       </c>
     </row>
     <row r="60">
-      <c r="K60" s="47" t="n">
-        <v>59740</v>
-      </c>
-      <c r="L60" s="27" t="n">
-        <v>0.213555128049</v>
+      <c r="K60" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$61</f>
+        <v/>
+      </c>
+      <c r="L60" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$61</f>
+        <v/>
       </c>
     </row>
     <row r="61">
-      <c r="K61" s="47" t="n">
-        <v>60106</v>
-      </c>
-      <c r="L61" s="27" t="n">
-        <v>0.206442087377</v>
+      <c r="K61" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$62</f>
+        <v/>
+      </c>
+      <c r="L61" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$62</f>
+        <v/>
       </c>
     </row>
     <row r="62">
-      <c r="K62" s="47" t="n">
-        <v>60471</v>
-      </c>
-      <c r="L62" s="27" t="n">
-        <v>0.199584437739</v>
+      <c r="K62" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$63</f>
+        <v/>
+      </c>
+      <c r="L62" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$63</f>
+        <v/>
       </c>
     </row>
     <row r="63">
-      <c r="K63" s="47" t="n">
-        <v>60836</v>
-      </c>
-      <c r="L63" s="27" t="n">
-        <v>0.19295458738</v>
+      <c r="K63" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$64</f>
+        <v/>
+      </c>
+      <c r="L63" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$64</f>
+        <v/>
       </c>
     </row>
     <row r="64">
-      <c r="K64" s="47" t="n">
-        <v>61203</v>
-      </c>
-      <c r="L64" s="27" t="n">
-        <v>0.18790374831</v>
+      <c r="K64" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$65</f>
+        <v/>
+      </c>
+      <c r="L64" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$65</f>
+        <v/>
       </c>
     </row>
     <row r="65">
-      <c r="K65" s="47" t="n">
-        <v>61567</v>
-      </c>
-      <c r="L65" s="27" t="n">
-        <v>0.183024801744</v>
+      <c r="K65" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$66</f>
+        <v/>
+      </c>
+      <c r="L65" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$66</f>
+        <v/>
       </c>
     </row>
     <row r="66">
-      <c r="K66" s="47" t="n">
-        <v>61932</v>
-      </c>
-      <c r="L66" s="27" t="n">
-        <v>0.178259653471</v>
+      <c r="K66" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$67</f>
+        <v/>
+      </c>
+      <c r="L66" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$67</f>
+        <v/>
       </c>
     </row>
     <row r="67">
-      <c r="K67" s="47" t="n">
-        <v>62297</v>
-      </c>
-      <c r="L67" s="27" t="n">
-        <v>0.173618568373</v>
+      <c r="K67" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$68</f>
+        <v/>
+      </c>
+      <c r="L67" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$68</f>
+        <v/>
       </c>
     </row>
     <row r="68">
-      <c r="K68" s="47" t="n">
-        <v>62662</v>
-      </c>
-      <c r="L68" s="27" t="n">
-        <v>0.169098316399</v>
+      <c r="K68" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$69</f>
+        <v/>
+      </c>
+      <c r="L68" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$69</f>
+        <v/>
       </c>
     </row>
     <row r="69">
-      <c r="K69" s="47" t="n">
-        <v>63030</v>
-      </c>
-      <c r="L69" s="27" t="n">
-        <v>0.164660045199</v>
+      <c r="K69" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$70</f>
+        <v/>
+      </c>
+      <c r="L69" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$70</f>
+        <v/>
       </c>
     </row>
     <row r="70">
-      <c r="K70" s="47" t="n">
-        <v>63394</v>
-      </c>
-      <c r="L70" s="27" t="n">
-        <v>0.160384624568</v>
+      <c r="K70" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$71</f>
+        <v/>
+      </c>
+      <c r="L70" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$71</f>
+        <v/>
       </c>
     </row>
     <row r="71">
-      <c r="K71" s="47" t="n">
-        <v>63758</v>
-      </c>
-      <c r="L71" s="27" t="n">
-        <v>0.156220215819</v>
+      <c r="K71" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$72</f>
+        <v/>
+      </c>
+      <c r="L71" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$72</f>
+        <v/>
       </c>
     </row>
     <row r="72">
-      <c r="K72" s="47" t="n">
-        <v>64123</v>
-      </c>
-      <c r="L72" s="27" t="n">
-        <v>0.152152939228</v>
+      <c r="K72" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$73</f>
+        <v/>
+      </c>
+      <c r="L72" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$73</f>
+        <v/>
       </c>
     </row>
     <row r="73">
-      <c r="K73" s="47" t="n">
-        <v>64489</v>
-      </c>
-      <c r="L73" s="27" t="n">
-        <v>0.148180846161</v>
+      <c r="K73" s="194">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$K$74</f>
+        <v/>
+      </c>
+      <c r="L73" s="203">
+        <f>'[USD_SOFR_Curve_Bloomberg_Pricer.xlsx]Curve_Interface'!$L$74</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -45,7 +45,7 @@
     <numFmt numFmtId="174" formatCode="0.###"/>
     <numFmt numFmtId="175" formatCode="$#,##0;($#,##0);-"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -215,6 +215,11 @@
       <color rgb="00FF0000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -301,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="204">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -590,6 +595,8 @@
     <xf numFmtId="164" fontId="17" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="17" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1148,6 +1155,280 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Default probability 1-Q(t)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Curves'!D74</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Curves'!$A$75:$A$80</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Curves'!$D$75:$D$80</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>probability</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>CDSW view - credit curve vs traded spread</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Curves'!B84</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Curves'!$A$85:$A$90</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Curves'!$B$85:$B$90</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Curves'!C84</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Curves'!$A$85:$A$90</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Curves'!$C$85:$C$90</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Curves'!E84</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Curves'!$A$85:$A$90</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Curves'!$E$85:$E$90</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>bp</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -1411,6 +1692,50 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>83</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="6" name="Chart 6"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1708,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1734,7 +2059,7 @@
     <row r="2">
       <c r="A2" s="177" t="inlineStr">
         <is>
-          <t>On = 0 takes a name out. Overrides beat the BDP pull; blank uses the pull.</t>
+          <t>Type a name and its Bloomberg ticker on any free row. On = 0 removes a name. Overrides beat the BDP pull; blank uses the pull.</t>
         </is>
       </c>
     </row>
@@ -1746,21 +2071,26 @@
       </c>
       <c r="B4" s="178" t="inlineStr">
         <is>
-          <t>China CITIC Bank Intl</t>
+          <t>DEMO curve (not market)</t>
         </is>
       </c>
       <c r="C4" s="177" t="inlineStr">
         <is>
-          <t>only this name is stripped</t>
-        </is>
+          <t>only this name is stripped and priced</t>
+        </is>
+      </c>
+      <c r="E4" s="67" t="inlineStr">
+        <is>
+          <t>ticker in use</t>
+        </is>
+      </c>
+      <c r="F4" s="204">
+        <f>IFERROR(IF(ISTEXT(INDEX($C$7:$C$16,MATCH($B$4,$B$7:$B$16,0))),INDEX($C$7:$C$16,MATCH($B$4,$B$7:$B$16,0)),""),"")</f>
+        <v/>
       </c>
     </row>
     <row r="5">
-      <c r="F5" s="177" t="inlineStr">
-        <is>
-          <t>override spreads (bp)</t>
-        </is>
-      </c>
+      <c r="F5" s="177" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="179" t="inlineStr">
@@ -1770,12 +2100,12 @@
       </c>
       <c r="B6" s="179" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>Entity name</t>
         </is>
       </c>
       <c r="C6" s="179" t="inlineStr">
         <is>
-          <t>Ticker</t>
+          <t>Bloomberg ticker</t>
         </is>
       </c>
       <c r="D6" s="179" t="inlineStr">
@@ -1823,17 +2153,16 @@
       <c r="A7" s="178" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="180">
-        <f>CDS_Entities!A5</f>
-        <v/>
-      </c>
-      <c r="C7" s="180">
-        <f>CDS_Entities!B5</f>
-        <v/>
-      </c>
-      <c r="D7" s="180">
-        <f>CDS_Entities!C5</f>
-        <v/>
+      <c r="B7" s="178" t="inlineStr">
+        <is>
+          <t>China CITIC Bank Intl</t>
+        </is>
+      </c>
+      <c r="C7" s="178" t="n"/>
+      <c r="D7" s="178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
       </c>
       <c r="E7" s="181" t="n"/>
       <c r="F7" s="182" t="n"/>
@@ -1847,17 +2176,16 @@
       <c r="A8" s="178" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="180">
-        <f>CDS_Entities!A6</f>
-        <v/>
-      </c>
-      <c r="C8" s="180">
-        <f>CDS_Entities!B6</f>
-        <v/>
-      </c>
-      <c r="D8" s="180">
-        <f>CDS_Entities!C6</f>
-        <v/>
+      <c r="B8" s="178" t="inlineStr">
+        <is>
+          <t>DEMO curve (not market)</t>
+        </is>
+      </c>
+      <c r="C8" s="178" t="n"/>
+      <c r="D8" s="178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
       </c>
       <c r="E8" s="181" t="n"/>
       <c r="F8" s="182" t="n"/>
@@ -1867,133 +2195,538 @@
       <c r="J8" s="182" t="n"/>
       <c r="K8" s="182" t="n"/>
     </row>
+    <row r="9">
+      <c r="A9" s="178" t="n"/>
+      <c r="B9" s="178" t="n"/>
+      <c r="C9" s="178" t="n"/>
+      <c r="D9" s="178" t="n"/>
+      <c r="E9" s="181" t="n"/>
+      <c r="F9" s="182" t="n"/>
+      <c r="G9" s="182" t="n"/>
+      <c r="H9" s="182" t="n"/>
+      <c r="I9" s="182" t="n"/>
+      <c r="J9" s="182" t="n"/>
+      <c r="K9" s="182" t="n"/>
+    </row>
     <row r="10">
-      <c r="A10" s="67" t="inlineStr">
+      <c r="A10" s="178" t="n"/>
+      <c r="B10" s="178" t="n"/>
+      <c r="C10" s="178" t="n"/>
+      <c r="D10" s="178" t="n"/>
+      <c r="E10" s="181" t="n"/>
+      <c r="F10" s="182" t="n"/>
+      <c r="G10" s="182" t="n"/>
+      <c r="H10" s="182" t="n"/>
+      <c r="I10" s="182" t="n"/>
+      <c r="J10" s="182" t="n"/>
+      <c r="K10" s="182" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="178" t="n"/>
+      <c r="B11" s="178" t="n"/>
+      <c r="C11" s="178" t="n"/>
+      <c r="D11" s="178" t="n"/>
+      <c r="E11" s="181" t="n"/>
+      <c r="F11" s="182" t="n"/>
+      <c r="G11" s="182" t="n"/>
+      <c r="H11" s="182" t="n"/>
+      <c r="I11" s="182" t="n"/>
+      <c r="J11" s="182" t="n"/>
+      <c r="K11" s="182" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="178" t="n"/>
+      <c r="B12" s="178" t="n"/>
+      <c r="C12" s="178" t="n"/>
+      <c r="D12" s="178" t="n"/>
+      <c r="E12" s="181" t="n"/>
+      <c r="F12" s="182" t="n"/>
+      <c r="G12" s="182" t="n"/>
+      <c r="H12" s="182" t="n"/>
+      <c r="I12" s="182" t="n"/>
+      <c r="J12" s="182" t="n"/>
+      <c r="K12" s="182" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="178" t="n"/>
+      <c r="B13" s="178" t="n"/>
+      <c r="C13" s="178" t="n"/>
+      <c r="D13" s="178" t="n"/>
+      <c r="E13" s="181" t="n"/>
+      <c r="F13" s="182" t="n"/>
+      <c r="G13" s="182" t="n"/>
+      <c r="H13" s="182" t="n"/>
+      <c r="I13" s="182" t="n"/>
+      <c r="J13" s="182" t="n"/>
+      <c r="K13" s="182" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="178" t="n"/>
+      <c r="B14" s="178" t="n"/>
+      <c r="C14" s="178" t="n"/>
+      <c r="D14" s="178" t="n"/>
+      <c r="E14" s="181" t="n"/>
+      <c r="F14" s="182" t="n"/>
+      <c r="G14" s="182" t="n"/>
+      <c r="H14" s="182" t="n"/>
+      <c r="I14" s="182" t="n"/>
+      <c r="J14" s="182" t="n"/>
+      <c r="K14" s="182" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="178" t="n"/>
+      <c r="B15" s="178" t="n"/>
+      <c r="C15" s="178" t="n"/>
+      <c r="D15" s="178" t="n"/>
+      <c r="E15" s="181" t="n"/>
+      <c r="F15" s="182" t="n"/>
+      <c r="G15" s="182" t="n"/>
+      <c r="H15" s="182" t="n"/>
+      <c r="I15" s="182" t="n"/>
+      <c r="J15" s="182" t="n"/>
+      <c r="K15" s="182" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="178" t="n"/>
+      <c r="B16" s="178" t="n"/>
+      <c r="C16" s="178" t="n"/>
+      <c r="D16" s="178" t="n"/>
+      <c r="E16" s="181" t="n"/>
+      <c r="F16" s="182" t="n"/>
+      <c r="G16" s="182" t="n"/>
+      <c r="H16" s="182" t="n"/>
+      <c r="I16" s="182" t="n"/>
+      <c r="J16" s="182" t="n"/>
+      <c r="K16" s="182" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="67" t="inlineStr">
         <is>
           <t>Effective (what the strip uses)</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="183" t="inlineStr">
+      <c r="F19" s="177" t="inlineStr">
+        <is>
+          <t>override &gt; BDP pull &gt; manual &gt; 0. This block is what the strip uses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="183" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="E11" s="183" t="inlineStr">
+      <c r="E20" s="183" t="inlineStr">
         <is>
           <t>Recovery</t>
         </is>
       </c>
-      <c r="F11" s="183" t="inlineStr">
+      <c r="F20" s="183" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="G11" s="183" t="inlineStr">
+      <c r="G20" s="183" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
       </c>
-      <c r="H11" s="183" t="inlineStr">
+      <c r="H20" s="183" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
-      <c r="I11" s="183" t="inlineStr">
+      <c r="I20" s="183" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
-      <c r="J11" s="183" t="inlineStr">
+      <c r="J20" s="183" t="inlineStr">
         <is>
           <t>7Y</t>
         </is>
       </c>
-      <c r="K11" s="183" t="inlineStr">
+      <c r="K20" s="183" t="inlineStr">
         <is>
           <t>10Y</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="184" t="n"/>
-      <c r="B12" s="184">
-        <f>B7</f>
-        <v/>
-      </c>
-      <c r="C12" s="184" t="n"/>
-      <c r="D12" s="184" t="n"/>
-      <c r="E12" s="184">
-        <f>IF($A7=0,"off",IF(ISNUMBER(E7),E7,CDS_Entities!F5))</f>
-        <v/>
-      </c>
-      <c r="F12" s="185">
-        <f>IF($A7=0,0,IF(ISNUMBER(F7),F7,IF(ISNUMBER(CDS_Entities!H5),CDS_Entities!H5,0)))</f>
-        <v/>
-      </c>
-      <c r="G12" s="185">
-        <f>IF($A7=0,0,IF(ISNUMBER(G7),G7,IF(ISNUMBER(CDS_Entities!I5),CDS_Entities!I5,0)))</f>
-        <v/>
-      </c>
-      <c r="H12" s="185">
-        <f>IF($A7=0,0,IF(ISNUMBER(H7),H7,IF(ISNUMBER(CDS_Entities!J5),CDS_Entities!J5,0)))</f>
-        <v/>
-      </c>
-      <c r="I12" s="185">
-        <f>IF($A7=0,0,IF(ISNUMBER(I7),I7,IF(ISNUMBER(CDS_Entities!K5),CDS_Entities!K5,0)))</f>
-        <v/>
-      </c>
-      <c r="J12" s="185">
-        <f>IF($A7=0,0,IF(ISNUMBER(J7),J7,IF(ISNUMBER(CDS_Entities!L5),CDS_Entities!L5,0)))</f>
-        <v/>
-      </c>
-      <c r="K12" s="185">
-        <f>IF($A7=0,0,IF(ISNUMBER(K7),K7,IF(ISNUMBER(CDS_Entities!M5),CDS_Entities!M5,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="184" t="n"/>
-      <c r="B13" s="184">
-        <f>B8</f>
-        <v/>
-      </c>
-      <c r="C13" s="184" t="n"/>
-      <c r="D13" s="184" t="n"/>
-      <c r="E13" s="184">
-        <f>IF($A8=0,"off",IF(ISNUMBER(E8),E8,CDS_Entities!F6))</f>
-        <v/>
-      </c>
-      <c r="F13" s="185">
-        <f>IF($A8=0,0,IF(ISNUMBER(F8),F8,IF(ISNUMBER(CDS_Entities!H6),CDS_Entities!H6,0)))</f>
-        <v/>
-      </c>
-      <c r="G13" s="185">
-        <f>IF($A8=0,0,IF(ISNUMBER(G8),G8,IF(ISNUMBER(CDS_Entities!I6),CDS_Entities!I6,0)))</f>
-        <v/>
-      </c>
-      <c r="H13" s="185">
-        <f>IF($A8=0,0,IF(ISNUMBER(H8),H8,IF(ISNUMBER(CDS_Entities!J6),CDS_Entities!J6,0)))</f>
-        <v/>
-      </c>
-      <c r="I13" s="185">
-        <f>IF($A8=0,0,IF(ISNUMBER(I8),I8,IF(ISNUMBER(CDS_Entities!K6),CDS_Entities!K6,0)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="185">
-        <f>IF($A8=0,0,IF(ISNUMBER(J8),J8,IF(ISNUMBER(CDS_Entities!L6),CDS_Entities!L6,0)))</f>
-        <v/>
-      </c>
-      <c r="K13" s="185">
-        <f>IF($A8=0,0,IF(ISNUMBER(K8),K8,IF(ISNUMBER(CDS_Entities!M6),CDS_Entities!M6,0)))</f>
+    <row r="21">
+      <c r="A21" s="204" t="n"/>
+      <c r="B21" s="204">
+        <f>IF($B7="","",$B7)</f>
+        <v/>
+      </c>
+      <c r="C21" s="204" t="n"/>
+      <c r="D21" s="204" t="n"/>
+      <c r="E21" s="204">
+        <f>IF($B7="","",IF($A7=0,"off",IF(ISNUMBER($E7),$E7,CDS_Entities!$F$5)))</f>
+        <v/>
+      </c>
+      <c r="F21" s="205">
+        <f>IF($B7="","",IF($A7=0,0,IF(ISNUMBER($F7),$F7,IF(ISNUMBER(CDS_Entities!$AG$5),CDS_Entities!$AG$5,IF(ISNUMBER(CDS_Entities!$H$5),CDS_Entities!$H$5,0)))))</f>
+        <v/>
+      </c>
+      <c r="G21" s="205">
+        <f>IF($B7="","",IF($A7=0,0,IF(ISNUMBER($G7),$G7,IF(ISNUMBER(CDS_Entities!$AI$5),CDS_Entities!$AI$5,IF(ISNUMBER(CDS_Entities!$I$5),CDS_Entities!$I$5,0)))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="205">
+        <f>IF($B7="","",IF($A7=0,0,IF(ISNUMBER($H7),$H7,IF(ISNUMBER(CDS_Entities!$AK$5),CDS_Entities!$AK$5,IF(ISNUMBER(CDS_Entities!$J$5),CDS_Entities!$J$5,0)))))</f>
+        <v/>
+      </c>
+      <c r="I21" s="205">
+        <f>IF($B7="","",IF($A7=0,0,IF(ISNUMBER($I7),$I7,IF(ISNUMBER(CDS_Entities!$AM$5),CDS_Entities!$AM$5,IF(ISNUMBER(CDS_Entities!$K$5),CDS_Entities!$K$5,0)))))</f>
+        <v/>
+      </c>
+      <c r="J21" s="205">
+        <f>IF($B7="","",IF($A7=0,0,IF(ISNUMBER($J7),$J7,IF(ISNUMBER(CDS_Entities!$AO$5),CDS_Entities!$AO$5,IF(ISNUMBER(CDS_Entities!$L$5),CDS_Entities!$L$5,0)))))</f>
+        <v/>
+      </c>
+      <c r="K21" s="205">
+        <f>IF($B7="","",IF($A7=0,0,IF(ISNUMBER($K7),$K7,IF(ISNUMBER(CDS_Entities!$AQ$5),CDS_Entities!$AQ$5,IF(ISNUMBER(CDS_Entities!$M$5),CDS_Entities!$M$5,0)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="204" t="n"/>
+      <c r="B22" s="204">
+        <f>IF($B8="","",$B8)</f>
+        <v/>
+      </c>
+      <c r="C22" s="204" t="n"/>
+      <c r="D22" s="204" t="n"/>
+      <c r="E22" s="204">
+        <f>IF($B8="","",IF($A8=0,"off",IF(ISNUMBER($E8),$E8,CDS_Entities!$F$6)))</f>
+        <v/>
+      </c>
+      <c r="F22" s="205">
+        <f>IF($B8="","",IF($A8=0,0,IF(ISNUMBER($F8),$F8,IF(ISNUMBER(CDS_Entities!$AG$6),CDS_Entities!$AG$6,IF(ISNUMBER(CDS_Entities!$H$6),CDS_Entities!$H$6,0)))))</f>
+        <v/>
+      </c>
+      <c r="G22" s="205">
+        <f>IF($B8="","",IF($A8=0,0,IF(ISNUMBER($G8),$G8,IF(ISNUMBER(CDS_Entities!$AI$6),CDS_Entities!$AI$6,IF(ISNUMBER(CDS_Entities!$I$6),CDS_Entities!$I$6,0)))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="205">
+        <f>IF($B8="","",IF($A8=0,0,IF(ISNUMBER($H8),$H8,IF(ISNUMBER(CDS_Entities!$AK$6),CDS_Entities!$AK$6,IF(ISNUMBER(CDS_Entities!$J$6),CDS_Entities!$J$6,0)))))</f>
+        <v/>
+      </c>
+      <c r="I22" s="205">
+        <f>IF($B8="","",IF($A8=0,0,IF(ISNUMBER($I8),$I8,IF(ISNUMBER(CDS_Entities!$AM$6),CDS_Entities!$AM$6,IF(ISNUMBER(CDS_Entities!$K$6),CDS_Entities!$K$6,0)))))</f>
+        <v/>
+      </c>
+      <c r="J22" s="205">
+        <f>IF($B8="","",IF($A8=0,0,IF(ISNUMBER($J8),$J8,IF(ISNUMBER(CDS_Entities!$AO$6),CDS_Entities!$AO$6,IF(ISNUMBER(CDS_Entities!$L$6),CDS_Entities!$L$6,0)))))</f>
+        <v/>
+      </c>
+      <c r="K22" s="205">
+        <f>IF($B8="","",IF($A8=0,0,IF(ISNUMBER($K8),$K8,IF(ISNUMBER(CDS_Entities!$AQ$6),CDS_Entities!$AQ$6,IF(ISNUMBER(CDS_Entities!$M$6),CDS_Entities!$M$6,0)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="204" t="n"/>
+      <c r="B23" s="204">
+        <f>IF($B9="","",$B9)</f>
+        <v/>
+      </c>
+      <c r="C23" s="204" t="n"/>
+      <c r="D23" s="204" t="n"/>
+      <c r="E23" s="204">
+        <f>IF($B9="","",IF($A9=0,"off",IF(ISNUMBER($E9),$E9,CDS_Entities!$F$7)))</f>
+        <v/>
+      </c>
+      <c r="F23" s="205">
+        <f>IF($B9="","",IF($A9=0,0,IF(ISNUMBER($F9),$F9,IF(ISNUMBER(CDS_Entities!$AG$7),CDS_Entities!$AG$7,IF(ISNUMBER(CDS_Entities!$H$7),CDS_Entities!$H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="G23" s="205">
+        <f>IF($B9="","",IF($A9=0,0,IF(ISNUMBER($G9),$G9,IF(ISNUMBER(CDS_Entities!$AI$7),CDS_Entities!$AI$7,IF(ISNUMBER(CDS_Entities!$I$7),CDS_Entities!$I$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="205">
+        <f>IF($B9="","",IF($A9=0,0,IF(ISNUMBER($H9),$H9,IF(ISNUMBER(CDS_Entities!$AK$7),CDS_Entities!$AK$7,IF(ISNUMBER(CDS_Entities!$J$7),CDS_Entities!$J$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I23" s="205">
+        <f>IF($B9="","",IF($A9=0,0,IF(ISNUMBER($I9),$I9,IF(ISNUMBER(CDS_Entities!$AM$7),CDS_Entities!$AM$7,IF(ISNUMBER(CDS_Entities!$K$7),CDS_Entities!$K$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="J23" s="205">
+        <f>IF($B9="","",IF($A9=0,0,IF(ISNUMBER($J9),$J9,IF(ISNUMBER(CDS_Entities!$AO$7),CDS_Entities!$AO$7,IF(ISNUMBER(CDS_Entities!$L$7),CDS_Entities!$L$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="K23" s="205">
+        <f>IF($B9="","",IF($A9=0,0,IF(ISNUMBER($K9),$K9,IF(ISNUMBER(CDS_Entities!$AQ$7),CDS_Entities!$AQ$7,IF(ISNUMBER(CDS_Entities!$M$7),CDS_Entities!$M$7,0)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="204" t="n"/>
+      <c r="B24" s="204">
+        <f>IF($B10="","",$B10)</f>
+        <v/>
+      </c>
+      <c r="C24" s="204" t="n"/>
+      <c r="D24" s="204" t="n"/>
+      <c r="E24" s="204">
+        <f>IF($B10="","",IF($A10=0,"off",IF(ISNUMBER($E10),$E10,CDS_Entities!$F$8)))</f>
+        <v/>
+      </c>
+      <c r="F24" s="205">
+        <f>IF($B10="","",IF($A10=0,0,IF(ISNUMBER($F10),$F10,IF(ISNUMBER(CDS_Entities!$AG$8),CDS_Entities!$AG$8,IF(ISNUMBER(CDS_Entities!$H$8),CDS_Entities!$H$8,0)))))</f>
+        <v/>
+      </c>
+      <c r="G24" s="205">
+        <f>IF($B10="","",IF($A10=0,0,IF(ISNUMBER($G10),$G10,IF(ISNUMBER(CDS_Entities!$AI$8),CDS_Entities!$AI$8,IF(ISNUMBER(CDS_Entities!$I$8),CDS_Entities!$I$8,0)))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="205">
+        <f>IF($B10="","",IF($A10=0,0,IF(ISNUMBER($H10),$H10,IF(ISNUMBER(CDS_Entities!$AK$8),CDS_Entities!$AK$8,IF(ISNUMBER(CDS_Entities!$J$8),CDS_Entities!$J$8,0)))))</f>
+        <v/>
+      </c>
+      <c r="I24" s="205">
+        <f>IF($B10="","",IF($A10=0,0,IF(ISNUMBER($I10),$I10,IF(ISNUMBER(CDS_Entities!$AM$8),CDS_Entities!$AM$8,IF(ISNUMBER(CDS_Entities!$K$8),CDS_Entities!$K$8,0)))))</f>
+        <v/>
+      </c>
+      <c r="J24" s="205">
+        <f>IF($B10="","",IF($A10=0,0,IF(ISNUMBER($J10),$J10,IF(ISNUMBER(CDS_Entities!$AO$8),CDS_Entities!$AO$8,IF(ISNUMBER(CDS_Entities!$L$8),CDS_Entities!$L$8,0)))))</f>
+        <v/>
+      </c>
+      <c r="K24" s="205">
+        <f>IF($B10="","",IF($A10=0,0,IF(ISNUMBER($K10),$K10,IF(ISNUMBER(CDS_Entities!$AQ$8),CDS_Entities!$AQ$8,IF(ISNUMBER(CDS_Entities!$M$8),CDS_Entities!$M$8,0)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="204" t="n"/>
+      <c r="B25" s="204">
+        <f>IF($B11="","",$B11)</f>
+        <v/>
+      </c>
+      <c r="C25" s="204" t="n"/>
+      <c r="D25" s="204" t="n"/>
+      <c r="E25" s="204">
+        <f>IF($B11="","",IF($A11=0,"off",IF(ISNUMBER($E11),$E11,CDS_Entities!$F$9)))</f>
+        <v/>
+      </c>
+      <c r="F25" s="205">
+        <f>IF($B11="","",IF($A11=0,0,IF(ISNUMBER($F11),$F11,IF(ISNUMBER(CDS_Entities!$AG$9),CDS_Entities!$AG$9,IF(ISNUMBER(CDS_Entities!$H$9),CDS_Entities!$H$9,0)))))</f>
+        <v/>
+      </c>
+      <c r="G25" s="205">
+        <f>IF($B11="","",IF($A11=0,0,IF(ISNUMBER($G11),$G11,IF(ISNUMBER(CDS_Entities!$AI$9),CDS_Entities!$AI$9,IF(ISNUMBER(CDS_Entities!$I$9),CDS_Entities!$I$9,0)))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="205">
+        <f>IF($B11="","",IF($A11=0,0,IF(ISNUMBER($H11),$H11,IF(ISNUMBER(CDS_Entities!$AK$9),CDS_Entities!$AK$9,IF(ISNUMBER(CDS_Entities!$J$9),CDS_Entities!$J$9,0)))))</f>
+        <v/>
+      </c>
+      <c r="I25" s="205">
+        <f>IF($B11="","",IF($A11=0,0,IF(ISNUMBER($I11),$I11,IF(ISNUMBER(CDS_Entities!$AM$9),CDS_Entities!$AM$9,IF(ISNUMBER(CDS_Entities!$K$9),CDS_Entities!$K$9,0)))))</f>
+        <v/>
+      </c>
+      <c r="J25" s="205">
+        <f>IF($B11="","",IF($A11=0,0,IF(ISNUMBER($J11),$J11,IF(ISNUMBER(CDS_Entities!$AO$9),CDS_Entities!$AO$9,IF(ISNUMBER(CDS_Entities!$L$9),CDS_Entities!$L$9,0)))))</f>
+        <v/>
+      </c>
+      <c r="K25" s="205">
+        <f>IF($B11="","",IF($A11=0,0,IF(ISNUMBER($K11),$K11,IF(ISNUMBER(CDS_Entities!$AQ$9),CDS_Entities!$AQ$9,IF(ISNUMBER(CDS_Entities!$M$9),CDS_Entities!$M$9,0)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="204" t="n"/>
+      <c r="B26" s="204">
+        <f>IF($B12="","",$B12)</f>
+        <v/>
+      </c>
+      <c r="C26" s="204" t="n"/>
+      <c r="D26" s="204" t="n"/>
+      <c r="E26" s="204">
+        <f>IF($B12="","",IF($A12=0,"off",IF(ISNUMBER($E12),$E12,CDS_Entities!$F$10)))</f>
+        <v/>
+      </c>
+      <c r="F26" s="205">
+        <f>IF($B12="","",IF($A12=0,0,IF(ISNUMBER($F12),$F12,IF(ISNUMBER(CDS_Entities!$AG$10),CDS_Entities!$AG$10,IF(ISNUMBER(CDS_Entities!$H$10),CDS_Entities!$H$10,0)))))</f>
+        <v/>
+      </c>
+      <c r="G26" s="205">
+        <f>IF($B12="","",IF($A12=0,0,IF(ISNUMBER($G12),$G12,IF(ISNUMBER(CDS_Entities!$AI$10),CDS_Entities!$AI$10,IF(ISNUMBER(CDS_Entities!$I$10),CDS_Entities!$I$10,0)))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="205">
+        <f>IF($B12="","",IF($A12=0,0,IF(ISNUMBER($H12),$H12,IF(ISNUMBER(CDS_Entities!$AK$10),CDS_Entities!$AK$10,IF(ISNUMBER(CDS_Entities!$J$10),CDS_Entities!$J$10,0)))))</f>
+        <v/>
+      </c>
+      <c r="I26" s="205">
+        <f>IF($B12="","",IF($A12=0,0,IF(ISNUMBER($I12),$I12,IF(ISNUMBER(CDS_Entities!$AM$10),CDS_Entities!$AM$10,IF(ISNUMBER(CDS_Entities!$K$10),CDS_Entities!$K$10,0)))))</f>
+        <v/>
+      </c>
+      <c r="J26" s="205">
+        <f>IF($B12="","",IF($A12=0,0,IF(ISNUMBER($J12),$J12,IF(ISNUMBER(CDS_Entities!$AO$10),CDS_Entities!$AO$10,IF(ISNUMBER(CDS_Entities!$L$10),CDS_Entities!$L$10,0)))))</f>
+        <v/>
+      </c>
+      <c r="K26" s="205">
+        <f>IF($B12="","",IF($A12=0,0,IF(ISNUMBER($K12),$K12,IF(ISNUMBER(CDS_Entities!$AQ$10),CDS_Entities!$AQ$10,IF(ISNUMBER(CDS_Entities!$M$10),CDS_Entities!$M$10,0)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="204" t="n"/>
+      <c r="B27" s="204">
+        <f>IF($B13="","",$B13)</f>
+        <v/>
+      </c>
+      <c r="C27" s="204" t="n"/>
+      <c r="D27" s="204" t="n"/>
+      <c r="E27" s="204">
+        <f>IF($B13="","",IF($A13=0,"off",IF(ISNUMBER($E13),$E13,CDS_Entities!$F$11)))</f>
+        <v/>
+      </c>
+      <c r="F27" s="205">
+        <f>IF($B13="","",IF($A13=0,0,IF(ISNUMBER($F13),$F13,IF(ISNUMBER(CDS_Entities!$AG$11),CDS_Entities!$AG$11,IF(ISNUMBER(CDS_Entities!$H$11),CDS_Entities!$H$11,0)))))</f>
+        <v/>
+      </c>
+      <c r="G27" s="205">
+        <f>IF($B13="","",IF($A13=0,0,IF(ISNUMBER($G13),$G13,IF(ISNUMBER(CDS_Entities!$AI$11),CDS_Entities!$AI$11,IF(ISNUMBER(CDS_Entities!$I$11),CDS_Entities!$I$11,0)))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="205">
+        <f>IF($B13="","",IF($A13=0,0,IF(ISNUMBER($H13),$H13,IF(ISNUMBER(CDS_Entities!$AK$11),CDS_Entities!$AK$11,IF(ISNUMBER(CDS_Entities!$J$11),CDS_Entities!$J$11,0)))))</f>
+        <v/>
+      </c>
+      <c r="I27" s="205">
+        <f>IF($B13="","",IF($A13=0,0,IF(ISNUMBER($I13),$I13,IF(ISNUMBER(CDS_Entities!$AM$11),CDS_Entities!$AM$11,IF(ISNUMBER(CDS_Entities!$K$11),CDS_Entities!$K$11,0)))))</f>
+        <v/>
+      </c>
+      <c r="J27" s="205">
+        <f>IF($B13="","",IF($A13=0,0,IF(ISNUMBER($J13),$J13,IF(ISNUMBER(CDS_Entities!$AO$11),CDS_Entities!$AO$11,IF(ISNUMBER(CDS_Entities!$L$11),CDS_Entities!$L$11,0)))))</f>
+        <v/>
+      </c>
+      <c r="K27" s="205">
+        <f>IF($B13="","",IF($A13=0,0,IF(ISNUMBER($K13),$K13,IF(ISNUMBER(CDS_Entities!$AQ$11),CDS_Entities!$AQ$11,IF(ISNUMBER(CDS_Entities!$M$11),CDS_Entities!$M$11,0)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="204" t="n"/>
+      <c r="B28" s="204">
+        <f>IF($B14="","",$B14)</f>
+        <v/>
+      </c>
+      <c r="C28" s="204" t="n"/>
+      <c r="D28" s="204" t="n"/>
+      <c r="E28" s="204">
+        <f>IF($B14="","",IF($A14=0,"off",IF(ISNUMBER($E14),$E14,CDS_Entities!$F$12)))</f>
+        <v/>
+      </c>
+      <c r="F28" s="205">
+        <f>IF($B14="","",IF($A14=0,0,IF(ISNUMBER($F14),$F14,IF(ISNUMBER(CDS_Entities!$AG$12),CDS_Entities!$AG$12,IF(ISNUMBER(CDS_Entities!$H$12),CDS_Entities!$H$12,0)))))</f>
+        <v/>
+      </c>
+      <c r="G28" s="205">
+        <f>IF($B14="","",IF($A14=0,0,IF(ISNUMBER($G14),$G14,IF(ISNUMBER(CDS_Entities!$AI$12),CDS_Entities!$AI$12,IF(ISNUMBER(CDS_Entities!$I$12),CDS_Entities!$I$12,0)))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="205">
+        <f>IF($B14="","",IF($A14=0,0,IF(ISNUMBER($H14),$H14,IF(ISNUMBER(CDS_Entities!$AK$12),CDS_Entities!$AK$12,IF(ISNUMBER(CDS_Entities!$J$12),CDS_Entities!$J$12,0)))))</f>
+        <v/>
+      </c>
+      <c r="I28" s="205">
+        <f>IF($B14="","",IF($A14=0,0,IF(ISNUMBER($I14),$I14,IF(ISNUMBER(CDS_Entities!$AM$12),CDS_Entities!$AM$12,IF(ISNUMBER(CDS_Entities!$K$12),CDS_Entities!$K$12,0)))))</f>
+        <v/>
+      </c>
+      <c r="J28" s="205">
+        <f>IF($B14="","",IF($A14=0,0,IF(ISNUMBER($J14),$J14,IF(ISNUMBER(CDS_Entities!$AO$12),CDS_Entities!$AO$12,IF(ISNUMBER(CDS_Entities!$L$12),CDS_Entities!$L$12,0)))))</f>
+        <v/>
+      </c>
+      <c r="K28" s="205">
+        <f>IF($B14="","",IF($A14=0,0,IF(ISNUMBER($K14),$K14,IF(ISNUMBER(CDS_Entities!$AQ$12),CDS_Entities!$AQ$12,IF(ISNUMBER(CDS_Entities!$M$12),CDS_Entities!$M$12,0)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="204" t="n"/>
+      <c r="B29" s="204">
+        <f>IF($B15="","",$B15)</f>
+        <v/>
+      </c>
+      <c r="C29" s="204" t="n"/>
+      <c r="D29" s="204" t="n"/>
+      <c r="E29" s="204">
+        <f>IF($B15="","",IF($A15=0,"off",IF(ISNUMBER($E15),$E15,CDS_Entities!$F$13)))</f>
+        <v/>
+      </c>
+      <c r="F29" s="205">
+        <f>IF($B15="","",IF($A15=0,0,IF(ISNUMBER($F15),$F15,IF(ISNUMBER(CDS_Entities!$AG$13),CDS_Entities!$AG$13,IF(ISNUMBER(CDS_Entities!$H$13),CDS_Entities!$H$13,0)))))</f>
+        <v/>
+      </c>
+      <c r="G29" s="205">
+        <f>IF($B15="","",IF($A15=0,0,IF(ISNUMBER($G15),$G15,IF(ISNUMBER(CDS_Entities!$AI$13),CDS_Entities!$AI$13,IF(ISNUMBER(CDS_Entities!$I$13),CDS_Entities!$I$13,0)))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="205">
+        <f>IF($B15="","",IF($A15=0,0,IF(ISNUMBER($H15),$H15,IF(ISNUMBER(CDS_Entities!$AK$13),CDS_Entities!$AK$13,IF(ISNUMBER(CDS_Entities!$J$13),CDS_Entities!$J$13,0)))))</f>
+        <v/>
+      </c>
+      <c r="I29" s="205">
+        <f>IF($B15="","",IF($A15=0,0,IF(ISNUMBER($I15),$I15,IF(ISNUMBER(CDS_Entities!$AM$13),CDS_Entities!$AM$13,IF(ISNUMBER(CDS_Entities!$K$13),CDS_Entities!$K$13,0)))))</f>
+        <v/>
+      </c>
+      <c r="J29" s="205">
+        <f>IF($B15="","",IF($A15=0,0,IF(ISNUMBER($J15),$J15,IF(ISNUMBER(CDS_Entities!$AO$13),CDS_Entities!$AO$13,IF(ISNUMBER(CDS_Entities!$L$13),CDS_Entities!$L$13,0)))))</f>
+        <v/>
+      </c>
+      <c r="K29" s="205">
+        <f>IF($B15="","",IF($A15=0,0,IF(ISNUMBER($K15),$K15,IF(ISNUMBER(CDS_Entities!$AQ$13),CDS_Entities!$AQ$13,IF(ISNUMBER(CDS_Entities!$M$13),CDS_Entities!$M$13,0)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="204" t="n"/>
+      <c r="B30" s="204">
+        <f>IF($B16="","",$B16)</f>
+        <v/>
+      </c>
+      <c r="C30" s="204" t="n"/>
+      <c r="D30" s="204" t="n"/>
+      <c r="E30" s="204">
+        <f>IF($B16="","",IF($A16=0,"off",IF(ISNUMBER($E16),$E16,CDS_Entities!$F$14)))</f>
+        <v/>
+      </c>
+      <c r="F30" s="205">
+        <f>IF($B16="","",IF($A16=0,0,IF(ISNUMBER($F16),$F16,IF(ISNUMBER(CDS_Entities!$AG$14),CDS_Entities!$AG$14,IF(ISNUMBER(CDS_Entities!$H$14),CDS_Entities!$H$14,0)))))</f>
+        <v/>
+      </c>
+      <c r="G30" s="205">
+        <f>IF($B16="","",IF($A16=0,0,IF(ISNUMBER($G16),$G16,IF(ISNUMBER(CDS_Entities!$AI$14),CDS_Entities!$AI$14,IF(ISNUMBER(CDS_Entities!$I$14),CDS_Entities!$I$14,0)))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="205">
+        <f>IF($B16="","",IF($A16=0,0,IF(ISNUMBER($H16),$H16,IF(ISNUMBER(CDS_Entities!$AK$14),CDS_Entities!$AK$14,IF(ISNUMBER(CDS_Entities!$J$14),CDS_Entities!$J$14,0)))))</f>
+        <v/>
+      </c>
+      <c r="I30" s="205">
+        <f>IF($B16="","",IF($A16=0,0,IF(ISNUMBER($I16),$I16,IF(ISNUMBER(CDS_Entities!$AM$14),CDS_Entities!$AM$14,IF(ISNUMBER(CDS_Entities!$K$14),CDS_Entities!$K$14,0)))))</f>
+        <v/>
+      </c>
+      <c r="J30" s="205">
+        <f>IF($B16="","",IF($A16=0,0,IF(ISNUMBER($J16),$J16,IF(ISNUMBER(CDS_Entities!$AO$14),CDS_Entities!$AO$14,IF(ISNUMBER(CDS_Entities!$L$14),CDS_Entities!$L$14,0)))))</f>
+        <v/>
+      </c>
+      <c r="K30" s="205">
+        <f>IF($B16="","",IF($A16=0,0,IF(ISNUMBER($K16),$K16,IF(ISNUMBER(CDS_Entities!$AQ$14),CDS_Entities!$AQ$14,IF(ISNUMBER(CDS_Entities!$M$14),CDS_Entities!$M$14,0)))))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"China CITIC Bank Intl,DEMO curve (not market)"</formula1>
+      <formula1>=$B$7:$B$16</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23076,7 +23809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24321,6 +25054,11 @@
           <t>Survival Q</t>
         </is>
       </c>
+      <c r="D74" s="183" t="inlineStr">
+        <is>
+          <t>Default prob 1-Q</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -24335,6 +25073,10 @@
         <f>Hazard_Bootstrap!E7</f>
         <v/>
       </c>
+      <c r="D75" s="33">
+        <f>Hazard_Bootstrap!F7</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -24349,6 +25091,10 @@
         <f>Hazard_Bootstrap!E8</f>
         <v/>
       </c>
+      <c r="D76" s="33">
+        <f>Hazard_Bootstrap!F8</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -24363,6 +25109,10 @@
         <f>Hazard_Bootstrap!E9</f>
         <v/>
       </c>
+      <c r="D77" s="33">
+        <f>Hazard_Bootstrap!F9</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -24377,6 +25127,10 @@
         <f>Hazard_Bootstrap!E10</f>
         <v/>
       </c>
+      <c r="D78" s="33">
+        <f>Hazard_Bootstrap!F10</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -24391,6 +25145,10 @@
         <f>Hazard_Bootstrap!E11</f>
         <v/>
       </c>
+      <c r="D79" s="33">
+        <f>Hazard_Bootstrap!F11</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -24405,6 +25163,10 @@
         <f>Hazard_Bootstrap!E12</f>
         <v/>
       </c>
+      <c r="D80" s="33">
+        <f>Hazard_Bootstrap!F12</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="67" t="inlineStr">
@@ -24432,6 +25194,11 @@
       <c r="D84" s="183" t="inlineStr">
         <is>
           <t>Diff bp</t>
+        </is>
+      </c>
+      <c r="E84" s="183" t="inlineStr">
+        <is>
+          <t>Traded spread</t>
         </is>
       </c>
     </row>
@@ -24452,6 +25219,10 @@
         <f>Hazard_Bootstrap!J7</f>
         <v/>
       </c>
+      <c r="E85" s="50">
+        <f>CDS_Pricer!$B$15</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -24470,6 +25241,10 @@
         <f>Hazard_Bootstrap!J8</f>
         <v/>
       </c>
+      <c r="E86" s="50">
+        <f>CDS_Pricer!$B$15</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -24488,6 +25263,10 @@
         <f>Hazard_Bootstrap!J9</f>
         <v/>
       </c>
+      <c r="E87" s="50">
+        <f>CDS_Pricer!$B$15</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -24506,6 +25285,10 @@
         <f>Hazard_Bootstrap!J10</f>
         <v/>
       </c>
+      <c r="E88" s="50">
+        <f>CDS_Pricer!$B$15</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -24524,6 +25307,10 @@
         <f>Hazard_Bootstrap!J11</f>
         <v/>
       </c>
+      <c r="E89" s="50">
+        <f>CDS_Pricer!$B$15</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -24540,6 +25327,10 @@
       </c>
       <c r="D90" s="33">
         <f>Hazard_Bootstrap!J12</f>
+        <v/>
+      </c>
+      <c r="E90" s="50">
+        <f>CDS_Pricer!$B$15</f>
         <v/>
       </c>
     </row>
@@ -28686,9 +29477,9 @@
           <t>DYNAMIC PULL: Help Desk H#1330731572</t>
         </is>
       </c>
-      <c r="AR3" s="67" t="inlineStr">
-        <is>
-          <t>IN USE  =  live if it resolved, else manual, else 0</t>
+      <c r="AR3" s="177" t="inlineStr">
+        <is>
+          <t>in use = Entities effective block (override &gt; BDP &gt; manual)</t>
         </is>
       </c>
     </row>
@@ -28930,16 +29721,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="68" t="inlineStr">
-        <is>
-          <t>China CITIC Bank Intl</t>
-        </is>
-      </c>
-      <c r="B5" s="68" t="inlineStr"/>
-      <c r="C5" s="68" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
+      <c r="A5" s="68">
+        <f>IF(Entities!$B7="","",Entities!$B7)</f>
+        <v/>
+      </c>
+      <c r="B5" s="68">
+        <f>IF(Entities!$C7="","",Entities!$C7)</f>
+        <v/>
+      </c>
+      <c r="C5" s="68">
+        <f>IF(Entities!$D7="","",Entities!$D7)</f>
+        <v/>
       </c>
       <c r="D5" s="68" t="inlineStr">
         <is>
@@ -29059,41 +29851,42 @@
         <v/>
       </c>
       <c r="AR5" s="133">
-        <f>IF(ISNUMBER(AG5),AG5,IF(ISNUMBER(H5),H5,0))</f>
+        <f>IF(Entities!$F21="",0,Entities!$F21)</f>
         <v/>
       </c>
       <c r="AS5" s="133">
-        <f>IF(ISNUMBER(AI5),AI5,IF(ISNUMBER(I5),I5,0))</f>
+        <f>IF(Entities!$G21="",0,Entities!$G21)</f>
         <v/>
       </c>
       <c r="AT5" s="133">
-        <f>IF(ISNUMBER(AK5),AK5,IF(ISNUMBER(J5),J5,0))</f>
+        <f>IF(Entities!$H21="",0,Entities!$H21)</f>
         <v/>
       </c>
       <c r="AU5" s="133">
-        <f>IF(ISNUMBER(AM5),AM5,IF(ISNUMBER(K5),K5,0))</f>
+        <f>IF(Entities!$I21="",0,Entities!$I21)</f>
         <v/>
       </c>
       <c r="AV5" s="133">
-        <f>IF(ISNUMBER(AO5),AO5,IF(ISNUMBER(L5),L5,0))</f>
+        <f>IF(Entities!$J21="",0,Entities!$J21)</f>
         <v/>
       </c>
       <c r="AW5" s="133">
-        <f>IF(ISNUMBER(AQ5),AQ5,IF(ISNUMBER(M5),M5,0))</f>
+        <f>IF(Entities!$K21="",0,Entities!$K21)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="68" t="inlineStr">
-        <is>
-          <t>DEMO curve (not market)</t>
-        </is>
-      </c>
-      <c r="B6" s="68" t="n"/>
-      <c r="C6" s="68" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
+      <c r="A6" s="68">
+        <f>IF(Entities!$B8="","",Entities!$B8)</f>
+        <v/>
+      </c>
+      <c r="B6" s="68">
+        <f>IF(Entities!$C8="","",Entities!$C8)</f>
+        <v/>
+      </c>
+      <c r="C6" s="68">
+        <f>IF(Entities!$D8="","",Entities!$D8)</f>
+        <v/>
       </c>
       <c r="D6" s="68" t="inlineStr">
         <is>
@@ -29191,37 +29984,48 @@
         <v/>
       </c>
       <c r="AR6" s="133">
-        <f>IF(ISNUMBER(AG6),AG6,IF(ISNUMBER(H6),H6,0))</f>
+        <f>IF(Entities!$F22="",0,Entities!$F22)</f>
         <v/>
       </c>
       <c r="AS6" s="133">
-        <f>IF(ISNUMBER(AI6),AI6,IF(ISNUMBER(I6),I6,0))</f>
+        <f>IF(Entities!$G22="",0,Entities!$G22)</f>
         <v/>
       </c>
       <c r="AT6" s="133">
-        <f>IF(ISNUMBER(AK6),AK6,IF(ISNUMBER(J6),J6,0))</f>
+        <f>IF(Entities!$H22="",0,Entities!$H22)</f>
         <v/>
       </c>
       <c r="AU6" s="133">
-        <f>IF(ISNUMBER(AM6),AM6,IF(ISNUMBER(K6),K6,0))</f>
+        <f>IF(Entities!$I22="",0,Entities!$I22)</f>
         <v/>
       </c>
       <c r="AV6" s="133">
-        <f>IF(ISNUMBER(AO6),AO6,IF(ISNUMBER(L6),L6,0))</f>
+        <f>IF(Entities!$J22="",0,Entities!$J22)</f>
         <v/>
       </c>
       <c r="AW6" s="133">
-        <f>IF(ISNUMBER(AQ6),AQ6,IF(ISNUMBER(M6),M6,0))</f>
+        <f>IF(Entities!$K22="",0,Entities!$K22)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="68" t="n"/>
-      <c r="B7" s="68" t="n"/>
-      <c r="C7" s="68" t="n"/>
+      <c r="A7" s="68">
+        <f>IF(Entities!$B9="","",Entities!$B9)</f>
+        <v/>
+      </c>
+      <c r="B7" s="68">
+        <f>IF(Entities!$C9="","",Entities!$C9)</f>
+        <v/>
+      </c>
+      <c r="C7" s="68">
+        <f>IF(Entities!$D9="","",Entities!$D9)</f>
+        <v/>
+      </c>
       <c r="D7" s="68" t="n"/>
       <c r="E7" s="68" t="n"/>
-      <c r="F7" s="147" t="n"/>
+      <c r="F7" s="147" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G7" s="111" t="n"/>
       <c r="H7" s="64" t="n"/>
       <c r="I7" s="64" t="n"/>
@@ -29293,37 +30097,48 @@
         <v/>
       </c>
       <c r="AR7" s="133">
-        <f>IF(ISNUMBER(AG7),AG7,IF(ISNUMBER(H7),H7,0))</f>
+        <f>IF(Entities!$F23="",0,Entities!$F23)</f>
         <v/>
       </c>
       <c r="AS7" s="133">
-        <f>IF(ISNUMBER(AI7),AI7,IF(ISNUMBER(I7),I7,0))</f>
+        <f>IF(Entities!$G23="",0,Entities!$G23)</f>
         <v/>
       </c>
       <c r="AT7" s="133">
-        <f>IF(ISNUMBER(AK7),AK7,IF(ISNUMBER(J7),J7,0))</f>
+        <f>IF(Entities!$H23="",0,Entities!$H23)</f>
         <v/>
       </c>
       <c r="AU7" s="133">
-        <f>IF(ISNUMBER(AM7),AM7,IF(ISNUMBER(K7),K7,0))</f>
+        <f>IF(Entities!$I23="",0,Entities!$I23)</f>
         <v/>
       </c>
       <c r="AV7" s="133">
-        <f>IF(ISNUMBER(AO7),AO7,IF(ISNUMBER(L7),L7,0))</f>
+        <f>IF(Entities!$J23="",0,Entities!$J23)</f>
         <v/>
       </c>
       <c r="AW7" s="133">
-        <f>IF(ISNUMBER(AQ7),AQ7,IF(ISNUMBER(M7),M7,0))</f>
+        <f>IF(Entities!$K23="",0,Entities!$K23)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="68" t="n"/>
-      <c r="B8" s="68" t="n"/>
-      <c r="C8" s="68" t="n"/>
+      <c r="A8" s="68">
+        <f>IF(Entities!$B10="","",Entities!$B10)</f>
+        <v/>
+      </c>
+      <c r="B8" s="68">
+        <f>IF(Entities!$C10="","",Entities!$C10)</f>
+        <v/>
+      </c>
+      <c r="C8" s="68">
+        <f>IF(Entities!$D10="","",Entities!$D10)</f>
+        <v/>
+      </c>
       <c r="D8" s="68" t="n"/>
       <c r="E8" s="68" t="n"/>
-      <c r="F8" s="147" t="n"/>
+      <c r="F8" s="147" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G8" s="111" t="n"/>
       <c r="H8" s="64" t="n"/>
       <c r="I8" s="64" t="n"/>
@@ -29395,37 +30210,48 @@
         <v/>
       </c>
       <c r="AR8" s="133">
-        <f>IF(ISNUMBER(AG8),AG8,IF(ISNUMBER(H8),H8,0))</f>
+        <f>IF(Entities!$F24="",0,Entities!$F24)</f>
         <v/>
       </c>
       <c r="AS8" s="133">
-        <f>IF(ISNUMBER(AI8),AI8,IF(ISNUMBER(I8),I8,0))</f>
+        <f>IF(Entities!$G24="",0,Entities!$G24)</f>
         <v/>
       </c>
       <c r="AT8" s="133">
-        <f>IF(ISNUMBER(AK8),AK8,IF(ISNUMBER(J8),J8,0))</f>
+        <f>IF(Entities!$H24="",0,Entities!$H24)</f>
         <v/>
       </c>
       <c r="AU8" s="133">
-        <f>IF(ISNUMBER(AM8),AM8,IF(ISNUMBER(K8),K8,0))</f>
+        <f>IF(Entities!$I24="",0,Entities!$I24)</f>
         <v/>
       </c>
       <c r="AV8" s="133">
-        <f>IF(ISNUMBER(AO8),AO8,IF(ISNUMBER(L8),L8,0))</f>
+        <f>IF(Entities!$J24="",0,Entities!$J24)</f>
         <v/>
       </c>
       <c r="AW8" s="133">
-        <f>IF(ISNUMBER(AQ8),AQ8,IF(ISNUMBER(M8),M8,0))</f>
+        <f>IF(Entities!$K24="",0,Entities!$K24)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="68" t="n"/>
-      <c r="B9" s="68" t="n"/>
-      <c r="C9" s="68" t="n"/>
+      <c r="A9" s="68">
+        <f>IF(Entities!$B11="","",Entities!$B11)</f>
+        <v/>
+      </c>
+      <c r="B9" s="68">
+        <f>IF(Entities!$C11="","",Entities!$C11)</f>
+        <v/>
+      </c>
+      <c r="C9" s="68">
+        <f>IF(Entities!$D11="","",Entities!$D11)</f>
+        <v/>
+      </c>
       <c r="D9" s="68" t="n"/>
       <c r="E9" s="68" t="n"/>
-      <c r="F9" s="147" t="n"/>
+      <c r="F9" s="147" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G9" s="111" t="n"/>
       <c r="H9" s="64" t="n"/>
       <c r="I9" s="64" t="n"/>
@@ -29497,37 +30323,48 @@
         <v/>
       </c>
       <c r="AR9" s="133">
-        <f>IF(ISNUMBER(AG9),AG9,IF(ISNUMBER(H9),H9,0))</f>
+        <f>IF(Entities!$F25="",0,Entities!$F25)</f>
         <v/>
       </c>
       <c r="AS9" s="133">
-        <f>IF(ISNUMBER(AI9),AI9,IF(ISNUMBER(I9),I9,0))</f>
+        <f>IF(Entities!$G25="",0,Entities!$G25)</f>
         <v/>
       </c>
       <c r="AT9" s="133">
-        <f>IF(ISNUMBER(AK9),AK9,IF(ISNUMBER(J9),J9,0))</f>
+        <f>IF(Entities!$H25="",0,Entities!$H25)</f>
         <v/>
       </c>
       <c r="AU9" s="133">
-        <f>IF(ISNUMBER(AM9),AM9,IF(ISNUMBER(K9),K9,0))</f>
+        <f>IF(Entities!$I25="",0,Entities!$I25)</f>
         <v/>
       </c>
       <c r="AV9" s="133">
-        <f>IF(ISNUMBER(AO9),AO9,IF(ISNUMBER(L9),L9,0))</f>
+        <f>IF(Entities!$J25="",0,Entities!$J25)</f>
         <v/>
       </c>
       <c r="AW9" s="133">
-        <f>IF(ISNUMBER(AQ9),AQ9,IF(ISNUMBER(M9),M9,0))</f>
+        <f>IF(Entities!$K25="",0,Entities!$K25)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="68" t="n"/>
-      <c r="B10" s="68" t="n"/>
-      <c r="C10" s="68" t="n"/>
+      <c r="A10" s="68">
+        <f>IF(Entities!$B12="","",Entities!$B12)</f>
+        <v/>
+      </c>
+      <c r="B10" s="68">
+        <f>IF(Entities!$C12="","",Entities!$C12)</f>
+        <v/>
+      </c>
+      <c r="C10" s="68">
+        <f>IF(Entities!$D12="","",Entities!$D12)</f>
+        <v/>
+      </c>
       <c r="D10" s="68" t="n"/>
       <c r="E10" s="68" t="n"/>
-      <c r="F10" s="147" t="n"/>
+      <c r="F10" s="147" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G10" s="111" t="n"/>
       <c r="H10" s="64" t="n"/>
       <c r="I10" s="64" t="n"/>
@@ -29599,37 +30436,48 @@
         <v/>
       </c>
       <c r="AR10" s="133">
-        <f>IF(ISNUMBER(AG10),AG10,IF(ISNUMBER(H10),H10,0))</f>
+        <f>IF(Entities!$F26="",0,Entities!$F26)</f>
         <v/>
       </c>
       <c r="AS10" s="133">
-        <f>IF(ISNUMBER(AI10),AI10,IF(ISNUMBER(I10),I10,0))</f>
+        <f>IF(Entities!$G26="",0,Entities!$G26)</f>
         <v/>
       </c>
       <c r="AT10" s="133">
-        <f>IF(ISNUMBER(AK10),AK10,IF(ISNUMBER(J10),J10,0))</f>
+        <f>IF(Entities!$H26="",0,Entities!$H26)</f>
         <v/>
       </c>
       <c r="AU10" s="133">
-        <f>IF(ISNUMBER(AM10),AM10,IF(ISNUMBER(K10),K10,0))</f>
+        <f>IF(Entities!$I26="",0,Entities!$I26)</f>
         <v/>
       </c>
       <c r="AV10" s="133">
-        <f>IF(ISNUMBER(AO10),AO10,IF(ISNUMBER(L10),L10,0))</f>
+        <f>IF(Entities!$J26="",0,Entities!$J26)</f>
         <v/>
       </c>
       <c r="AW10" s="133">
-        <f>IF(ISNUMBER(AQ10),AQ10,IF(ISNUMBER(M10),M10,0))</f>
+        <f>IF(Entities!$K26="",0,Entities!$K26)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="68" t="n"/>
-      <c r="B11" s="68" t="n"/>
-      <c r="C11" s="68" t="n"/>
+      <c r="A11" s="68">
+        <f>IF(Entities!$B13="","",Entities!$B13)</f>
+        <v/>
+      </c>
+      <c r="B11" s="68">
+        <f>IF(Entities!$C13="","",Entities!$C13)</f>
+        <v/>
+      </c>
+      <c r="C11" s="68">
+        <f>IF(Entities!$D13="","",Entities!$D13)</f>
+        <v/>
+      </c>
       <c r="D11" s="68" t="n"/>
       <c r="E11" s="68" t="n"/>
-      <c r="F11" s="147" t="n"/>
+      <c r="F11" s="147" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G11" s="111" t="n"/>
       <c r="H11" s="64" t="n"/>
       <c r="I11" s="64" t="n"/>
@@ -29701,37 +30549,48 @@
         <v/>
       </c>
       <c r="AR11" s="133">
-        <f>IF(ISNUMBER(AG11),AG11,IF(ISNUMBER(H11),H11,0))</f>
+        <f>IF(Entities!$F27="",0,Entities!$F27)</f>
         <v/>
       </c>
       <c r="AS11" s="133">
-        <f>IF(ISNUMBER(AI11),AI11,IF(ISNUMBER(I11),I11,0))</f>
+        <f>IF(Entities!$G27="",0,Entities!$G27)</f>
         <v/>
       </c>
       <c r="AT11" s="133">
-        <f>IF(ISNUMBER(AK11),AK11,IF(ISNUMBER(J11),J11,0))</f>
+        <f>IF(Entities!$H27="",0,Entities!$H27)</f>
         <v/>
       </c>
       <c r="AU11" s="133">
-        <f>IF(ISNUMBER(AM11),AM11,IF(ISNUMBER(K11),K11,0))</f>
+        <f>IF(Entities!$I27="",0,Entities!$I27)</f>
         <v/>
       </c>
       <c r="AV11" s="133">
-        <f>IF(ISNUMBER(AO11),AO11,IF(ISNUMBER(L11),L11,0))</f>
+        <f>IF(Entities!$J27="",0,Entities!$J27)</f>
         <v/>
       </c>
       <c r="AW11" s="133">
-        <f>IF(ISNUMBER(AQ11),AQ11,IF(ISNUMBER(M11),M11,0))</f>
+        <f>IF(Entities!$K27="",0,Entities!$K27)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="68" t="n"/>
-      <c r="B12" s="68" t="n"/>
-      <c r="C12" s="68" t="n"/>
+      <c r="A12" s="68">
+        <f>IF(Entities!$B14="","",Entities!$B14)</f>
+        <v/>
+      </c>
+      <c r="B12" s="68">
+        <f>IF(Entities!$C14="","",Entities!$C14)</f>
+        <v/>
+      </c>
+      <c r="C12" s="68">
+        <f>IF(Entities!$D14="","",Entities!$D14)</f>
+        <v/>
+      </c>
       <c r="D12" s="68" t="n"/>
       <c r="E12" s="68" t="n"/>
-      <c r="F12" s="147" t="n"/>
+      <c r="F12" s="147" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G12" s="111" t="n"/>
       <c r="H12" s="64" t="n"/>
       <c r="I12" s="64" t="n"/>
@@ -29803,37 +30662,48 @@
         <v/>
       </c>
       <c r="AR12" s="133">
-        <f>IF(ISNUMBER(AG12),AG12,IF(ISNUMBER(H12),H12,0))</f>
+        <f>IF(Entities!$F28="",0,Entities!$F28)</f>
         <v/>
       </c>
       <c r="AS12" s="133">
-        <f>IF(ISNUMBER(AI12),AI12,IF(ISNUMBER(I12),I12,0))</f>
+        <f>IF(Entities!$G28="",0,Entities!$G28)</f>
         <v/>
       </c>
       <c r="AT12" s="133">
-        <f>IF(ISNUMBER(AK12),AK12,IF(ISNUMBER(J12),J12,0))</f>
+        <f>IF(Entities!$H28="",0,Entities!$H28)</f>
         <v/>
       </c>
       <c r="AU12" s="133">
-        <f>IF(ISNUMBER(AM12),AM12,IF(ISNUMBER(K12),K12,0))</f>
+        <f>IF(Entities!$I28="",0,Entities!$I28)</f>
         <v/>
       </c>
       <c r="AV12" s="133">
-        <f>IF(ISNUMBER(AO12),AO12,IF(ISNUMBER(L12),L12,0))</f>
+        <f>IF(Entities!$J28="",0,Entities!$J28)</f>
         <v/>
       </c>
       <c r="AW12" s="133">
-        <f>IF(ISNUMBER(AQ12),AQ12,IF(ISNUMBER(M12),M12,0))</f>
+        <f>IF(Entities!$K28="",0,Entities!$K28)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="68" t="n"/>
-      <c r="B13" s="68" t="n"/>
-      <c r="C13" s="68" t="n"/>
+      <c r="A13" s="68">
+        <f>IF(Entities!$B15="","",Entities!$B15)</f>
+        <v/>
+      </c>
+      <c r="B13" s="68">
+        <f>IF(Entities!$C15="","",Entities!$C15)</f>
+        <v/>
+      </c>
+      <c r="C13" s="68">
+        <f>IF(Entities!$D15="","",Entities!$D15)</f>
+        <v/>
+      </c>
       <c r="D13" s="68" t="n"/>
       <c r="E13" s="68" t="n"/>
-      <c r="F13" s="147" t="n"/>
+      <c r="F13" s="147" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G13" s="111" t="n"/>
       <c r="H13" s="64" t="n"/>
       <c r="I13" s="64" t="n"/>
@@ -29905,37 +30775,48 @@
         <v/>
       </c>
       <c r="AR13" s="133">
-        <f>IF(ISNUMBER(AG13),AG13,IF(ISNUMBER(H13),H13,0))</f>
+        <f>IF(Entities!$F29="",0,Entities!$F29)</f>
         <v/>
       </c>
       <c r="AS13" s="133">
-        <f>IF(ISNUMBER(AI13),AI13,IF(ISNUMBER(I13),I13,0))</f>
+        <f>IF(Entities!$G29="",0,Entities!$G29)</f>
         <v/>
       </c>
       <c r="AT13" s="133">
-        <f>IF(ISNUMBER(AK13),AK13,IF(ISNUMBER(J13),J13,0))</f>
+        <f>IF(Entities!$H29="",0,Entities!$H29)</f>
         <v/>
       </c>
       <c r="AU13" s="133">
-        <f>IF(ISNUMBER(AM13),AM13,IF(ISNUMBER(K13),K13,0))</f>
+        <f>IF(Entities!$I29="",0,Entities!$I29)</f>
         <v/>
       </c>
       <c r="AV13" s="133">
-        <f>IF(ISNUMBER(AO13),AO13,IF(ISNUMBER(L13),L13,0))</f>
+        <f>IF(Entities!$J29="",0,Entities!$J29)</f>
         <v/>
       </c>
       <c r="AW13" s="133">
-        <f>IF(ISNUMBER(AQ13),AQ13,IF(ISNUMBER(M13),M13,0))</f>
+        <f>IF(Entities!$K29="",0,Entities!$K29)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="68" t="n"/>
-      <c r="B14" s="68" t="n"/>
-      <c r="C14" s="68" t="n"/>
+      <c r="A14" s="68">
+        <f>IF(Entities!$B16="","",Entities!$B16)</f>
+        <v/>
+      </c>
+      <c r="B14" s="68">
+        <f>IF(Entities!$C16="","",Entities!$C16)</f>
+        <v/>
+      </c>
+      <c r="C14" s="68">
+        <f>IF(Entities!$D16="","",Entities!$D16)</f>
+        <v/>
+      </c>
       <c r="D14" s="68" t="n"/>
       <c r="E14" s="68" t="n"/>
-      <c r="F14" s="147" t="n"/>
+      <c r="F14" s="147" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G14" s="111" t="n"/>
       <c r="H14" s="64" t="n"/>
       <c r="I14" s="64" t="n"/>
@@ -30007,27 +30888,27 @@
         <v/>
       </c>
       <c r="AR14" s="133">
-        <f>IF(ISNUMBER(AG14),AG14,IF(ISNUMBER(H14),H14,0))</f>
+        <f>IF(Entities!$F30="",0,Entities!$F30)</f>
         <v/>
       </c>
       <c r="AS14" s="133">
-        <f>IF(ISNUMBER(AI14),AI14,IF(ISNUMBER(I14),I14,0))</f>
+        <f>IF(Entities!$G30="",0,Entities!$G30)</f>
         <v/>
       </c>
       <c r="AT14" s="133">
-        <f>IF(ISNUMBER(AK14),AK14,IF(ISNUMBER(J14),J14,0))</f>
+        <f>IF(Entities!$H30="",0,Entities!$H30)</f>
         <v/>
       </c>
       <c r="AU14" s="133">
-        <f>IF(ISNUMBER(AM14),AM14,IF(ISNUMBER(K14),K14,0))</f>
+        <f>IF(Entities!$I30="",0,Entities!$I30)</f>
         <v/>
       </c>
       <c r="AV14" s="133">
-        <f>IF(ISNUMBER(AO14),AO14,IF(ISNUMBER(L14),L14,0))</f>
+        <f>IF(Entities!$J30="",0,Entities!$J30)</f>
         <v/>
       </c>
       <c r="AW14" s="133">
-        <f>IF(ISNUMBER(AQ14),AQ14,IF(ISNUMBER(M14),M14,0))</f>
+        <f>IF(Entities!$K30="",0,Entities!$K30)</f>
         <v/>
       </c>
     </row>
@@ -30294,14 +31175,13 @@
           <t>Reference entity ticker</t>
         </is>
       </c>
-      <c r="B19" s="68" t="inlineStr">
-        <is>
-          <t>HSBA LN Equity</t>
-        </is>
-      </c>
-      <c r="C19" s="65" t="inlineStr">
-        <is>
-          <t>Drives the CDS_SPREAD_TICKER_nY lookups on CDS_Quotes.</t>
+      <c r="B19" s="68">
+        <f>IF(Entities!$F$4="","",Entities!$F$4)</f>
+        <v/>
+      </c>
+      <c r="C19" s="177" t="inlineStr">
+        <is>
+          <t>from Entities!F4 - the selected name's ticker</t>
         </is>
       </c>
     </row>
@@ -30409,10 +31289,9 @@
           <t>Active entity</t>
         </is>
       </c>
-      <c r="B27" s="68" t="inlineStr">
-        <is>
-          <t>DEMO curve (not market)</t>
-        </is>
+      <c r="B27" s="68">
+        <f>Entities!$B$4</f>
+        <v/>
       </c>
       <c r="C27" s="65" t="inlineStr">
         <is>

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -777,6 +777,125 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SOFR zero curve</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Curves'!D5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Curves'!$B$6:$B$70</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Curves'!$D$6:$D$70</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>T (years)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>zero %</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
@@ -1429,6 +1548,434 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>CDS term structure - market vs model</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Curves'!B84</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Curves'!$F$85:$F$90</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Curves'!$B$85:$B$90</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Curves'!C84</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Curves'!$F$85:$F$90</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Curves'!$C$85:$C$90</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>tenor (years)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>spread (bp)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Hazard and survival term structure</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Curves'!B74</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Curves'!$E$75:$E$80</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Curves'!$B$75:$B$80</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Curves'!C74</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Curves'!$E$75:$E$80</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Curves'!$C$75:$C$80</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>tenor (years)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Default probability term structure</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Curves'!D74</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Curves'!$E$75:$E$80</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Curves'!$D$75:$D$80</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>tenor (years)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>1 - Q(t)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -1736,6 +2283,94 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>99</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="7" name="Chart 7"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="8" name="Chart 8"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>131</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="9" name="Chart 9"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>147</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="10" name="Chart 10"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -23809,7 +24444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25059,6 +25694,11 @@
           <t>Default prob 1-Q</t>
         </is>
       </c>
+      <c r="E74" s="183" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -25077,6 +25717,10 @@
         <f>Hazard_Bootstrap!F7</f>
         <v/>
       </c>
+      <c r="E75" s="32">
+        <f>CDS_Quotes!B7</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -25095,6 +25739,10 @@
         <f>Hazard_Bootstrap!F8</f>
         <v/>
       </c>
+      <c r="E76" s="32">
+        <f>CDS_Quotes!B8</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -25113,6 +25761,10 @@
         <f>Hazard_Bootstrap!F9</f>
         <v/>
       </c>
+      <c r="E77" s="32">
+        <f>CDS_Quotes!B9</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -25131,6 +25783,10 @@
         <f>Hazard_Bootstrap!F10</f>
         <v/>
       </c>
+      <c r="E78" s="32">
+        <f>CDS_Quotes!B10</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -25149,6 +25805,10 @@
         <f>Hazard_Bootstrap!F11</f>
         <v/>
       </c>
+      <c r="E79" s="32">
+        <f>CDS_Quotes!B11</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -25167,6 +25827,10 @@
         <f>Hazard_Bootstrap!F12</f>
         <v/>
       </c>
+      <c r="E80" s="32">
+        <f>CDS_Quotes!B12</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="67" t="inlineStr">
@@ -25199,6 +25863,11 @@
       <c r="E84" s="183" t="inlineStr">
         <is>
           <t>Traded spread</t>
+        </is>
+      </c>
+      <c r="F84" s="183" t="inlineStr">
+        <is>
+          <t>Years</t>
         </is>
       </c>
     </row>
@@ -25223,6 +25892,10 @@
         <f>CDS_Pricer!$B$15</f>
         <v/>
       </c>
+      <c r="F85" s="32">
+        <f>CDS_Quotes!B7</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -25245,6 +25918,10 @@
         <f>CDS_Pricer!$B$15</f>
         <v/>
       </c>
+      <c r="F86" s="32">
+        <f>CDS_Quotes!B8</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -25267,6 +25944,10 @@
         <f>CDS_Pricer!$B$15</f>
         <v/>
       </c>
+      <c r="F87" s="32">
+        <f>CDS_Quotes!B9</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -25289,6 +25970,10 @@
         <f>CDS_Pricer!$B$15</f>
         <v/>
       </c>
+      <c r="F88" s="32">
+        <f>CDS_Quotes!B10</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -25311,6 +25996,10 @@
         <f>CDS_Pricer!$B$15</f>
         <v/>
       </c>
+      <c r="F89" s="32">
+        <f>CDS_Quotes!B11</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -25332,6 +26021,17 @@
       <c r="E90" s="50">
         <f>CDS_Pricer!$B$15</f>
         <v/>
+      </c>
+      <c r="F90" s="32">
+        <f>CDS_Quotes!B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="177" t="inlineStr">
+        <is>
+          <t>Term structure on a true time axis. The line charts above use tenor labels, which space 1Y-2Y and 5Y-10Y equally.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -675,110 +675,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>SOFR zero curve</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Curves'!D5</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Curves'!$A$6:$A$70</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Curves'!$D$6:$D$70</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>zero %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="13"/>
   <chart>
     <title>
@@ -838,7 +734,10 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="50"/>
+          <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -856,15 +755,19 @@
             </rich>
           </tx>
         </title>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="20"/>
+        <majorUnit val="5"/>
       </valAx>
       <valAx>
         <axId val="20"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -876,19 +779,21 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>zero %</a:t>
+                  <a:t>zero rate (%)</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="0.00" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -898,6 +803,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
   <chart>
     <title>
       <tx>
@@ -908,15 +814,14 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Discount factors</a:t>
+              <a:t>SOFR discount factors</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
+      <scatterChart>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -938,37 +843,29 @@
               </a:ln>
             </spPr>
           </marker>
-          <cat>
+          <xVal>
             <numRef>
-              <f>'Curves'!$A$6:$A$70</f>
+              <f>'Curves'!$B$6:$B$70</f>
             </numRef>
-          </cat>
-          <val>
+          </xVal>
+          <yVal>
             <numRef>
               <f>'Curves'!$C$6:$C$70</f>
             </numRef>
-          </val>
+          </yVal>
           <smooth val="0"/>
         </ser>
         <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="50"/>
+          <min val="0"/>
         </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -980,19 +877,51 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>DF</a:t>
+                  <a:t>T (years)</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="20"/>
+        <majorUnit val="5"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>D(0,t)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0.00" sourceLinked="0"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1002,6 +931,7 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
   <chart>
     <title>
       <tx>
@@ -1012,21 +942,20 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Hazard (piecewise constant) and survival</a:t>
+              <a:t>SOFR zero curve - first 10 years</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
+      <scatterChart>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Curves'!B74</f>
+              <f>'Curves'!D5</f>
             </strRef>
           </tx>
           <spPr>
@@ -1042,70 +971,29 @@
               </a:ln>
             </spPr>
           </marker>
-          <cat>
+          <xVal>
             <numRef>
-              <f>'Curves'!$A$75:$A$80</f>
+              <f>'Curves'!$B$6:$B$70</f>
             </numRef>
-          </cat>
-          <val>
+          </xVal>
+          <yVal>
             <numRef>
-              <f>'Curves'!$B$75:$B$80</f>
+              <f>'Curves'!$D$6:$D$70</f>
             </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Curves'!C74</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Curves'!$A$75:$A$80</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Curves'!$C$75:$C$80</f>
-            </numRef>
-          </val>
+          </yVal>
           <smooth val="0"/>
         </ser>
         <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="10"/>
+          <min val="0"/>
         </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -1117,132 +1005,25 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>%</a:t>
+                  <a:t>T (years)</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
-        <crossAx val="10"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="20"/>
+        <majorUnit val="1"/>
       </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Spread term structure - market vs model</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Curves'!B84</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Curves'!$A$85:$A$90</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Curves'!$B$85:$B$90</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Curves'!C84</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Curves'!$A$85:$A$90</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Curves'!$C$85:$C$90</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
+      <valAx>
+        <axId val="20"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -1254,19 +1035,21 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>bp</a:t>
+                  <a:t>zero rate (%)</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="0.00" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1274,281 +1057,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Default probability 1-Q(t)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Curves'!D74</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Curves'!$A$75:$A$80</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Curves'!$D$75:$D$80</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>probability</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>CDSW view - credit curve vs traded spread</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Curves'!B84</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Curves'!$A$85:$A$90</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Curves'!$B$85:$B$90</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Curves'!C84</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Curves'!$A$85:$A$90</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Curves'!$C$85:$C$90</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'Curves'!E84</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Curves'!$A$85:$A$90</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Curves'!$E$85:$E$90</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>bp</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="13"/>
   <chart>
@@ -1644,7 +1153,10 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="10"/>
+          <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -1662,15 +1174,19 @@
             </rich>
           </tx>
         </title>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="20"/>
+        <majorUnit val="1"/>
       </valAx>
       <valAx>
         <axId val="20"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -1688,13 +1204,15 @@
             </rich>
           </tx>
         </title>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="0" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1702,7 +1220,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="13"/>
   <chart>
@@ -1715,7 +1233,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Hazard and survival term structure</a:t>
+              <a:t>CDSW view - credit curve vs traded spread</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1728,7 +1246,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Curves'!B74</f>
+              <f>'Curves'!B84</f>
             </strRef>
           </tx>
           <spPr>
@@ -1747,12 +1265,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Curves'!$E$75:$E$80</f>
+              <f>'Curves'!$F$85:$F$90</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Curves'!$B$75:$B$80</f>
+              <f>'Curves'!$B$85:$B$90</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -1760,6 +1278,287 @@
         <ser>
           <idx val="1"/>
           <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Curves'!C84</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Curves'!$F$85:$F$90</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Curves'!$C$85:$C$90</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Curves'!E84</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Curves'!$F$85:$F$90</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Curves'!$E$85:$E$90</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="10"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>tenor (years)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="20"/>
+        <majorUnit val="1"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>spread (bp)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Hazard rate (piecewise constant)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Curves'!$A$100:$A$111</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Curves'!$B$100:$B$111</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="10"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>t (years)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="20"/>
+        <majorUnit val="1"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>hazard (%)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0.00" sourceLinked="0"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Survival Q(t)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
           <tx>
             <strRef>
               <f>'Curves'!C74</f>
@@ -1798,7 +1597,10 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="10"/>
+          <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -1816,15 +1618,19 @@
             </rich>
           </tx>
         </title>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="20"/>
+        <majorUnit val="1"/>
       </valAx>
       <valAx>
         <axId val="20"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -1836,19 +1642,21 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>Q(t)</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="0.00" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1856,7 +1664,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="13"/>
   <chart>
@@ -1869,7 +1677,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Default probability term structure</a:t>
+              <a:t>Default probability 1 - Q(t)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1918,7 +1726,10 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="10"/>
+          <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -1936,15 +1747,19 @@
             </rich>
           </tx>
         </title>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="20"/>
+        <majorUnit val="1"/>
       </valAx>
       <valAx>
         <axId val="20"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -1962,13 +1777,15 @@
             </rich>
           </tx>
         </title>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -2158,12 +1975,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="6120000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2180,12 +1997,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="6120000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -2202,12 +2019,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="6120000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -2224,12 +2041,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="6120000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -2246,12 +2063,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="6120000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -2268,12 +2085,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="6120000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -2290,12 +2107,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="2880000"/>
+    <ext cx="6120000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -2312,12 +2129,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>115</row>
+      <row>129</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="2880000"/>
+    <ext cx="6120000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -2327,50 +2144,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>131</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5760000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="9" name="Chart 9"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>147</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5760000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="10" name="Chart 10"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -24444,7 +24217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24463,7 +24236,7 @@
     <row r="2">
       <c r="A2" s="177" t="inlineStr">
         <is>
-          <t>Discount curve is the pasted snapshot. Hazard and survival come from the strip.</t>
+          <t>Discount curve from Curve_Interface. Hazard and survival from the strip. All charts use a numeric time axis, so pillar spacing is to scale.</t>
         </is>
       </c>
     </row>
@@ -26028,10 +25801,147 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="177" t="inlineStr">
-        <is>
-          <t>Term structure on a true time axis. The line charts above use tenor labels, which space 1Y-2Y and 5Y-10Y equally.</t>
-        </is>
+      <c r="A98" s="67" t="inlineStr">
+        <is>
+          <t>Hazard step coordinates (drawing aid)</t>
+        </is>
+      </c>
+      <c r="C98" s="177" t="inlineStr">
+        <is>
+          <t>piecewise constant per p.8, so it is drawn flat-then-jump</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="183" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="B99" s="183" t="inlineStr">
+        <is>
+          <t>hazard %</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="50">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="B100" s="33">
+        <f>$B$75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="50">
+        <f>$E$75</f>
+        <v/>
+      </c>
+      <c r="B101" s="33">
+        <f>$B$75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="50">
+        <f>$E$75</f>
+        <v/>
+      </c>
+      <c r="B102" s="33">
+        <f>$B$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="50">
+        <f>$E$76</f>
+        <v/>
+      </c>
+      <c r="B103" s="33">
+        <f>$B$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="50">
+        <f>$E$76</f>
+        <v/>
+      </c>
+      <c r="B104" s="33">
+        <f>$B$77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="50">
+        <f>$E$77</f>
+        <v/>
+      </c>
+      <c r="B105" s="33">
+        <f>$B$77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="50">
+        <f>$E$77</f>
+        <v/>
+      </c>
+      <c r="B106" s="33">
+        <f>$B$78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="50">
+        <f>$E$78</f>
+        <v/>
+      </c>
+      <c r="B107" s="33">
+        <f>$B$78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="50">
+        <f>$E$78</f>
+        <v/>
+      </c>
+      <c r="B108" s="33">
+        <f>$B$79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="50">
+        <f>$E$79</f>
+        <v/>
+      </c>
+      <c r="B109" s="33">
+        <f>$B$79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="50">
+        <f>$E$79</f>
+        <v/>
+      </c>
+      <c r="B110" s="33">
+        <f>$B$80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="50">
+        <f>$E$80</f>
+        <v/>
+      </c>
+      <c r="B111" s="33">
+        <f>$B$80</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -46,7 +46,7 @@
     <numFmt numFmtId="174" formatCode="0.###"/>
     <numFmt numFmtId="175" formatCode="$#,##0;($#,##0);-"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -221,6 +221,11 @@
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="15"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -307,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="208">
+  <cellXfs count="225">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -602,6 +607,27 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="12" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="17" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="17" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="17" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="17" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2438,352 +2464,917 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="66" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="173" t="inlineStr">
-        <is>
-          <t>How this workbook prices a CDS</t>
-        </is>
-      </c>
+      <c r="A1" s="208" t="inlineStr">
+        <is>
+          <t>CDS Pricer</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="177" t="inlineStr">
-        <is>
-          <t>Left to right along the tabs. Each step feeds the next.</t>
-        </is>
-      </c>
+      <c r="A2" s="209" t="inlineStr">
+        <is>
+          <t>Put a ticker in the yellow box. Everything below follows: spreads pull, hazard strips, CDSW figures come out.</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="11" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="206" t="inlineStr">
+      <c r="A4" s="210" t="inlineStr">
+        <is>
+          <t>INPUTS</t>
+        </is>
+      </c>
+      <c r="B4" s="211" t="n"/>
+      <c r="C4" s="211" t="n"/>
+      <c r="D4" s="211" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="212" t="inlineStr">
+        <is>
+          <t>Reference entity ticker</t>
+        </is>
+      </c>
+      <c r="B5" s="213" t="inlineStr">
+        <is>
+          <t>HSBA LN Equity</t>
+        </is>
+      </c>
+      <c r="C5" s="209" t="inlineStr">
+        <is>
+          <t>BDP resolves the CDS tickers from this</t>
+        </is>
+      </c>
+      <c r="D5" s="212" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="212" t="inlineStr">
+        <is>
+          <t>Notional</t>
+        </is>
+      </c>
+      <c r="B6" s="214" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C6" s="209" t="inlineStr"/>
+      <c r="D6" s="212" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="212" t="inlineStr">
+        <is>
+          <t>Standard coupon (bp)</t>
+        </is>
+      </c>
+      <c r="B7" s="95" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" s="209" t="inlineStr">
+        <is>
+          <t>100 or 500</t>
+        </is>
+      </c>
+      <c r="D7" s="212" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="212" t="inlineStr">
+        <is>
+          <t>Recovery R</t>
+        </is>
+      </c>
+      <c r="B8" s="121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C8" s="209" t="inlineStr">
+        <is>
+          <t>model parameter, conventionally 0.40</t>
+        </is>
+      </c>
+      <c r="D8" s="212" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="212" t="inlineStr">
+        <is>
+          <t>Maturity (tenor yrs)</t>
+        </is>
+      </c>
+      <c r="B9" s="95" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="209" t="inlineStr"/>
+      <c r="D9" s="212" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="11" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="212" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="B10" s="213" t="inlineStr">
+        <is>
+          <t>Buy protection</t>
+        </is>
+      </c>
+      <c r="C10" s="209" t="inlineStr"/>
+      <c r="D10" s="212" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="11" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="212" t="inlineStr">
+        <is>
+          <t>Valuation date</t>
+        </is>
+      </c>
+      <c r="B11" s="111" t="n"/>
+      <c r="C11" s="209" t="inlineStr">
+        <is>
+          <t>leave blank to keep the curve's date</t>
+        </is>
+      </c>
+      <c r="D11" s="212" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="212" t="inlineStr">
+        <is>
+          <t>Hazard solver</t>
+        </is>
+      </c>
+      <c r="B12" s="184">
+        <f>CDS_Parameters!$B$30</f>
+        <v/>
+      </c>
+      <c r="C12" s="209" t="inlineStr">
+        <is>
+          <t>Brent, one call per tenor. Change at CDS_Parameters!B30.</t>
+        </is>
+      </c>
+      <c r="D12" s="212" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="215" t="n"/>
+      <c r="B13" s="215" t="n"/>
+      <c r="C13" s="212" t="n"/>
+      <c r="D13" s="212" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="215" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="212" t="inlineStr">
+        <is>
+          <t>Curve link</t>
+        </is>
+      </c>
+      <c r="B15" s="184">
+        <f>IF(COUNT(Curve_Interface!$L$8:$L$73)=0,"curve workbook not open",COUNT(Curve_Interface!$L$8:$L$73)&amp;" pillars")</f>
+        <v/>
+      </c>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="212" t="inlineStr">
+        <is>
+          <t>Spreads</t>
+        </is>
+      </c>
+      <c r="B16" s="184">
+        <f>IF(COUNTIF(CDS_Quotes!$H$7:$H$12,"BDP live")&gt;0,COUNTIF(CDS_Quotes!$H$7:$H$12,"BDP live")&amp;" of 6 live","manual / demo")</f>
+        <v/>
+      </c>
+      <c r="C16" s="212" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="212" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="B17" s="184">
+        <f>IF(MAX(ABS(Hazard_Bootstrap!$J$7:$J$12))&lt;0.01,"reprices, max err "&amp;TEXT(MAX(ABS(Hazard_Bootstrap!$J$7:$J$12)),"0.00E+00")&amp;" bp","STRIP FAILED - check the quotes, see Model_Notes p.9")</f>
+        <v/>
+      </c>
+      <c r="C17" s="212" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="215" t="n"/>
+      <c r="C18" s="212" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="215" t="inlineStr">
+        <is>
+          <t>CDSW SCREEN</t>
+        </is>
+      </c>
+      <c r="B19" s="215" t="n"/>
+      <c r="C19" s="209" t="inlineStr">
+        <is>
+          <t>mirrors CDS_Pricer rows 15-37</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="212" t="inlineStr">
+        <is>
+          <t>Par spread (bp)</t>
+        </is>
+      </c>
+      <c r="B20" s="170">
+        <f>CDS_Pricer!$B$15</f>
+        <v/>
+      </c>
+      <c r="C20" s="212" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="212" t="inlineStr">
+        <is>
+          <t>Points upfront</t>
+        </is>
+      </c>
+      <c r="B21" s="170">
+        <f>CDS_Pricer!$B$31</f>
+        <v/>
+      </c>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="212" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B22" s="170">
+        <f>CDS_Pricer!$B$32</f>
+        <v/>
+      </c>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="212" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="B23" s="216">
+        <f>CDS_Pricer!$B$33</f>
+        <v/>
+      </c>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="212" t="inlineStr">
+        <is>
+          <t>Accrued days</t>
+        </is>
+      </c>
+      <c r="B24" s="217">
+        <f>CDS_Pricer!$B$34</f>
+        <v/>
+      </c>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="212" t="inlineStr">
+        <is>
+          <t>Accrued</t>
+        </is>
+      </c>
+      <c r="B25" s="216">
+        <f>CDS_Pricer!$B$35</f>
+        <v/>
+      </c>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="212" t="inlineStr">
+        <is>
+          <t>Cash amount</t>
+        </is>
+      </c>
+      <c r="B26" s="216">
+        <f>CDS_Pricer!$B$36</f>
+        <v/>
+      </c>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="11" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="212" t="inlineStr">
+        <is>
+          <t>Default exposure</t>
+        </is>
+      </c>
+      <c r="B27" s="216">
+        <f>CDS_Pricer!$B$37</f>
+        <v/>
+      </c>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="212" t="inlineStr">
+        <is>
+          <t>Spread DV01 / CS01</t>
+        </is>
+      </c>
+      <c r="B29" s="216">
+        <f>CDS_Pricer!$B$22</f>
+        <v/>
+      </c>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="212" t="inlineStr">
+        <is>
+          <t>IR DV01</t>
+        </is>
+      </c>
+      <c r="B30" s="216">
+        <f>CDS_Pricer!$B$23</f>
+        <v/>
+      </c>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="212" t="inlineStr">
+        <is>
+          <t>Rec risk 1%</t>
+        </is>
+      </c>
+      <c r="B31" s="216">
+        <f>CDS_Pricer!$B$24</f>
+        <v/>
+      </c>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="212" t="inlineStr">
+        <is>
+          <t>Jump to default</t>
+        </is>
+      </c>
+      <c r="B32" s="216">
+        <f>CDS_Pricer!$B$25</f>
+        <v/>
+      </c>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="11" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="11" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="215" t="inlineStr">
+        <is>
+          <t>PIPELINE</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="11" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="206" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B4" s="206" t="inlineStr">
+      <c r="B35" s="206" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="C4" s="206" t="inlineStr">
+      <c r="C35" s="206" t="inlineStr">
         <is>
           <t>What happens</t>
         </is>
       </c>
-      <c r="D4" s="206" t="inlineStr">
+      <c r="D35" s="206" t="inlineStr">
         <is>
           <t>What to check</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="207" t="inlineStr">
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="11" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="106" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="106" t="inlineStr">
+      <c r="B36" s="106" t="inlineStr">
         <is>
           <t>Entities</t>
         </is>
       </c>
-      <c r="C5" s="190" t="inlineStr">
+      <c r="C36" s="190" t="inlineStr">
         <is>
           <t>Type the names and Bloomberg tickers. Pick the live one at B4.</t>
         </is>
       </c>
-      <c r="D5" s="190" t="inlineStr">
+      <c r="D36" s="190" t="inlineStr">
         <is>
           <t>F4 shows the ticker the pull will use.</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="207" t="inlineStr">
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="106" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="106" t="inlineStr">
+      <c r="B37" s="106" t="inlineStr">
         <is>
           <t>CDS_Parameters</t>
         </is>
       </c>
-      <c r="C6" s="190" t="inlineStr">
+      <c r="C37" s="190" t="inlineStr">
         <is>
           <t>Contract terms: recovery, notional, coupon, direction, maturity.</t>
         </is>
       </c>
-      <c r="D6" s="190" t="inlineStr">
+      <c r="D37" s="190" t="inlineStr">
         <is>
           <t>B30 picks the hazard solver.</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="207" t="inlineStr">
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="106" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="106" t="inlineStr">
+      <c r="B38" s="106" t="inlineStr">
         <is>
           <t>Curve_Interface</t>
         </is>
       </c>
-      <c r="C7" s="190" t="inlineStr">
+      <c r="C38" s="190" t="inlineStr">
         <is>
           <t>SOFR discount curve, linked from the curve workbook.</t>
         </is>
       </c>
-      <c r="D7" s="190" t="inlineStr">
+      <c r="D38" s="190" t="inlineStr">
         <is>
           <t>LINK CHECK at N8. Open the curve workbook first.</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="207" t="inlineStr">
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="106" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="106" t="inlineStr">
+      <c r="B39" s="106" t="inlineStr">
         <is>
           <t>CDS_Quotes</t>
         </is>
       </c>
-      <c r="C8" s="190" t="inlineStr">
+      <c r="C39" s="190" t="inlineStr">
         <is>
           <t>Two-step Bloomberg pull: entity -&gt; CDS ticker -&gt; spread.</t>
         </is>
       </c>
-      <c r="D8" s="190" t="inlineStr">
+      <c r="D39" s="190" t="inlineStr">
         <is>
           <t>Col H says whether each tenor came live or manual.</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="207" t="inlineStr">
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="106" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="106" t="inlineStr">
+      <c r="B40" s="106" t="inlineStr">
         <is>
           <t>Hazard_Bootstrap</t>
         </is>
       </c>
-      <c r="C9" s="190" t="inlineStr">
+      <c r="C40" s="190" t="inlineStr">
         <is>
           <t>Strips the hazard curve, one tenor at a time, earlier hazards held.</t>
         </is>
       </c>
-      <c r="D9" s="190" t="inlineStr">
+      <c r="D40" s="190" t="inlineStr">
         <is>
           <t>Col J is the repricing error. It must go to zero.</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="207" t="inlineStr">
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="106" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="106" t="inlineStr">
+      <c r="B41" s="106" t="inlineStr">
         <is>
           <t>CDS_Schedule</t>
         </is>
       </c>
-      <c r="C10" s="190" t="inlineStr">
+      <c r="C41" s="190" t="inlineStr">
         <is>
           <t>Builds the quarterly legs: DF, survival, accrual per period.</t>
         </is>
       </c>
-      <c r="D10" s="190" t="inlineStr">
+      <c r="D41" s="190" t="inlineStr">
         <is>
           <t>One row per coupon period.</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="207" t="inlineStr">
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="106" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B11" s="106" t="inlineStr">
+      <c r="B42" s="106" t="inlineStr">
         <is>
           <t>CDS_Pricer</t>
         </is>
       </c>
-      <c r="C11" s="190" t="inlineStr">
+      <c r="C42" s="190" t="inlineStr">
         <is>
           <t>Prices the trade and produces the CDSW settlement figures.</t>
         </is>
       </c>
-      <c r="D11" s="190" t="inlineStr">
+      <c r="D42" s="190" t="inlineStr">
         <is>
           <t>Row 28 down is the CDSW screen block.</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="207" t="inlineStr">
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="106" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B12" s="106" t="inlineStr">
+      <c r="B43" s="106" t="inlineStr">
         <is>
           <t>Curves</t>
         </is>
       </c>
-      <c r="C12" s="190" t="inlineStr">
+      <c r="C43" s="190" t="inlineStr">
         <is>
           <t>Charts: discount curve, hazard, survival, term structures.</t>
         </is>
       </c>
-      <c r="D12" s="190" t="inlineStr">
+      <c r="D43" s="190" t="inlineStr">
         <is>
           <t>Hazard is drawn as a step because it is piecewise constant.</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="207" t="inlineStr">
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="106" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B13" s="106" t="inlineStr">
+      <c r="B44" s="106" t="inlineStr">
         <is>
           <t>CDS_Validation</t>
         </is>
       </c>
-      <c r="C13" s="190" t="inlineStr">
+      <c r="C44" s="190" t="inlineStr">
         <is>
           <t>Internal checks on the strip.</t>
         </is>
       </c>
-      <c r="D13" s="190" t="inlineStr">
+      <c r="D44" s="190" t="inlineStr">
         <is>
           <t>All should pass before the numbers are used.</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="67" t="inlineStr">
-        <is>
-          <t>Reference tabs (not in the pricing path)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="67" t="inlineStr">
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="n"/>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="215" t="inlineStr">
+        <is>
+          <t>Reference tabs</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="n"/>
+      <c r="B47" s="215" t="inlineStr">
         <is>
           <t>Model_Notes</t>
         </is>
       </c>
-      <c r="C16" s="126" t="inlineStr">
+      <c r="C47" s="212" t="inlineStr">
         <is>
           <t>B-Model equations (3.1)-(3.6), conventions, strippability check.</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="67" t="inlineStr">
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="11" t="n"/>
+      <c r="F47" s="11" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="n"/>
+      <c r="B48" s="215" t="inlineStr">
         <is>
           <t>Brent_vs_Bisection</t>
         </is>
       </c>
-      <c r="C17" s="126" t="inlineStr">
+      <c r="C48" s="212" t="inlineStr">
         <is>
           <t>The two solvers side by side on the same objective.</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="67" t="inlineStr">
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="11" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="n"/>
+      <c r="B49" s="215" t="inlineStr">
         <is>
           <t>Root_Methods</t>
         </is>
       </c>
-      <c r="C18" s="126" t="inlineStr">
-        <is>
-          <t>Eight root-finders from MATH5030 M2 on the same objective.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="67" t="inlineStr">
+      <c r="C49" s="212" t="inlineStr">
+        <is>
+          <t>Eight root-finders from MATH5030 M2.</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="n"/>
+      <c r="B50" s="215" t="inlineStr">
         <is>
           <t>Hazard_Solver</t>
         </is>
       </c>
-      <c r="C19" s="126" t="inlineStr">
-        <is>
-          <t>The in-cell bisection ladder. 30 halvings per tenor, one row each.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="67" t="inlineStr">
+      <c r="C50" s="212" t="inlineStr">
+        <is>
+          <t>In-cell bisection ladder, the fallback solver.</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="11" t="n"/>
+      <c r="F50" s="11" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="n"/>
+      <c r="B51" s="215" t="inlineStr">
         <is>
           <t>CDS_Entities</t>
         </is>
       </c>
-      <c r="C20" s="126" t="inlineStr">
+      <c r="C51" s="212" t="inlineStr">
         <is>
           <t>Data store behind Entities, plus the CDSW capture block.</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="67" t="inlineStr">
-        <is>
-          <t>Needs VBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="126" t="inlineStr">
-        <is>
-          <t>CDSBrent.bas       hazard solver (Brent) and the objective</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="126" t="inlineStr">
-        <is>
-          <t>CDSRootFinders.bas the eight methods on Root_Methods</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="177" t="inlineStr">
-        <is>
-          <t>Without them the hazard column falls back to the in-cell ladder and still prices.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="66" t="inlineStr">
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="11" t="n"/>
+      <c r="F51" s="11" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="n"/>
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="11" t="n"/>
+      <c r="F52" s="11" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="n"/>
+      <c r="B53" s="209" t="inlineStr">
+        <is>
+          <t>Needs CDSBrent.bas and CDSRootFinders.bas imported, saved as .xlsm. Without them the strip falls back to the ladder and still prices.</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="11" t="n"/>
+      <c r="F53" s="11" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="n"/>
+      <c r="B54" s="218" t="inlineStr">
         <is>
           <t>Spreads are demo values. The SOFR curve is real market data; the credit curve is not.</t>
         </is>
       </c>
+      <c r="C54" s="11" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="11" t="n"/>
+      <c r="F54" s="11" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="n"/>
+      <c r="B55" s="11" t="n"/>
+      <c r="C55" s="11" t="n"/>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="11" t="n"/>
+      <c r="F55" s="11" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="n"/>
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="11" t="n"/>
+      <c r="F56" s="11" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="n"/>
+      <c r="B57" s="11" t="n"/>
+      <c r="C57" s="11" t="n"/>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="11" t="n"/>
+      <c r="F57" s="11" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="n"/>
+      <c r="B58" s="11" t="n"/>
+      <c r="C58" s="11" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="11" t="n"/>
+      <c r="F58" s="11" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="n"/>
+      <c r="B59" s="11" t="n"/>
+      <c r="C59" s="11" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="11" t="n"/>
+      <c r="F59" s="11" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="n"/>
+      <c r="B60" s="11" t="n"/>
+      <c r="C60" s="11" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="11" t="n"/>
+      <c r="F60" s="11" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Buy protection,Sell protection"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24272,8 +24863,9 @@
           <t>Recovery rate R</t>
         </is>
       </c>
-      <c r="B8" s="54" t="n">
-        <v>0.4</v>
+      <c r="B8" s="219">
+        <f>IF(Steps!$B$8="",0.4,Steps!$B$8)</f>
+        <v/>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
@@ -24287,8 +24879,9 @@
           <t>Notional</t>
         </is>
       </c>
-      <c r="B9" s="39" t="n">
-        <v>10000000</v>
+      <c r="B9" s="220">
+        <f>IF(Steps!$B$6="",10000000,Steps!$B$6)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -24297,8 +24890,9 @@
           <t>Standard coupon (bp)</t>
         </is>
       </c>
-      <c r="B10" s="41" t="n">
-        <v>100</v>
+      <c r="B10" s="221">
+        <f>IF(Steps!$B$7="",100,Steps!$B$7)</f>
+        <v/>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
@@ -24360,10 +24954,9 @@
           <t>Protection direction</t>
         </is>
       </c>
-      <c r="B15" s="37" t="inlineStr">
-        <is>
-          <t>Buy protection</t>
-        </is>
+      <c r="B15" s="222">
+        <f>IF(Steps!$B$10="","Buy protection",Steps!$B$10)</f>
+        <v/>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
@@ -24421,8 +25014,8 @@
           <t>Reference entity ticker</t>
         </is>
       </c>
-      <c r="B19" s="68">
-        <f>IF(Entities!$F$4="","",Entities!$F$4)</f>
+      <c r="B19" s="223">
+        <f>IF(Steps!$B$5="",IF(Entities!$F$4="","",Entities!$F$4),Steps!$B$5)</f>
         <v/>
       </c>
       <c r="C19" s="177" t="inlineStr">
@@ -24662,8 +25255,9 @@
           <t>Valuation date</t>
         </is>
       </c>
-      <c r="O5" s="186" t="n">
-        <v>46224</v>
+      <c r="O5" s="224">
+        <f>IF(Steps!$B$11&lt;&gt;"",Steps!$B$11,$K$8)</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -24679,7 +25273,7 @@
       </c>
       <c r="N6" s="177" t="inlineStr">
         <is>
-          <t>drives every date on the CDS sheets</t>
+          <t>blank on Steps = follow the curve workbook</t>
         </is>
       </c>
     </row>
@@ -30370,8 +30964,9 @@
           <t>Maturity (tenor yrs)</t>
         </is>
       </c>
-      <c r="B7" s="41" t="n">
-        <v>5</v>
+      <c r="B7" s="41">
+        <f>IF(Steps!$B$9="",5,Steps!$B$9)</f>
+        <v/>
       </c>
       <c r="J7" s="138" t="inlineStr">
         <is>

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -22593,14 +22593,24 @@
           <t>Spreads H:M are T3 (term structure). O:AC are T4 (the CDSW screen for that name) and are the acceptance test: see TEST_CASES.md.</t>
         </is>
       </c>
+      <c r="B3" s="177" t="inlineStr">
+        <is>
+          <t>display only - the ticker in use comes from Entities!F4</t>
+        </is>
+      </c>
       <c r="H3" s="67" t="inlineStr">
         <is>
           <t>TERM STRUCTURE (T3)</t>
         </is>
       </c>
-      <c r="O3" s="67" t="inlineStr">
-        <is>
-          <t>CDSW SCREEN CAPTURE (T4)</t>
+      <c r="O3" s="177" t="inlineStr">
+        <is>
+          <t>CDSW capture - context</t>
+        </is>
+      </c>
+      <c r="S3" s="177" t="inlineStr">
+        <is>
+          <t>CDSW capture - compared on CDS_Pricer rows 44-54</t>
         </is>
       </c>
       <c r="AE3" s="67" t="inlineStr">
@@ -22864,18 +22874,17 @@
         <f>IF(Entities!$D7="","",Entities!$D7)</f>
         <v/>
       </c>
-      <c r="D5" s="68" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E5" s="68" t="inlineStr">
-        <is>
-          <t>CR14</t>
-        </is>
-      </c>
-      <c r="F5" s="147" t="n">
-        <v>0.4</v>
+      <c r="D5" s="68">
+        <f>IF(Entities!$L7="","",Entities!$L7)</f>
+        <v/>
+      </c>
+      <c r="E5" s="68">
+        <f>IF(Entities!$M7="","",Entities!$M7)</f>
+        <v/>
+      </c>
+      <c r="F5" s="147">
+        <f>IF(Entities!$N7="",0.4,Entities!$N7)</f>
+        <v/>
       </c>
       <c r="G5" s="111" t="n">
         <v>46224</v>
@@ -23019,18 +23028,17 @@
         <f>IF(Entities!$D8="","",Entities!$D8)</f>
         <v/>
       </c>
-      <c r="D6" s="68" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E6" s="68" t="inlineStr">
-        <is>
-          <t>CR14</t>
-        </is>
-      </c>
-      <c r="F6" s="147" t="n">
-        <v>0.4</v>
+      <c r="D6" s="68">
+        <f>IF(Entities!$L8="","",Entities!$L8)</f>
+        <v/>
+      </c>
+      <c r="E6" s="68">
+        <f>IF(Entities!$M8="","",Entities!$M8)</f>
+        <v/>
+      </c>
+      <c r="F6" s="147">
+        <f>IF(Entities!$N8="",0.4,Entities!$N8)</f>
+        <v/>
       </c>
       <c r="G6" s="111" t="n"/>
       <c r="H6" s="64" t="n">
@@ -23152,10 +23160,17 @@
         <f>IF(Entities!$D9="","",Entities!$D9)</f>
         <v/>
       </c>
-      <c r="D7" s="68" t="n"/>
-      <c r="E7" s="68" t="n"/>
-      <c r="F7" s="147" t="n">
-        <v>0.4</v>
+      <c r="D7" s="68">
+        <f>IF(Entities!$L9="","",Entities!$L9)</f>
+        <v/>
+      </c>
+      <c r="E7" s="68">
+        <f>IF(Entities!$M9="","",Entities!$M9)</f>
+        <v/>
+      </c>
+      <c r="F7" s="147">
+        <f>IF(Entities!$N9="",0.4,Entities!$N9)</f>
+        <v/>
       </c>
       <c r="G7" s="111" t="n"/>
       <c r="H7" s="64" t="n"/>
@@ -23265,10 +23280,17 @@
         <f>IF(Entities!$D10="","",Entities!$D10)</f>
         <v/>
       </c>
-      <c r="D8" s="68" t="n"/>
-      <c r="E8" s="68" t="n"/>
-      <c r="F8" s="147" t="n">
-        <v>0.4</v>
+      <c r="D8" s="68">
+        <f>IF(Entities!$L10="","",Entities!$L10)</f>
+        <v/>
+      </c>
+      <c r="E8" s="68">
+        <f>IF(Entities!$M10="","",Entities!$M10)</f>
+        <v/>
+      </c>
+      <c r="F8" s="147">
+        <f>IF(Entities!$N10="",0.4,Entities!$N10)</f>
+        <v/>
       </c>
       <c r="G8" s="111" t="n"/>
       <c r="H8" s="64" t="n"/>
@@ -23378,10 +23400,17 @@
         <f>IF(Entities!$D11="","",Entities!$D11)</f>
         <v/>
       </c>
-      <c r="D9" s="68" t="n"/>
-      <c r="E9" s="68" t="n"/>
-      <c r="F9" s="147" t="n">
-        <v>0.4</v>
+      <c r="D9" s="68">
+        <f>IF(Entities!$L11="","",Entities!$L11)</f>
+        <v/>
+      </c>
+      <c r="E9" s="68">
+        <f>IF(Entities!$M11="","",Entities!$M11)</f>
+        <v/>
+      </c>
+      <c r="F9" s="147">
+        <f>IF(Entities!$N11="",0.4,Entities!$N11)</f>
+        <v/>
       </c>
       <c r="G9" s="111" t="n"/>
       <c r="H9" s="64" t="n"/>
@@ -23491,10 +23520,17 @@
         <f>IF(Entities!$D12="","",Entities!$D12)</f>
         <v/>
       </c>
-      <c r="D10" s="68" t="n"/>
-      <c r="E10" s="68" t="n"/>
-      <c r="F10" s="147" t="n">
-        <v>0.4</v>
+      <c r="D10" s="68">
+        <f>IF(Entities!$L12="","",Entities!$L12)</f>
+        <v/>
+      </c>
+      <c r="E10" s="68">
+        <f>IF(Entities!$M12="","",Entities!$M12)</f>
+        <v/>
+      </c>
+      <c r="F10" s="147">
+        <f>IF(Entities!$N12="",0.4,Entities!$N12)</f>
+        <v/>
       </c>
       <c r="G10" s="111" t="n"/>
       <c r="H10" s="64" t="n"/>
@@ -23604,10 +23640,17 @@
         <f>IF(Entities!$D13="","",Entities!$D13)</f>
         <v/>
       </c>
-      <c r="D11" s="68" t="n"/>
-      <c r="E11" s="68" t="n"/>
-      <c r="F11" s="147" t="n">
-        <v>0.4</v>
+      <c r="D11" s="68">
+        <f>IF(Entities!$L13="","",Entities!$L13)</f>
+        <v/>
+      </c>
+      <c r="E11" s="68">
+        <f>IF(Entities!$M13="","",Entities!$M13)</f>
+        <v/>
+      </c>
+      <c r="F11" s="147">
+        <f>IF(Entities!$N13="",0.4,Entities!$N13)</f>
+        <v/>
       </c>
       <c r="G11" s="111" t="n"/>
       <c r="H11" s="64" t="n"/>
@@ -23717,10 +23760,17 @@
         <f>IF(Entities!$D14="","",Entities!$D14)</f>
         <v/>
       </c>
-      <c r="D12" s="68" t="n"/>
-      <c r="E12" s="68" t="n"/>
-      <c r="F12" s="147" t="n">
-        <v>0.4</v>
+      <c r="D12" s="68">
+        <f>IF(Entities!$L14="","",Entities!$L14)</f>
+        <v/>
+      </c>
+      <c r="E12" s="68">
+        <f>IF(Entities!$M14="","",Entities!$M14)</f>
+        <v/>
+      </c>
+      <c r="F12" s="147">
+        <f>IF(Entities!$N14="",0.4,Entities!$N14)</f>
+        <v/>
       </c>
       <c r="G12" s="111" t="n"/>
       <c r="H12" s="64" t="n"/>
@@ -23830,10 +23880,17 @@
         <f>IF(Entities!$D15="","",Entities!$D15)</f>
         <v/>
       </c>
-      <c r="D13" s="68" t="n"/>
-      <c r="E13" s="68" t="n"/>
-      <c r="F13" s="147" t="n">
-        <v>0.4</v>
+      <c r="D13" s="68">
+        <f>IF(Entities!$L15="","",Entities!$L15)</f>
+        <v/>
+      </c>
+      <c r="E13" s="68">
+        <f>IF(Entities!$M15="","",Entities!$M15)</f>
+        <v/>
+      </c>
+      <c r="F13" s="147">
+        <f>IF(Entities!$N15="",0.4,Entities!$N15)</f>
+        <v/>
       </c>
       <c r="G13" s="111" t="n"/>
       <c r="H13" s="64" t="n"/>
@@ -23943,10 +24000,17 @@
         <f>IF(Entities!$D16="","",Entities!$D16)</f>
         <v/>
       </c>
-      <c r="D14" s="68" t="n"/>
-      <c r="E14" s="68" t="n"/>
-      <c r="F14" s="147" t="n">
-        <v>0.4</v>
+      <c r="D14" s="68">
+        <f>IF(Entities!$L16="","",Entities!$L16)</f>
+        <v/>
+      </c>
+      <c r="E14" s="68">
+        <f>IF(Entities!$M16="","",Entities!$M16)</f>
+        <v/>
+      </c>
+      <c r="F14" s="147">
+        <f>IF(Entities!$N16="",0.4,Entities!$N16)</f>
+        <v/>
       </c>
       <c r="G14" s="111" t="n"/>
       <c r="H14" s="64" t="n"/>
@@ -24068,7 +24132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -24125,7 +24189,17 @@
       </c>
     </row>
     <row r="5">
+      <c r="E5" s="177" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
       <c r="F5" s="177" t="n"/>
+      <c r="L5" s="177" t="inlineStr">
+        <is>
+          <t>identity - picks the ticker</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="179" t="inlineStr">
@@ -24181,6 +24255,21 @@
       <c r="K6" s="179" t="inlineStr">
         <is>
           <t>10Y</t>
+        </is>
+      </c>
+      <c r="L6" s="179" t="inlineStr">
+        <is>
+          <t>Seniority</t>
+        </is>
+      </c>
+      <c r="M6" s="179" t="inlineStr">
+        <is>
+          <t>Clause</t>
+        </is>
+      </c>
+      <c r="N6" s="179" t="inlineStr">
+        <is>
+          <t>Recovery</t>
         </is>
       </c>
     </row>
@@ -24206,6 +24295,19 @@
       <c r="I7" s="182" t="n"/>
       <c r="J7" s="182" t="n"/>
       <c r="K7" s="182" t="n"/>
+      <c r="L7" s="178" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="M7" s="178" t="inlineStr">
+        <is>
+          <t>CR14</t>
+        </is>
+      </c>
+      <c r="N7" s="181" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="178" t="n">
@@ -24229,6 +24331,19 @@
       <c r="I8" s="182" t="n"/>
       <c r="J8" s="182" t="n"/>
       <c r="K8" s="182" t="n"/>
+      <c r="L8" s="178" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="M8" s="178" t="inlineStr">
+        <is>
+          <t>CR14</t>
+        </is>
+      </c>
+      <c r="N8" s="181" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="178" t="n"/>
@@ -24242,6 +24357,11 @@
       <c r="I9" s="182" t="n"/>
       <c r="J9" s="182" t="n"/>
       <c r="K9" s="182" t="n"/>
+      <c r="L9" s="178" t="n"/>
+      <c r="M9" s="178" t="n"/>
+      <c r="N9" s="181" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="178" t="n"/>
@@ -24255,6 +24375,11 @@
       <c r="I10" s="182" t="n"/>
       <c r="J10" s="182" t="n"/>
       <c r="K10" s="182" t="n"/>
+      <c r="L10" s="178" t="n"/>
+      <c r="M10" s="178" t="n"/>
+      <c r="N10" s="181" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="178" t="n"/>
@@ -24268,6 +24393,11 @@
       <c r="I11" s="182" t="n"/>
       <c r="J11" s="182" t="n"/>
       <c r="K11" s="182" t="n"/>
+      <c r="L11" s="178" t="n"/>
+      <c r="M11" s="178" t="n"/>
+      <c r="N11" s="181" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="178" t="n"/>
@@ -24281,6 +24411,11 @@
       <c r="I12" s="182" t="n"/>
       <c r="J12" s="182" t="n"/>
       <c r="K12" s="182" t="n"/>
+      <c r="L12" s="178" t="n"/>
+      <c r="M12" s="178" t="n"/>
+      <c r="N12" s="181" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="178" t="n"/>
@@ -24294,6 +24429,11 @@
       <c r="I13" s="182" t="n"/>
       <c r="J13" s="182" t="n"/>
       <c r="K13" s="182" t="n"/>
+      <c r="L13" s="178" t="n"/>
+      <c r="M13" s="178" t="n"/>
+      <c r="N13" s="181" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="178" t="n"/>
@@ -24307,6 +24447,11 @@
       <c r="I14" s="182" t="n"/>
       <c r="J14" s="182" t="n"/>
       <c r="K14" s="182" t="n"/>
+      <c r="L14" s="178" t="n"/>
+      <c r="M14" s="178" t="n"/>
+      <c r="N14" s="181" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="178" t="n"/>
@@ -24320,6 +24465,11 @@
       <c r="I15" s="182" t="n"/>
       <c r="J15" s="182" t="n"/>
       <c r="K15" s="182" t="n"/>
+      <c r="L15" s="178" t="n"/>
+      <c r="M15" s="178" t="n"/>
+      <c r="N15" s="181" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="178" t="n"/>
@@ -24333,6 +24483,11 @@
       <c r="I16" s="182" t="n"/>
       <c r="J16" s="182" t="n"/>
       <c r="K16" s="182" t="n"/>
+      <c r="L16" s="178" t="n"/>
+      <c r="M16" s="178" t="n"/>
+      <c r="N16" s="181" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="67" t="inlineStr">
@@ -30876,7 +31031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -31427,9 +31582,9 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="65" t="inlineStr">
-        <is>
-          <t>Blank until the CDSW capture is typed into CDS_Entities. This is the acceptance test for the module.</t>
+      <c r="A42" s="177" t="inlineStr">
+        <is>
+          <t>Blank until a CDSW capture is typed into CDS_Entities O:AC. Notional, coupon, maturity and traded spread there are context for the capture, not compared.</t>
         </is>
       </c>
     </row>
@@ -31585,6 +31740,82 @@
       </c>
       <c r="D50" s="93">
         <f>IF(OR(B50="",NOT(ISNUMBER(B50))),"",C50-B50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="190" t="inlineStr">
+        <is>
+          <t>Spread DV01</t>
+        </is>
+      </c>
+      <c r="B51" s="180">
+        <f>IFERROR(INDEX(CDS_Entities!$Y$5:$Y$14,CDS_Parameters!$B$28),"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="180">
+        <f>B22</f>
+        <v/>
+      </c>
+      <c r="D51" s="180">
+        <f>IF(OR(B51="",NOT(ISNUMBER(B51))),"",C51-B51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="190" t="inlineStr">
+        <is>
+          <t>IR DV01</t>
+        </is>
+      </c>
+      <c r="B52" s="180">
+        <f>IFERROR(INDEX(CDS_Entities!$Z$5:$Z$14,CDS_Parameters!$B$28),"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="180">
+        <f>B23</f>
+        <v/>
+      </c>
+      <c r="D52" s="180">
+        <f>IF(OR(B52="",NOT(ISNUMBER(B52))),"",C52-B52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="190" t="inlineStr">
+        <is>
+          <t>Rec risk 1%</t>
+        </is>
+      </c>
+      <c r="B53" s="180">
+        <f>IFERROR(INDEX(CDS_Entities!$AA$5:$AA$14,CDS_Parameters!$B$28),"")</f>
+        <v/>
+      </c>
+      <c r="C53" s="180">
+        <f>B24</f>
+        <v/>
+      </c>
+      <c r="D53" s="180">
+        <f>IF(OR(B53="",NOT(ISNUMBER(B53))),"",C53-B53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="190" t="inlineStr">
+        <is>
+          <t>Prob 5Y (1-Q)</t>
+        </is>
+      </c>
+      <c r="B54" s="180">
+        <f>IFERROR(INDEX(CDS_Entities!$AC$5:$AC$14,CDS_Parameters!$B$28),"")</f>
+        <v/>
+      </c>
+      <c r="C54" s="180">
+        <f>IFERROR(INDEX(Hazard_Bootstrap!$F$7:$F$12,MATCH(5,CDS_Quotes!$B$7:$B$12,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D54" s="180">
+        <f>IF(OR(B54="",NOT(ISNUMBER(B54))),"",C54-B54)</f>
         <v/>
       </c>
     </row>

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -25333,7 +25333,7 @@
       </c>
       <c r="C30" s="177" t="inlineStr">
         <is>
-          <t>Brent = one call per tenor. Bisection = the 3,712-cell ladder on Hazard_Solver.</t>
+          <t>Brent = one call, strips off CDS_Schedule directly. Bisection = the 3,712-cell ladder on Hazard_Solver.</t>
         </is>
       </c>
     </row>
@@ -27999,7 +27999,7 @@
     <row r="5">
       <c r="N5" s="177" t="inlineStr">
         <is>
-          <t>Hazard: Brent when the VBA is loaded, else the in-cell ladder. Switch at CDS_Parameters!B30.</t>
+          <t>Brent strips straight off CDS_Schedule (CDS_StripHazard). Hazard_Solver is only the fallback when the VBA is not loaded. Switch at CDS_Parameters!B30.</t>
         </is>
       </c>
     </row>
@@ -28075,7 +28075,7 @@
         <v/>
       </c>
       <c r="D7" s="71">
-        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,IF(LEFT(CDS_Parameters!$B$30,5)="Brent",IFERROR(CDS_Hazard(Hazard_Solver!$D$7,Hazard_Solver!$F$7,Hazard_Solver!$B$8,Hazard_Solver!$D$8,Hazard_Solver!$F$8,CDS_Parameters!$B$26,Hazard_Solver!$F$10:$U$10,Hazard_Solver!$F$14:$U$14,Hazard_Solver!$F$12:$U$12,Hazard_Solver!$F$13:$U$13),Hazard_Solver!$B$46),Hazard_Solver!$B$46))</f>
+        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,IF(LEFT(CDS_Parameters!$B$30,5)="Brent",IFERROR(CDS_StripHazard(1,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46),Hazard_Solver!$B$46),Hazard_Solver!$B$46))</f>
         <v/>
       </c>
       <c r="E7" s="34">
@@ -28122,7 +28122,7 @@
         <v/>
       </c>
       <c r="D8" s="71">
-        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,IF(LEFT(CDS_Parameters!$B$30,5)="Brent",IFERROR(CDS_Hazard(Hazard_Solver!$D$50,Hazard_Solver!$F$50,Hazard_Solver!$B$51,Hazard_Solver!$D$51,Hazard_Solver!$F$51,CDS_Parameters!$B$26,Hazard_Solver!$F$53:$U$53,Hazard_Solver!$F$57:$U$57,Hazard_Solver!$F$55:$U$55,Hazard_Solver!$F$56:$U$56),Hazard_Solver!$B$89),Hazard_Solver!$B$89))</f>
+        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,IF(LEFT(CDS_Parameters!$B$30,5)="Brent",IFERROR(CDS_StripHazard(2,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46),Hazard_Solver!$B$89),Hazard_Solver!$B$89))</f>
         <v/>
       </c>
       <c r="E8" s="34">
@@ -28169,7 +28169,7 @@
         <v/>
       </c>
       <c r="D9" s="71">
-        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,IF(LEFT(CDS_Parameters!$B$30,5)="Brent",IFERROR(CDS_Hazard(Hazard_Solver!$D$93,Hazard_Solver!$F$93,Hazard_Solver!$B$94,Hazard_Solver!$D$94,Hazard_Solver!$F$94,CDS_Parameters!$B$26,Hazard_Solver!$F$96:$U$96,Hazard_Solver!$F$100:$U$100,Hazard_Solver!$F$98:$U$98,Hazard_Solver!$F$99:$U$99),Hazard_Solver!$B$132),Hazard_Solver!$B$132))</f>
+        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,IF(LEFT(CDS_Parameters!$B$30,5)="Brent",IFERROR(CDS_StripHazard(3,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46),Hazard_Solver!$B$132),Hazard_Solver!$B$132))</f>
         <v/>
       </c>
       <c r="E9" s="34">
@@ -28216,7 +28216,7 @@
         <v/>
       </c>
       <c r="D10" s="71">
-        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,IF(LEFT(CDS_Parameters!$B$30,5)="Brent",IFERROR(CDS_Hazard(Hazard_Solver!$D$136,Hazard_Solver!$F$136,Hazard_Solver!$B$137,Hazard_Solver!$D$137,Hazard_Solver!$F$137,CDS_Parameters!$B$26,Hazard_Solver!$F$139:$U$139,Hazard_Solver!$F$143:$U$143,Hazard_Solver!$F$141:$U$141,Hazard_Solver!$F$142:$U$142),Hazard_Solver!$B$175),Hazard_Solver!$B$175))</f>
+        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,IF(LEFT(CDS_Parameters!$B$30,5)="Brent",IFERROR(CDS_StripHazard(4,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46),Hazard_Solver!$B$175),Hazard_Solver!$B$175))</f>
         <v/>
       </c>
       <c r="E10" s="34">
@@ -28263,7 +28263,7 @@
         <v/>
       </c>
       <c r="D11" s="71">
-        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,IF(LEFT(CDS_Parameters!$B$30,5)="Brent",IFERROR(CDS_Hazard(Hazard_Solver!$D$179,Hazard_Solver!$F$179,Hazard_Solver!$B$180,Hazard_Solver!$D$180,Hazard_Solver!$F$180,CDS_Parameters!$B$26,Hazard_Solver!$F$182:$U$182,Hazard_Solver!$F$186:$U$186,Hazard_Solver!$F$184:$U$184,Hazard_Solver!$F$185:$U$185),Hazard_Solver!$B$218),Hazard_Solver!$B$218))</f>
+        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,IF(LEFT(CDS_Parameters!$B$30,5)="Brent",IFERROR(CDS_StripHazard(5,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46),Hazard_Solver!$B$218),Hazard_Solver!$B$218))</f>
         <v/>
       </c>
       <c r="E11" s="34">
@@ -28310,7 +28310,7 @@
         <v/>
       </c>
       <c r="D12" s="71">
-        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,IF(LEFT(CDS_Parameters!$B$30,5)="Brent",IFERROR(CDS_Hazard(Hazard_Solver!$D$222,Hazard_Solver!$F$222,Hazard_Solver!$B$223,Hazard_Solver!$D$223,Hazard_Solver!$F$223,CDS_Parameters!$B$26,Hazard_Solver!$F$225:$U$225,Hazard_Solver!$F$229:$U$229,Hazard_Solver!$F$227:$U$227,Hazard_Solver!$F$228:$U$228),Hazard_Solver!$B$261),Hazard_Solver!$B$261))</f>
+        <f>IF(CDS_Parameters!$B$17="Flat hazard rate",CDS_Parameters!$B$18,IF(LEFT(CDS_Parameters!$B$30,5)="Brent",IFERROR(CDS_StripHazard(6,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46),Hazard_Solver!$B$261),Hazard_Solver!$B$261))</f>
         <v/>
       </c>
       <c r="E12" s="34">

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -2503,7 +2503,11 @@
       <c r="F2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n"/>
+      <c r="A3" s="209" t="inlineStr">
+        <is>
+          <t>Blank template. Enter a ticker, or add names and spreads on Entities. Notional, coupon, recovery, tenor and direction below are conventions, not data - overtype as needed.</t>
+        </is>
+      </c>
       <c r="B3" s="11" t="n"/>
       <c r="C3" s="11" t="n"/>
       <c r="D3" s="11" t="n"/>
@@ -2528,14 +2532,10 @@
           <t>Reference entity ticker</t>
         </is>
       </c>
-      <c r="B5" s="213" t="inlineStr">
-        <is>
-          <t>HSBA LN Equity</t>
-        </is>
-      </c>
+      <c r="B5" s="213" t="n"/>
       <c r="C5" s="209" t="inlineStr">
         <is>
-          <t>BDP resolves the CDS tickers from this</t>
+          <t>type a Bloomberg ticker here</t>
         </is>
       </c>
       <c r="D5" s="212" t="n"/>
@@ -2672,8 +2672,15 @@
         </is>
       </c>
       <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
+      <c r="C14" s="209" t="inlineStr">
+        <is>
+          <t>has spreads</t>
+        </is>
+      </c>
+      <c r="D14" s="11">
+        <f>SUM(CDS_Quotes!$F$7:$F$12)&gt;0</f>
+        <v/>
+      </c>
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="11" t="n"/>
     </row>
@@ -2699,7 +2706,7 @@
         </is>
       </c>
       <c r="B16" s="184">
-        <f>IF(COUNTIF(CDS_Quotes!$H$7:$H$12,"BDP live")&gt;0,COUNTIF(CDS_Quotes!$H$7:$H$12,"BDP live")&amp;" of 6 live","manual / demo")</f>
+        <f>IF(NOT(SUM(CDS_Quotes!$F$7:$F$12)&gt;0),"none",IF(COUNTIF(CDS_Quotes!$H$7:$H$12,"BDP live")&gt;0,COUNTIF(CDS_Quotes!$H$7:$H$12,"BDP live")&amp;" of 6 live","manual"))</f>
         <v/>
       </c>
       <c r="C16" s="212" t="n"/>
@@ -2714,7 +2721,7 @@
         </is>
       </c>
       <c r="B17" s="184">
-        <f>IF(MAX(ABS(Hazard_Bootstrap!$J$7:$J$12))&lt;0.01,"reprices, max err "&amp;TEXT(MAX(ABS(Hazard_Bootstrap!$J$7:$J$12)),"0.00E+00")&amp;" bp","STRIP FAILED - check the quotes, see Model_Notes p.9")</f>
+        <f>IF(NOT(SUM(CDS_Quotes!$F$7:$F$12)&gt;0),"nothing to strip yet",IF(MAX(ABS(Hazard_Bootstrap!$J$7:$J$12))&lt;0.01,"reprices, max err "&amp;TEXT(MAX(ABS(Hazard_Bootstrap!$J$7:$J$12)),"0.00E+00")&amp;" bp","STRIP FAILED - check the quotes, see Model_Notes p.9"))</f>
         <v/>
       </c>
       <c r="C17" s="212" t="n"/>
@@ -2753,10 +2760,14 @@
         </is>
       </c>
       <c r="B20" s="170">
-        <f>CDS_Pricer!$B$15</f>
-        <v/>
-      </c>
-      <c r="C20" s="212" t="n"/>
+        <f>IF(NOT(SUM(CDS_Quotes!$F$7:$F$12)&gt;0),"",CDS_Pricer!$B$15)</f>
+        <v/>
+      </c>
+      <c r="C20" s="209" t="inlineStr">
+        <is>
+          <t>blank until spreads are entered</t>
+        </is>
+      </c>
       <c r="D20" s="11" t="n"/>
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="11" t="n"/>
@@ -2768,7 +2779,7 @@
         </is>
       </c>
       <c r="B21" s="170">
-        <f>CDS_Pricer!$B$31</f>
+        <f>IF(NOT(SUM(CDS_Quotes!$F$7:$F$12)&gt;0),"",CDS_Pricer!$B$31)</f>
         <v/>
       </c>
       <c r="C21" s="11" t="n"/>
@@ -2783,7 +2794,7 @@
         </is>
       </c>
       <c r="B22" s="170">
-        <f>CDS_Pricer!$B$32</f>
+        <f>IF(NOT(SUM(CDS_Quotes!$F$7:$F$12)&gt;0),"",CDS_Pricer!$B$32)</f>
         <v/>
       </c>
       <c r="C22" s="11" t="n"/>
@@ -2798,7 +2809,7 @@
         </is>
       </c>
       <c r="B23" s="216">
-        <f>CDS_Pricer!$B$33</f>
+        <f>IF(NOT(SUM(CDS_Quotes!$F$7:$F$12)&gt;0),"",CDS_Pricer!$B$33)</f>
         <v/>
       </c>
       <c r="C23" s="11" t="n"/>
@@ -2813,7 +2824,7 @@
         </is>
       </c>
       <c r="B24" s="217">
-        <f>CDS_Pricer!$B$34</f>
+        <f>IF(NOT(SUM(CDS_Quotes!$F$7:$F$12)&gt;0),"",CDS_Pricer!$B$34)</f>
         <v/>
       </c>
       <c r="C24" s="11" t="n"/>
@@ -2828,7 +2839,7 @@
         </is>
       </c>
       <c r="B25" s="216">
-        <f>CDS_Pricer!$B$35</f>
+        <f>IF(NOT(SUM(CDS_Quotes!$F$7:$F$12)&gt;0),"",CDS_Pricer!$B$35)</f>
         <v/>
       </c>
       <c r="C25" s="11" t="n"/>
@@ -2843,7 +2854,7 @@
         </is>
       </c>
       <c r="B26" s="216">
-        <f>CDS_Pricer!$B$36</f>
+        <f>IF(NOT(SUM(CDS_Quotes!$F$7:$F$12)&gt;0),"",CDS_Pricer!$B$36)</f>
         <v/>
       </c>
       <c r="C26" s="11" t="n"/>
@@ -2858,7 +2869,7 @@
         </is>
       </c>
       <c r="B27" s="216">
-        <f>CDS_Pricer!$B$37</f>
+        <f>IF(NOT(SUM(CDS_Quotes!$F$7:$F$12)&gt;0),"",CDS_Pricer!$B$37)</f>
         <v/>
       </c>
       <c r="C27" s="11" t="n"/>
@@ -2881,7 +2892,7 @@
         </is>
       </c>
       <c r="B29" s="216">
-        <f>CDS_Pricer!$B$22</f>
+        <f>IF(NOT(SUM(CDS_Quotes!$F$7:$F$12)&gt;0),"",CDS_Pricer!$B$22)</f>
         <v/>
       </c>
       <c r="C29" s="11" t="n"/>
@@ -2896,7 +2907,7 @@
         </is>
       </c>
       <c r="B30" s="216">
-        <f>CDS_Pricer!$B$23</f>
+        <f>IF(NOT(SUM(CDS_Quotes!$F$7:$F$12)&gt;0),"",CDS_Pricer!$B$23)</f>
         <v/>
       </c>
       <c r="C30" s="11" t="n"/>
@@ -2911,7 +2922,7 @@
         </is>
       </c>
       <c r="B31" s="216">
-        <f>CDS_Pricer!$B$24</f>
+        <f>IF(NOT(SUM(CDS_Quotes!$F$7:$F$12)&gt;0),"",CDS_Pricer!$B$24)</f>
         <v/>
       </c>
       <c r="C31" s="11" t="n"/>
@@ -2926,7 +2937,7 @@
         </is>
       </c>
       <c r="B32" s="216">
-        <f>CDS_Pricer!$B$25</f>
+        <f>IF(NOT(SUM(CDS_Quotes!$F$7:$F$12)&gt;0),"",CDS_Pricer!$B$25)</f>
         <v/>
       </c>
       <c r="C32" s="11" t="n"/>
@@ -5370,62 +5381,28 @@
         <f>IF(Entities!$N7="",0.4,Entities!$N7)</f>
         <v/>
       </c>
-      <c r="G5" s="111" t="n">
-        <v>46224</v>
-      </c>
+      <c r="G5" s="111" t="n"/>
       <c r="H5" s="64" t="n"/>
       <c r="I5" s="64" t="n"/>
       <c r="J5" s="64" t="n"/>
-      <c r="K5" s="64" t="n">
-        <v>55.1514</v>
-      </c>
+      <c r="K5" s="64" t="n"/>
       <c r="L5" s="64" t="n"/>
       <c r="M5" s="64" t="n"/>
-      <c r="O5" s="118" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="P5" s="64" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q5" s="111" t="n">
-        <v>48019</v>
-      </c>
-      <c r="R5" s="64" t="n">
-        <v>55.1514</v>
-      </c>
-      <c r="S5" s="148" t="n">
-        <v>-1.97596265</v>
-      </c>
-      <c r="T5" s="148" t="n">
-        <v>101.97596265</v>
-      </c>
-      <c r="U5" s="118" t="n">
-        <v>-197597</v>
-      </c>
-      <c r="V5" s="95" t="n">
-        <v>30</v>
-      </c>
-      <c r="W5" s="118" t="n">
-        <v>-8333</v>
-      </c>
-      <c r="X5" s="118" t="n">
-        <v>-205930</v>
-      </c>
-      <c r="Y5" s="118" t="n">
-        <v>4482.41</v>
-      </c>
-      <c r="Z5" s="118" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="AA5" s="118" t="n">
-        <v>72</v>
-      </c>
-      <c r="AB5" s="118" t="n">
-        <v>6197596</v>
-      </c>
-      <c r="AC5" s="64" t="n">
-        <v>0.0446</v>
-      </c>
+      <c r="O5" s="118" t="n"/>
+      <c r="P5" s="64" t="n"/>
+      <c r="Q5" s="111" t="n"/>
+      <c r="R5" s="64" t="n"/>
+      <c r="S5" s="148" t="n"/>
+      <c r="T5" s="148" t="n"/>
+      <c r="U5" s="118" t="n"/>
+      <c r="V5" s="95" t="n"/>
+      <c r="W5" s="118" t="n"/>
+      <c r="X5" s="118" t="n"/>
+      <c r="Y5" s="118" t="n"/>
+      <c r="Z5" s="118" t="n"/>
+      <c r="AA5" s="118" t="n"/>
+      <c r="AB5" s="118" t="n"/>
+      <c r="AC5" s="64" t="n"/>
       <c r="AF5" s="93">
         <f>IFERROR(BDP($B5,"CDS_SPREAD_TICKER_1Y"),"")</f>
         <v/>
@@ -5525,24 +5502,12 @@
         <v/>
       </c>
       <c r="G6" s="111" t="n"/>
-      <c r="H6" s="64" t="n">
-        <v>40</v>
-      </c>
-      <c r="I6" s="64" t="n">
-        <v>55</v>
-      </c>
-      <c r="J6" s="64" t="n">
-        <v>70</v>
-      </c>
-      <c r="K6" s="64" t="n">
-        <v>95</v>
-      </c>
-      <c r="L6" s="64" t="n">
-        <v>115</v>
-      </c>
-      <c r="M6" s="64" t="n">
-        <v>135</v>
-      </c>
+      <c r="H6" s="64" t="n"/>
+      <c r="I6" s="64" t="n"/>
+      <c r="J6" s="64" t="n"/>
+      <c r="K6" s="64" t="n"/>
+      <c r="L6" s="64" t="n"/>
+      <c r="M6" s="64" t="n"/>
       <c r="O6" s="118" t="n"/>
       <c r="P6" s="64" t="n"/>
       <c r="Q6" s="111" t="n"/>
@@ -6652,11 +6617,7 @@
           <t>Live name</t>
         </is>
       </c>
-      <c r="B4" s="178" t="inlineStr">
-        <is>
-          <t>DEMO curve (not market)</t>
-        </is>
-      </c>
+      <c r="B4" s="178" t="n"/>
       <c r="C4" s="177" t="inlineStr">
         <is>
           <t>only this name is stripped and priced</t>
@@ -6758,20 +6719,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="178" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="178" t="inlineStr">
-        <is>
-          <t>China CITIC Bank Intl</t>
-        </is>
-      </c>
+      <c r="A7" s="178" t="n"/>
+      <c r="B7" s="178" t="n"/>
       <c r="C7" s="178" t="n"/>
-      <c r="D7" s="178" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+      <c r="D7" s="178" t="n"/>
       <c r="E7" s="181" t="n"/>
       <c r="F7" s="182" t="n"/>
       <c r="G7" s="182" t="n"/>
@@ -6779,35 +6730,15 @@
       <c r="I7" s="182" t="n"/>
       <c r="J7" s="182" t="n"/>
       <c r="K7" s="182" t="n"/>
-      <c r="L7" s="178" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="M7" s="178" t="inlineStr">
-        <is>
-          <t>CR14</t>
-        </is>
-      </c>
-      <c r="N7" s="181" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="L7" s="178" t="n"/>
+      <c r="M7" s="178" t="n"/>
+      <c r="N7" s="181" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="178" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="178" t="inlineStr">
-        <is>
-          <t>DEMO curve (not market)</t>
-        </is>
-      </c>
+      <c r="A8" s="178" t="n"/>
+      <c r="B8" s="178" t="n"/>
       <c r="C8" s="178" t="n"/>
-      <c r="D8" s="178" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+      <c r="D8" s="178" t="n"/>
       <c r="E8" s="181" t="n"/>
       <c r="F8" s="182" t="n"/>
       <c r="G8" s="182" t="n"/>
@@ -6815,19 +6746,9 @@
       <c r="I8" s="182" t="n"/>
       <c r="J8" s="182" t="n"/>
       <c r="K8" s="182" t="n"/>
-      <c r="L8" s="178" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="M8" s="178" t="inlineStr">
-        <is>
-          <t>CR14</t>
-        </is>
-      </c>
-      <c r="N8" s="181" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="L8" s="178" t="n"/>
+      <c r="M8" s="178" t="n"/>
+      <c r="N8" s="181" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="178" t="n"/>
@@ -6843,9 +6764,7 @@
       <c r="K9" s="182" t="n"/>
       <c r="L9" s="178" t="n"/>
       <c r="M9" s="178" t="n"/>
-      <c r="N9" s="181" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="N9" s="181" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="178" t="n"/>
@@ -6861,9 +6780,7 @@
       <c r="K10" s="182" t="n"/>
       <c r="L10" s="178" t="n"/>
       <c r="M10" s="178" t="n"/>
-      <c r="N10" s="181" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="N10" s="181" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="178" t="n"/>
@@ -6879,9 +6796,7 @@
       <c r="K11" s="182" t="n"/>
       <c r="L11" s="178" t="n"/>
       <c r="M11" s="178" t="n"/>
-      <c r="N11" s="181" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="N11" s="181" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="178" t="n"/>
@@ -6897,9 +6812,7 @@
       <c r="K12" s="182" t="n"/>
       <c r="L12" s="178" t="n"/>
       <c r="M12" s="178" t="n"/>
-      <c r="N12" s="181" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="N12" s="181" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="178" t="n"/>
@@ -6915,9 +6828,7 @@
       <c r="K13" s="182" t="n"/>
       <c r="L13" s="178" t="n"/>
       <c r="M13" s="178" t="n"/>
-      <c r="N13" s="181" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="N13" s="181" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="178" t="n"/>
@@ -6933,9 +6844,7 @@
       <c r="K14" s="182" t="n"/>
       <c r="L14" s="178" t="n"/>
       <c r="M14" s="178" t="n"/>
-      <c r="N14" s="181" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="N14" s="181" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="178" t="n"/>
@@ -6951,9 +6860,7 @@
       <c r="K15" s="182" t="n"/>
       <c r="L15" s="178" t="n"/>
       <c r="M15" s="178" t="n"/>
-      <c r="N15" s="181" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="N15" s="181" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="178" t="n"/>
@@ -6969,9 +6876,7 @@
       <c r="K16" s="182" t="n"/>
       <c r="L16" s="178" t="n"/>
       <c r="M16" s="178" t="n"/>
-      <c r="N16" s="181" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="N16" s="181" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="67" t="inlineStr">
@@ -14040,7 +13945,7 @@
     <row r="42">
       <c r="A42" s="177" t="inlineStr">
         <is>
-          <t>Blank until a CDSW capture is typed into CDS_Entities O:AC. Notional, coupon, maturity and traded spread there are context for the capture, not compared.</t>
+          <t>Blank until a CDSW capture is typed into CDS_Entities O:AC for the live name. Notional, coupon, maturity and traded spread there are context, not compared.</t>
         </is>
       </c>
     </row>

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -3329,7 +3329,7 @@
       <c r="A54" s="11" t="n"/>
       <c r="B54" s="218" t="inlineStr">
         <is>
-          <t>Spreads are demo values. The SOFR curve is real market data; the credit curve is not.</t>
+          <t>No external validation of the credit curve: Bloomberg exports no hazard curve (Help Desk H#1330731572). The SOFR curve can be checked against S490; the strip cannot.</t>
         </is>
       </c>
       <c r="C54" s="11" t="n"/>
@@ -4164,7 +4164,7 @@
     <row r="49">
       <c r="A49" s="126" t="inlineStr">
         <is>
-          <t>Spreads here are demo values. The SOFR curve is real market data; the credit curve is not.</t>
+          <t>The SOFR curve can be validated against S490. The credit curve cannot - Bloomberg exports no hazard curve, so only the priced outputs can be compared.</t>
         </is>
       </c>
     </row>
@@ -6557,16 +6557,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="66" t="inlineStr">
-        <is>
-          <t>Row 5 is the reference screen already on file. Only its 5Y spread is known: the rest of its term structure was never captured, which is exactly what T3 is for. Its CDSW outputs ARE known and are the target to hit.</t>
-        </is>
-      </c>
+      <c r="A16" s="66" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="66" t="inlineStr">
-        <is>
-          <t>Row 5 is the pending real case: only its 5Y spread is known, so its strip fails - a 0/0/0/55/0/0 term structure is not strippable, which is the D8 condition. That is correct behaviour, not a fault. Row 6 is a DEMO curve so the module has something sane to run on until the real term structure arrives.</t>
+      <c r="A17" s="177" t="inlineStr">
+        <is>
+          <t>One row per name. Identity columns read from Entities. H:M take manual spreads, AF:AQ the two-step BDP pull, AR:AW what the strip actually uses.</t>
         </is>
       </c>
     </row>
@@ -7585,9 +7581,9 @@
         <f>CDS_Parameters!$B$4+3+IF(WEEKDAY(CDS_Parameters!$B$4,2)&gt;=3,2,0)</f>
         <v/>
       </c>
-      <c r="C21" s="65" t="inlineStr">
-        <is>
-          <t>T + 3 business days (p.6). 07/21/26 -&gt; 07/24/26, matching the screen.</t>
+      <c r="C21" s="177" t="inlineStr">
+        <is>
+          <t>T + 3 business days (p.7).</t>
         </is>
       </c>
     </row>
@@ -10061,7 +10057,7 @@
         <v/>
       </c>
       <c r="H7" s="93">
-        <f>IF(ISNUMBER(IFERROR(BDP(D7&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL (demo)")</f>
+        <f>IF(ISNUMBER(IFERROR(BDP(D7&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL")</f>
         <v/>
       </c>
       <c r="K7" s="137" t="n"/>
@@ -10096,7 +10092,7 @@
         <v/>
       </c>
       <c r="H8" s="93">
-        <f>IF(ISNUMBER(IFERROR(BDP(D8&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL (demo)")</f>
+        <f>IF(ISNUMBER(IFERROR(BDP(D8&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL")</f>
         <v/>
       </c>
       <c r="I8" s="66" t="inlineStr">
@@ -10140,7 +10136,7 @@
         <v/>
       </c>
       <c r="H9" s="93">
-        <f>IF(ISNUMBER(IFERROR(BDP(D9&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL (demo)")</f>
+        <f>IF(ISNUMBER(IFERROR(BDP(D9&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL")</f>
         <v/>
       </c>
       <c r="K9" s="139" t="inlineStr">
@@ -10179,7 +10175,7 @@
         <v/>
       </c>
       <c r="H10" s="93">
-        <f>IF(ISNUMBER(IFERROR(BDP(D10&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL (demo)")</f>
+        <f>IF(ISNUMBER(IFERROR(BDP(D10&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL")</f>
         <v/>
       </c>
       <c r="K10" s="137" t="n"/>
@@ -10214,7 +10210,7 @@
         <v/>
       </c>
       <c r="H11" s="93">
-        <f>IF(ISNUMBER(IFERROR(BDP(D11&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL (demo)")</f>
+        <f>IF(ISNUMBER(IFERROR(BDP(D11&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL")</f>
         <v/>
       </c>
       <c r="K11" s="137" t="inlineStr">
@@ -10253,7 +10249,7 @@
         <v/>
       </c>
       <c r="H12" s="93">
-        <f>IF(ISNUMBER(IFERROR(BDP(D12&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL (demo)")</f>
+        <f>IF(ISNUMBER(IFERROR(BDP(D12&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL")</f>
         <v/>
       </c>
       <c r="K12" s="139" t="inlineStr">
@@ -10270,9 +10266,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="66" t="inlineStr">
-        <is>
-          <t>Manual spreads in col E are DEMO values, not market. Col H shows which source each tenor is using. Replace col E or connect a terminal before using any CDS output.</t>
+      <c r="A14" s="177" t="inlineStr">
+        <is>
+          <t>Col E takes a manual spread when the pull is unavailable. Col H reports which source each tenor is using, live or manual.</t>
         </is>
       </c>
       <c r="K14" s="139" t="inlineStr">
@@ -13924,16 +13920,12 @@
     <row r="38">
       <c r="A38" s="66" t="inlineStr">
         <is>
-          <t>Upfront (3.2) above is the paper's total. How it splits into CDSW's Principal / Accrued / Cash is NOT given by the paper - that mapping is unverified and awaits a live screen check.</t>
+          <t>Upfront (3.2) above is the paper's total. How it splits into CDSW's Principal / Accrued / Cash is INFERRED, not confirmed by the paper. A capture with non-zero accrued would settle it.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="65" t="inlineStr">
-        <is>
-          <t>CDSW reference (CINDBK 5Y, 07/21/26): pts upfront -1.97596265, price 101.97596265, principal -197,597, accrued -8,333 (30d), cash -205,930, def exp 6,197,596. Targets for a like-for-like trade; the demo spreads here are not that entity.</t>
-        </is>
-      </c>
+      <c r="A39" s="65" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="67" t="inlineStr">

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -312,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="228">
+  <cellXfs count="229">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -633,6 +633,7 @@
     </xf>
     <xf numFmtId="176" fontId="14" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="176" fontId="21" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2658,9 +2659,20 @@
       <c r="F12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="215" t="n"/>
-      <c r="B13" s="215" t="n"/>
-      <c r="C13" s="212" t="n"/>
+      <c r="A13" s="215" t="inlineStr">
+        <is>
+          <t>VBA</t>
+        </is>
+      </c>
+      <c r="B13" s="228">
+        <f>IF(ISERROR(CDS_StripIterations()),"NOT LOADED - import bloomberg/vba/CDSStrip.bas (Alt+F11 &gt; File &gt; Import File) and save as .xlsm","loaded")</f>
+        <v/>
+      </c>
+      <c r="C13" s="209" t="inlineStr">
+        <is>
+          <t>hazards read #N/A whenever this says NOT LOADED</t>
+        </is>
+      </c>
       <c r="D13" s="212" t="n"/>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="11" t="n"/>
@@ -10434,6 +10446,10 @@
         </is>
       </c>
       <c r="L6" s="140" t="n"/>
+      <c r="N6" s="165">
+        <f>IF(ISERROR(CDS_StripIterations()),"#N/A below = CDSStrip.bas not imported, or the file is still .xlsx","VBA loaded - #N/A below would mean a quote that will not strip, see Model_Notes p.9")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -13953,7 +13953,7 @@
     <row r="42">
       <c r="A42" s="177" t="inlineStr">
         <is>
-          <t>Blank until a CDSW capture is typed into CDS_Entities O:AC for the live name. Notional, coupon, maturity and traded spread there are context, not compared.</t>
+          <t>Blank until a CDSW capture is typed into CDS_Entities O:AC for the live name. A zero there reads as no capture, not as a captured zero.</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
         </is>
       </c>
       <c r="B44" s="87">
-        <f>IFERROR(INDEX(CDS_Entities!$S$5:$S$14,CDS_Parameters!$B$28),"")</f>
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$S$5:$S$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$S$5:$S$14,CDS_Parameters!$B$28)),"")</f>
         <v/>
       </c>
       <c r="C44" s="93">
@@ -13994,7 +13994,7 @@
         <v/>
       </c>
       <c r="D44" s="93">
-        <f>IF(OR(B44="",NOT(ISNUMBER(B44))),"",C44-B44)</f>
+        <f>IF(OR(B44="",NOT(ISNUMBER(B44)),NOT(ISNUMBER(C44))),"",C44-B44)</f>
         <v/>
       </c>
     </row>
@@ -14005,7 +14005,7 @@
         </is>
       </c>
       <c r="B45" s="87">
-        <f>IFERROR(INDEX(CDS_Entities!$T$5:$T$14,CDS_Parameters!$B$28),"")</f>
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$T$5:$T$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$T$5:$T$14,CDS_Parameters!$B$28)),"")</f>
         <v/>
       </c>
       <c r="C45" s="93">
@@ -14013,7 +14013,7 @@
         <v/>
       </c>
       <c r="D45" s="93">
-        <f>IF(OR(B45="",NOT(ISNUMBER(B45))),"",C45-B45)</f>
+        <f>IF(OR(B45="",NOT(ISNUMBER(B45)),NOT(ISNUMBER(C45))),"",C45-B45)</f>
         <v/>
       </c>
     </row>
@@ -14024,7 +14024,7 @@
         </is>
       </c>
       <c r="B46" s="87">
-        <f>IFERROR(INDEX(CDS_Entities!$U$5:$U$14,CDS_Parameters!$B$28),"")</f>
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$U$5:$U$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$U$5:$U$14,CDS_Parameters!$B$28)),"")</f>
         <v/>
       </c>
       <c r="C46" s="93">
@@ -14032,7 +14032,7 @@
         <v/>
       </c>
       <c r="D46" s="93">
-        <f>IF(OR(B46="",NOT(ISNUMBER(B46))),"",C46-B46)</f>
+        <f>IF(OR(B46="",NOT(ISNUMBER(B46)),NOT(ISNUMBER(C46))),"",C46-B46)</f>
         <v/>
       </c>
     </row>
@@ -14043,7 +14043,7 @@
         </is>
       </c>
       <c r="B47" s="87">
-        <f>IFERROR(INDEX(CDS_Entities!$V$5:$V$14,CDS_Parameters!$B$28),"")</f>
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$V$5:$V$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$V$5:$V$14,CDS_Parameters!$B$28)),"")</f>
         <v/>
       </c>
       <c r="C47" s="93">
@@ -14051,7 +14051,7 @@
         <v/>
       </c>
       <c r="D47" s="93">
-        <f>IF(OR(B47="",NOT(ISNUMBER(B47))),"",C47-B47)</f>
+        <f>IF(OR(B47="",NOT(ISNUMBER(B47)),NOT(ISNUMBER(C47))),"",C47-B47)</f>
         <v/>
       </c>
     </row>
@@ -14062,7 +14062,7 @@
         </is>
       </c>
       <c r="B48" s="87">
-        <f>IFERROR(INDEX(CDS_Entities!$W$5:$W$14,CDS_Parameters!$B$28),"")</f>
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$W$5:$W$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$W$5:$W$14,CDS_Parameters!$B$28)),"")</f>
         <v/>
       </c>
       <c r="C48" s="93">
@@ -14070,7 +14070,7 @@
         <v/>
       </c>
       <c r="D48" s="93">
-        <f>IF(OR(B48="",NOT(ISNUMBER(B48))),"",C48-B48)</f>
+        <f>IF(OR(B48="",NOT(ISNUMBER(B48)),NOT(ISNUMBER(C48))),"",C48-B48)</f>
         <v/>
       </c>
     </row>
@@ -14081,7 +14081,7 @@
         </is>
       </c>
       <c r="B49" s="87">
-        <f>IFERROR(INDEX(CDS_Entities!$X$5:$X$14,CDS_Parameters!$B$28),"")</f>
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$X$5:$X$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$X$5:$X$14,CDS_Parameters!$B$28)),"")</f>
         <v/>
       </c>
       <c r="C49" s="93">
@@ -14089,7 +14089,7 @@
         <v/>
       </c>
       <c r="D49" s="93">
-        <f>IF(OR(B49="",NOT(ISNUMBER(B49))),"",C49-B49)</f>
+        <f>IF(OR(B49="",NOT(ISNUMBER(B49)),NOT(ISNUMBER(C49))),"",C49-B49)</f>
         <v/>
       </c>
     </row>
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="B50" s="87">
-        <f>IFERROR(INDEX(CDS_Entities!$AB$5:$AB$14,CDS_Parameters!$B$28),"")</f>
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$AB$5:$AB$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$AB$5:$AB$14,CDS_Parameters!$B$28)),"")</f>
         <v/>
       </c>
       <c r="C50" s="93">
@@ -14108,7 +14108,7 @@
         <v/>
       </c>
       <c r="D50" s="93">
-        <f>IF(OR(B50="",NOT(ISNUMBER(B50))),"",C50-B50)</f>
+        <f>IF(OR(B50="",NOT(ISNUMBER(B50)),NOT(ISNUMBER(C50))),"",C50-B50)</f>
         <v/>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="B51" s="180">
-        <f>IFERROR(INDEX(CDS_Entities!$Y$5:$Y$14,CDS_Parameters!$B$28),"")</f>
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$Y$5:$Y$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$Y$5:$Y$14,CDS_Parameters!$B$28)),"")</f>
         <v/>
       </c>
       <c r="C51" s="180">
@@ -14127,7 +14127,7 @@
         <v/>
       </c>
       <c r="D51" s="180">
-        <f>IF(OR(B51="",NOT(ISNUMBER(B51))),"",C51-B51)</f>
+        <f>IF(OR(B51="",NOT(ISNUMBER(B51)),NOT(ISNUMBER(C51))),"",C51-B51)</f>
         <v/>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
         </is>
       </c>
       <c r="B52" s="180">
-        <f>IFERROR(INDEX(CDS_Entities!$Z$5:$Z$14,CDS_Parameters!$B$28),"")</f>
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$Z$5:$Z$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$Z$5:$Z$14,CDS_Parameters!$B$28)),"")</f>
         <v/>
       </c>
       <c r="C52" s="180">
@@ -14146,7 +14146,7 @@
         <v/>
       </c>
       <c r="D52" s="180">
-        <f>IF(OR(B52="",NOT(ISNUMBER(B52))),"",C52-B52)</f>
+        <f>IF(OR(B52="",NOT(ISNUMBER(B52)),NOT(ISNUMBER(C52))),"",C52-B52)</f>
         <v/>
       </c>
     </row>
@@ -14157,7 +14157,7 @@
         </is>
       </c>
       <c r="B53" s="180">
-        <f>IFERROR(INDEX(CDS_Entities!$AA$5:$AA$14,CDS_Parameters!$B$28),"")</f>
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$AA$5:$AA$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$AA$5:$AA$14,CDS_Parameters!$B$28)),"")</f>
         <v/>
       </c>
       <c r="C53" s="180">
@@ -14165,7 +14165,7 @@
         <v/>
       </c>
       <c r="D53" s="180">
-        <f>IF(OR(B53="",NOT(ISNUMBER(B53))),"",C53-B53)</f>
+        <f>IF(OR(B53="",NOT(ISNUMBER(B53)),NOT(ISNUMBER(C53))),"",C53-B53)</f>
         <v/>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="B54" s="180">
-        <f>IFERROR(INDEX(CDS_Entities!$AC$5:$AC$14,CDS_Parameters!$B$28),"")</f>
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$AC$5:$AC$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$AC$5:$AC$14,CDS_Parameters!$B$28)),"")</f>
         <v/>
       </c>
       <c r="C54" s="180">

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -227,7 +227,7 @@
       <sz val="15"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -284,6 +284,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -312,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,6 +639,7 @@
     <xf numFmtId="176" fontId="14" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="176" fontId="21" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="17" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -10447,7 +10453,7 @@
       </c>
       <c r="L6" s="140" t="n"/>
       <c r="N6" s="165">
-        <f>IF(ISERROR(CDS_StripIterations()),"#N/A below = CDSStrip.bas not imported, or the file is still .xlsx","VBA loaded - #N/A below would mean a quote that will not strip, see Model_Notes p.9")</f>
+        <f>IF(ISERROR(CDS_StripIterations()),"Hazards read #N/A because CDSStrip.bas is not imported, or the file is still .xlsx","VBA loaded. #N/A below would mean a quote that will not strip, see Model_Notes p.9")</f>
         <v/>
       </c>
     </row>
@@ -13404,7 +13410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13694,58 +13700,90 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>RISK MEASURES (analytic, first-order)</t>
+      <c r="A21" s="67" t="inlineStr">
+        <is>
+          <t>RISK MEASURES (full revalue, curve re-stripped on each bump)</t>
+        </is>
+      </c>
+      <c r="N21" s="67" t="inlineStr">
+        <is>
+          <t>full-revalue working</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>CS01  (per +1bp spread)</t>
+          <t>CS01 / Spread DV01  (+1bp)</t>
         </is>
       </c>
       <c r="B22" s="44">
-        <f>B4*B12*0.0001</f>
-        <v/>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Spread DV01 = Notional*RPV01*1bp.</t>
-        </is>
+        <f>IF(OR($O$22="",$O$23=""),"",$O$23-$O$22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="177" t="inlineStr">
+        <is>
+          <t>Spread DV01: revalue at +1bp on every quote, curve re-stripped (p.9).</t>
+        </is>
+      </c>
+      <c r="N22" s="126" t="inlineStr">
+        <is>
+          <t>MV base</t>
+        </is>
+      </c>
+      <c r="O22" s="229">
+        <f>IFERROR(CDS_MarketValue(0,0,0,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$F$7:$F$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46,$B$4,$B$6,$B$8),"")</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>IR01 / DV01  (per +1bp SOFR)</t>
+          <t>IR DV01  (+1bp rates)</t>
         </is>
       </c>
       <c r="B23" s="44">
-        <f>-(B4*(1-B5)*SUMPRODUCT((CDS_Schedule!$C$7:$C$46&lt;=B8)*CDS_Schedule!$O$7:$O$46*CDS_Schedule!$F$7:$F$46)-B4*(B6/10000)*SUMPRODUCT((CDS_Schedule!$C$7:$C$46&lt;=B8)*(CDS_Schedule!$M$7:$M$46+CDS_Schedule!$N$7:$N$46)*CDS_Schedule!$F$7:$F$46))*0.0001</f>
-        <v/>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Net-leg dollar duration x 1bp (small for CDS).</t>
-        </is>
+        <f>IF(OR($O$22="",$O$24=""),"",$O$24-$O$22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="177" t="inlineStr">
+        <is>
+          <t>IR DV01: parallel +1bp on the discount curve, curve re-stripped.</t>
+        </is>
+      </c>
+      <c r="N23" s="126" t="inlineStr">
+        <is>
+          <t>MV  spreads +1bp</t>
+        </is>
+      </c>
+      <c r="O23" s="229">
+        <f>IFERROR(CDS_MarketValue(1,0,0,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$F$7:$F$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46,$B$4,$B$6,$B$8),"")</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Rec01  (per +1% recovery)</t>
+          <t>Rec01  (+1% recovery)</t>
         </is>
       </c>
       <c r="B24" s="44">
-        <f>-B4*SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)*0.01</f>
-        <v/>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Sticky-hazard (hazards held; proper Rec01 re-fits spreads).</t>
-        </is>
+        <f>IF(OR($O$22="",$O$25=""),"",$O$25-$O$22)</f>
+        <v/>
+      </c>
+      <c r="C24" s="177" t="inlineStr">
+        <is>
+          <t>Rec01: recovery +1%, hazards re-fitted so the quotes still reprice.</t>
+        </is>
+      </c>
+      <c r="N24" s="126" t="inlineStr">
+        <is>
+          <t>MV  rates +1bp</t>
+        </is>
+      </c>
+      <c r="O24" s="229">
+        <f>IFERROR(CDS_MarketValue(0,1,0,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$F$7:$F$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46,$B$4,$B$6,$B$8),"")</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -13763,6 +13801,15 @@
           <t>Default-now P&amp;L to your direction: LGD payout - current PV.</t>
         </is>
       </c>
+      <c r="N25" s="126" t="inlineStr">
+        <is>
+          <t>MV  recovery +1%</t>
+        </is>
+      </c>
+      <c r="O25" s="229">
+        <f>IFERROR(CDS_MarketValue(0,0,0.01,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$F$7:$F$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46,$B$4,$B$6,$B$8),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="94" t="inlineStr">
@@ -13773,6 +13820,11 @@
       <c r="B26" s="120">
         <f>B4*(B6/10000)*CDS_Parameters!$B$25</f>
         <v/>
+      </c>
+      <c r="N26" s="177" t="inlineStr">
+        <is>
+          <t>Each measure is a difference of two full valuations. Holding hazards fixed and multiplying RPV01 by a bump answers a different question - that is what made Rec01 come out with the wrong sign.</t>
+        </is>
       </c>
     </row>
     <row r="27">

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -10785,6 +10785,11 @@
           <t>One row per quarterly coupon period. DF(end) and DF(mid) interpolate the SOFR curve; hazard is the piecewise-constant lambda for the segment, by pay date. Q(end) = Q(prev)*exp(-hazard*dt). See Model_Notes.</t>
         </is>
       </c>
+      <c r="P4" s="177" t="inlineStr">
+        <is>
+          <t>Period 1 accrues from the 1st accrual start (previous IMM, adjusted), not from the valuation date. CDSW does the same and rebates the accrued via (3.2).</t>
+        </is>
+      </c>
       <c r="Q4" s="139" t="inlineStr">
         <is>
           <t>Z(.) is the bootstrapped SOFR curve via Curve_Interface (B-Model p.6).</t>
@@ -10886,7 +10891,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="18">
-        <f>VAL_DATE</f>
+        <f>CDS_Parameters!$B$23</f>
         <v/>
       </c>
       <c r="C7" s="18">
@@ -13880,12 +13885,12 @@
         </is>
       </c>
       <c r="B31" s="71">
-        <f>(($B$15/10000)-CDS_Parameters!$B$10/10000)*$B$12*100</f>
-        <v/>
-      </c>
-      <c r="C31" s="65" t="inlineStr">
-        <is>
-          <t>(S - C) * RPV01 * 100, protection buyer.</t>
+        <f>IF($B$27="","",IF($B$9="Buy protection",1,-1)*$B$27/$B$4*100)</f>
+        <v/>
+      </c>
+      <c r="C31" s="177" t="inlineStr">
+        <is>
+          <t>Principal / notional. From (3.2), not (S-C)*RPV01.</t>
         </is>
       </c>
     </row>
@@ -13896,10 +13901,10 @@
         </is>
       </c>
       <c r="B32" s="71">
-        <f>100-B31</f>
-        <v/>
-      </c>
-      <c r="C32" s="65" t="inlineStr">
+        <f>IF($B$31="","",100-$B$31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="177" t="inlineStr">
         <is>
           <t>100 - points upfront.</t>
         </is>
@@ -13912,12 +13917,12 @@
         </is>
       </c>
       <c r="B33" s="103">
-        <f>IF(CDS_Parameters!$B$15="Buy protection",1,-1)*(($B$15/10000)-CDS_Parameters!$B$10/10000)*$B$12*CDS_Parameters!$B$9</f>
-        <v/>
-      </c>
-      <c r="C33" s="65" t="inlineStr">
-        <is>
-          <t>Clean upfront in cash.</t>
+        <f>IF($B$27="","",IF($B$9="Buy protection",1,-1)*$B$27)</f>
+        <v/>
+      </c>
+      <c r="C33" s="177" t="inlineStr">
+        <is>
+          <t>Upfront (3.2) = Market Value / D(T_s) + Accrued Interest.</t>
         </is>
       </c>
     </row>
@@ -13960,10 +13965,10 @@
         </is>
       </c>
       <c r="B36" s="105">
-        <f>B33+B35</f>
-        <v/>
-      </c>
-      <c r="C36" s="65" t="inlineStr">
+        <f>IF(OR($B$33="",$B$35=""),"",$B$33+$B$35)</f>
+        <v/>
+      </c>
+      <c r="C36" s="177" t="inlineStr">
         <is>
           <t>Principal + accrued.</t>
         </is>
@@ -13976,19 +13981,19 @@
         </is>
       </c>
       <c r="B37" s="103">
-        <f>(1-CDS_Parameters!$B$8)*CDS_Parameters!$B$9-B33</f>
-        <v/>
-      </c>
-      <c r="C37" s="65" t="inlineStr">
+        <f>IF($B$33="","",(1-$B$5)*$B$4-$B$33)</f>
+        <v/>
+      </c>
+      <c r="C37" s="177" t="inlineStr">
         <is>
           <t>(1-R) * notional less the principal already paid.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="66" t="inlineStr">
-        <is>
-          <t>Upfront (3.2) above is the paper's total. How it splits into CDSW's Principal / Accrued / Cash is INFERRED, not confirmed by the paper. A capture with non-zero accrued would settle it.</t>
+      <c r="A38" s="177" t="inlineStr">
+        <is>
+          <t>CDSW order. Principal is (3.2) end to end: Market Value / D(T_s) + Accrued Interest, compounded to settlement three business days on. The (S-C)*RPV01 shortcut drops the -S*AI term and the compounding.</t>
         </is>
       </c>
     </row>

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -13703,6 +13703,10 @@
           <t>Protection leg minus premium leg, both to the pricing date.</t>
         </is>
       </c>
+      <c r="N20" s="66">
+        <f>IFERROR(CDS_RiskLoaded(),"CDSRisk.bas NOT imported")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="67" t="inlineStr">
@@ -13845,6 +13849,11 @@
       <c r="C27" s="65" t="inlineStr">
         <is>
           <t>Market Value / D(T_s) + Accrued Interest. Identically zero when C = S.</t>
+        </is>
+      </c>
+      <c r="N27" s="177" t="inlineStr">
+        <is>
+          <t>If N20 says loaded but O22:O25 are blank, the call itself is failing - not the module. Delete the IFERROR wrapper on O22 to see the real error.</t>
         </is>
       </c>
     </row>

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -9966,9 +9966,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="65" t="inlineStr">
-        <is>
-          <t>Step 1 (col D) resolves each tenor's CDS ticker from CDS_Parameters!B19; step 2 (col F) quotes it. Col E used only when BDP fails.</t>
+      <c r="A2" s="177" t="inlineStr">
+        <is>
+          <t>Col D resolves each tenor's CDS ticker from CDS_Parameters!B19; col F quotes it. An override from Entities (col E) BEATS the live pull - col H says which is in use.</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10067,7 @@
         <v/>
       </c>
       <c r="F7" s="63">
-        <f>IFERROR(BDP(D7&amp;" BEST Curncy","PX_LAST")+0,IFERROR(BDP(D7&amp;" BEST Curncy","PX_MID")+0,E7))</f>
+        <f>IF(AND(ISNUMBER(E7),E7&gt;0),E7,IFERROR(BDP(D7&amp;" BEST Curncy","PX_LAST")+0,IFERROR(BDP(D7&amp;" BEST Curncy","PX_MID")+0,0)))</f>
         <v/>
       </c>
       <c r="G7" s="36">
@@ -10075,7 +10075,7 @@
         <v/>
       </c>
       <c r="H7" s="93">
-        <f>IF(ISNUMBER(IFERROR(BDP(D7&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL")</f>
+        <f>IF(AND(ISNUMBER(E7),E7&gt;0),"OVERRIDE",IF(ISNUMBER(IFERROR(BDP(D7&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","none"))</f>
         <v/>
       </c>
       <c r="K7" s="137" t="n"/>
@@ -10102,7 +10102,7 @@
         <v/>
       </c>
       <c r="F8" s="63">
-        <f>IFERROR(BDP(D8&amp;" BEST Curncy","PX_LAST")+0,IFERROR(BDP(D8&amp;" BEST Curncy","PX_MID")+0,E8))</f>
+        <f>IF(AND(ISNUMBER(E8),E8&gt;0),E8,IFERROR(BDP(D8&amp;" BEST Curncy","PX_LAST")+0,IFERROR(BDP(D8&amp;" BEST Curncy","PX_MID")+0,0)))</f>
         <v/>
       </c>
       <c r="G8" s="36">
@@ -10110,7 +10110,7 @@
         <v/>
       </c>
       <c r="H8" s="93">
-        <f>IF(ISNUMBER(IFERROR(BDP(D8&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL")</f>
+        <f>IF(AND(ISNUMBER(E8),E8&gt;0),"OVERRIDE",IF(ISNUMBER(IFERROR(BDP(D8&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","none"))</f>
         <v/>
       </c>
       <c r="I8" s="66" t="inlineStr">
@@ -10146,7 +10146,7 @@
         <v/>
       </c>
       <c r="F9" s="63">
-        <f>IFERROR(BDP(D9&amp;" BEST Curncy","PX_LAST")+0,IFERROR(BDP(D9&amp;" BEST Curncy","PX_MID")+0,E9))</f>
+        <f>IF(AND(ISNUMBER(E9),E9&gt;0),E9,IFERROR(BDP(D9&amp;" BEST Curncy","PX_LAST")+0,IFERROR(BDP(D9&amp;" BEST Curncy","PX_MID")+0,0)))</f>
         <v/>
       </c>
       <c r="G9" s="36">
@@ -10154,7 +10154,7 @@
         <v/>
       </c>
       <c r="H9" s="93">
-        <f>IF(ISNUMBER(IFERROR(BDP(D9&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL")</f>
+        <f>IF(AND(ISNUMBER(E9),E9&gt;0),"OVERRIDE",IF(ISNUMBER(IFERROR(BDP(D9&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","none"))</f>
         <v/>
       </c>
       <c r="K9" s="139" t="inlineStr">
@@ -10185,7 +10185,7 @@
         <v/>
       </c>
       <c r="F10" s="63">
-        <f>IFERROR(BDP(D10&amp;" BEST Curncy","PX_LAST")+0,IFERROR(BDP(D10&amp;" BEST Curncy","PX_MID")+0,E10))</f>
+        <f>IF(AND(ISNUMBER(E10),E10&gt;0),E10,IFERROR(BDP(D10&amp;" BEST Curncy","PX_LAST")+0,IFERROR(BDP(D10&amp;" BEST Curncy","PX_MID")+0,0)))</f>
         <v/>
       </c>
       <c r="G10" s="36">
@@ -10193,7 +10193,7 @@
         <v/>
       </c>
       <c r="H10" s="93">
-        <f>IF(ISNUMBER(IFERROR(BDP(D10&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL")</f>
+        <f>IF(AND(ISNUMBER(E10),E10&gt;0),"OVERRIDE",IF(ISNUMBER(IFERROR(BDP(D10&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","none"))</f>
         <v/>
       </c>
       <c r="K10" s="137" t="n"/>
@@ -10220,7 +10220,7 @@
         <v/>
       </c>
       <c r="F11" s="63">
-        <f>IFERROR(BDP(D11&amp;" BEST Curncy","PX_LAST")+0,IFERROR(BDP(D11&amp;" BEST Curncy","PX_MID")+0,E11))</f>
+        <f>IF(AND(ISNUMBER(E11),E11&gt;0),E11,IFERROR(BDP(D11&amp;" BEST Curncy","PX_LAST")+0,IFERROR(BDP(D11&amp;" BEST Curncy","PX_MID")+0,0)))</f>
         <v/>
       </c>
       <c r="G11" s="36">
@@ -10228,7 +10228,7 @@
         <v/>
       </c>
       <c r="H11" s="93">
-        <f>IF(ISNUMBER(IFERROR(BDP(D11&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL")</f>
+        <f>IF(AND(ISNUMBER(E11),E11&gt;0),"OVERRIDE",IF(ISNUMBER(IFERROR(BDP(D11&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","none"))</f>
         <v/>
       </c>
       <c r="K11" s="137" t="inlineStr">
@@ -10259,7 +10259,7 @@
         <v/>
       </c>
       <c r="F12" s="63">
-        <f>IFERROR(BDP(D12&amp;" BEST Curncy","PX_LAST")+0,IFERROR(BDP(D12&amp;" BEST Curncy","PX_MID")+0,E12))</f>
+        <f>IF(AND(ISNUMBER(E12),E12&gt;0),E12,IFERROR(BDP(D12&amp;" BEST Curncy","PX_LAST")+0,IFERROR(BDP(D12&amp;" BEST Curncy","PX_MID")+0,0)))</f>
         <v/>
       </c>
       <c r="G12" s="36">
@@ -10267,7 +10267,7 @@
         <v/>
       </c>
       <c r="H12" s="93">
-        <f>IF(ISNUMBER(IFERROR(BDP(D12&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","MANUAL")</f>
+        <f>IF(AND(ISNUMBER(E12),E12&gt;0),"OVERRIDE",IF(ISNUMBER(IFERROR(BDP(D12&amp;" BEST Curncy","PX_LAST")+0,"")),"BDP live","none"))</f>
         <v/>
       </c>
       <c r="K12" s="139" t="inlineStr">

--- a/bloomberg/CDS_Pricer.xlsx
+++ b/bloomberg/CDS_Pricer.xlsx
@@ -10303,9 +10303,14 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="65" t="inlineStr">
-        <is>
-          <t>Help Desk H#1330731572. Step 1 BDP(ticker,"CDS_SPREAD_TICKER_nY"); step 2 BDP(returned&amp;" BEST Curncy","PX_LAST"). Tenors 1Y/3Y/5Y/7Y/10Y.</t>
+      <c r="A16" s="67" t="inlineStr">
+        <is>
+          <t>Quote source</t>
+        </is>
+      </c>
+      <c r="B16" s="184" t="inlineStr">
+        <is>
+          <t>BEST, PX_LAST (falls back to PX_MID)</t>
         </is>
       </c>
       <c r="K16" s="139" t="inlineStr">
@@ -10315,9 +10320,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="66" t="inlineStr">
-        <is>
-          <t>No Bloomberg export exists for zero-coupon CDS spreads or bootstrapped hazard rates (Help Desk). The credit curve has no external ground truth, unlike the SOFR curve.</t>
+      <c r="A17" s="177" t="inlineStr">
+        <is>
+          <t>Col D resolves the ticker, col F quotes it as &lt;ticker&gt; &amp; " BEST Curncy". That is the BEST composite. CDSW's CDS Curve dropdown must be set to BEST to compare like with like - CMAN, CMAI, CMAL and the rest are single-contributor curves and will not match.</t>
         </is>
       </c>
       <c r="K17" s="139" t="inlineStr">
@@ -10327,9 +10332,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="65" t="inlineStr">
-        <is>
-          <t>Bloomberg suggest the credit triangle, hazard = S/(1-R). Exact only for a flat curve. CDSStrip.CDS_StripHazard bootstraps properly; CDS_Validation 13-18 compares the two.</t>
+      <c r="A18" s="177" t="inlineStr">
+        <is>
+          <t>If BEST on CDSW still disagrees, the difference is the instrument, not the source: check the doc clause behind the resolved ticker against the XR14 on the CDSW deal.</t>
         </is>
       </c>
     </row>
